--- a/Project_1_May2026_Update.xlsx
+++ b/Project_1_May2026_Update.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LSQ_Returns" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP500TR_Returns" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NVIDIA_Returns" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Updated_Table_2" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Updated_Table_4" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regression" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Serial_Correlation" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Newey_West" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="LSQ_Returns" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SP500TR_Returns" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="NVIDIA_Returns" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Verification" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Updated_Table_2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Updated_Table_4" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Regression" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Serial_Correlation" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Newey_West" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="59" customWidth="1" min="2" max="2"/>
+    <col width="53" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>project1_may2026_deliverables\data\LSQ_latest_spartan.pdf</t>
+          <t>data/LSQ_latest_spartan.pdf</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-12T02:01:28</t>
+          <t>2026-06-12T16:40:04</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4131,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.02285956720180793</v>
+        <v>0.02285929685021193</v>
       </c>
     </row>
     <row r="3">
@@ -4146,7 +4146,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.07052604356294512</v>
+        <v>-0.07052562470952384</v>
       </c>
     </row>
     <row r="4">
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.07476805121952501</v>
+        <v>0.07476813959401474</v>
       </c>
     </row>
     <row r="5">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.04250421583286856</v>
+        <v>-0.04250447489194809</v>
       </c>
     </row>
     <row r="6">
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.3839884098304449</v>
+        <v>0.3839885382872792</v>
       </c>
     </row>
     <row r="7">
@@ -4206,7 +4206,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.002509417020269522</v>
+        <v>0.002509685278008655</v>
       </c>
     </row>
     <row r="8">
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.1241703906311096</v>
+        <v>0.1241695546462829</v>
       </c>
     </row>
     <row r="9">
@@ -4236,7 +4236,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.042642832566262</v>
+        <v>0.04264380498718268</v>
       </c>
     </row>
     <row r="10">
@@ -4251,7 +4251,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.05599341871636443</v>
+        <v>0.05599305070825578</v>
       </c>
     </row>
     <row r="11">
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.15684926079897</v>
+        <v>0.1568492438443789</v>
       </c>
     </row>
     <row r="12">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.02949579108762135</v>
+        <v>-0.02949597520951819</v>
       </c>
     </row>
     <row r="13">
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.03525258070522685</v>
+        <v>-0.03525248782048929</v>
       </c>
     </row>
     <row r="14">
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.2702840449401422</v>
+        <v>0.2702843443308522</v>
       </c>
     </row>
     <row r="15">
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.01545940462696405</v>
+        <v>-0.01545979379661466</v>
       </c>
     </row>
     <row r="16">
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.042422091310234</v>
+        <v>-0.04242177889535137</v>
       </c>
     </row>
     <row r="17">
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.02888714967079109</v>
+        <v>-0.02888722818772815</v>
       </c>
     </row>
     <row r="18">
@@ -4371,7 +4371,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.1213427060924364</v>
+        <v>0.1213426956799988</v>
       </c>
     </row>
     <row r="19">
@@ -4386,7 +4386,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.06004776811367074</v>
+        <v>-0.06004776351854657</v>
       </c>
     </row>
     <row r="20">
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0336005150522356</v>
+        <v>0.03360075655618111</v>
       </c>
     </row>
     <row r="21">
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.1462879444147493</v>
+        <v>0.1462871894254973</v>
       </c>
     </row>
     <row r="22">
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.001758746802028588</v>
+        <v>0.001759297122216452</v>
       </c>
     </row>
     <row r="23">
@@ -4446,7 +4446,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.2497686501646835</v>
+        <v>-0.2497686673607447</v>
       </c>
     </row>
     <row r="24">
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.2248255762550559</v>
+        <v>-0.2248259008642258</v>
       </c>
     </row>
     <row r="25">
@@ -4476,7 +4476,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.182319165739989</v>
+        <v>-0.1823190318263749</v>
       </c>
     </row>
     <row r="26">
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.07677896314296184</v>
+        <v>0.07677889655705639</v>
       </c>
     </row>
     <row r="27">
@@ -4506,7 +4506,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.07311310865577525</v>
+        <v>0.07311291750783333</v>
       </c>
     </row>
     <row r="28">
@@ -4521,7 +4521,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.1652080591136154</v>
+        <v>0.1652085475935621</v>
       </c>
     </row>
     <row r="29">
@@ -4536,7 +4536,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.008019905667705052</v>
+        <v>0.008020011943399297</v>
       </c>
     </row>
     <row r="30">
@@ -4551,7 +4551,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.2516023421696284</v>
+        <v>-0.2516024481115456</v>
       </c>
     </row>
     <row r="31">
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.2137715849809971</v>
+        <v>0.2137713567816002</v>
       </c>
     </row>
     <row r="32">
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.02733957678342636</v>
+        <v>0.02733934597857735</v>
       </c>
     </row>
     <row r="33">
@@ -4596,7 +4596,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-0.007171650506887617</v>
+        <v>-0.00717119740444272</v>
       </c>
     </row>
     <row r="34">
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.04019053924864879</v>
+        <v>0.04019030521676048</v>
       </c>
     </row>
     <row r="35">
@@ -4626,7 +4626,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.1548228494725041</v>
+        <v>0.1548226459888284</v>
       </c>
     </row>
     <row r="36">
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.07820089684145959</v>
+        <v>0.07820120572670053</v>
       </c>
     </row>
     <row r="37">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.08643395566166379</v>
+        <v>0.086433778525842</v>
       </c>
     </row>
     <row r="38">
@@ -4671,7 +4671,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.004802033998286603</v>
+        <v>0.00480219782459379</v>
       </c>
     </row>
     <row r="39">
@@ -4686,7 +4686,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.1422831798125233</v>
+        <v>0.1422832609445948</v>
       </c>
     </row>
     <row r="40">
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-0.02337295768505621</v>
+        <v>-0.02337295602496314</v>
       </c>
     </row>
     <row r="41">
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.1088013073235865</v>
+        <v>0.1088010812327445</v>
       </c>
     </row>
     <row r="42">
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.2146567229905958</v>
+        <v>0.2146575382268885</v>
       </c>
     </row>
     <row r="43">
@@ -4746,7 +4746,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.07010912259352398</v>
+        <v>0.07010843675235567</v>
       </c>
     </row>
     <row r="44">
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.1181168732147577</v>
+        <v>0.1181168851353178</v>
       </c>
     </row>
     <row r="45">
@@ -4776,7 +4776,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.2599918765598133</v>
+        <v>0.2599920805477076</v>
       </c>
     </row>
     <row r="46">
@@ -4791,7 +4791,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.01166416049041263</v>
+        <v>0.01166394474764676</v>
       </c>
     </row>
     <row r="47">
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-0.07337155693543396</v>
+        <v>-0.07337114246742593</v>
       </c>
     </row>
     <row r="48">
@@ -4821,7 +4821,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.06921181850047553</v>
+        <v>0.06921179734475302</v>
       </c>
     </row>
     <row r="49">
@@ -4836,7 +4836,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-0.02585514253340404</v>
+        <v>-0.02585556396201738</v>
       </c>
     </row>
     <row r="50">
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-0.004704362017168506</v>
+        <v>-0.004704069239626296</v>
       </c>
     </row>
     <row r="51">
@@ -4866,7 +4866,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.05579406449729629</v>
+        <v>0.05579405627172118</v>
       </c>
     </row>
     <row r="52">
@@ -4881,7 +4881,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-0.02670521194141107</v>
+        <v>-0.02670541766719159</v>
       </c>
     </row>
     <row r="53">
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.1248425350174647</v>
+        <v>0.1248426157068663</v>
       </c>
     </row>
     <row r="54">
@@ -4911,7 +4911,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.08228136449543633</v>
+        <v>0.08228110940569455</v>
       </c>
     </row>
     <row r="55">
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.2313400691415173</v>
+        <v>0.2313404772121077</v>
       </c>
     </row>
     <row r="56">
@@ -4941,7 +4941,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-0.02494877269816898</v>
+        <v>-0.02494867460315708</v>
       </c>
     </row>
     <row r="57">
@@ -4956,7 +4956,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.1480076467541931</v>
+        <v>0.1480073232301915</v>
       </c>
     </row>
     <row r="58">
@@ -4971,7 +4971,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-0.07439577103852923</v>
+        <v>-0.07439560639689813</v>
       </c>
     </row>
     <row r="59">
@@ -4986,7 +4986,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.2341670254606225</v>
+        <v>0.2341669114563416</v>
       </c>
     </row>
     <row r="60">
@@ -5001,7 +5001,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.2780538211469497</v>
+        <v>0.278053372066061</v>
       </c>
     </row>
     <row r="61">
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-0.09992038929948788</v>
+        <v>-0.0999201901568485</v>
       </c>
     </row>
     <row r="62">
@@ -5031,7 +5031,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-0.1673525319215579</v>
+        <v>-0.1673522934414061</v>
       </c>
     </row>
     <row r="63">
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-0.004124780510119108</v>
+        <v>-0.004125014290136009</v>
       </c>
     </row>
     <row r="64">
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.1189665252488112</v>
+        <v>0.1189666130487661</v>
       </c>
     </row>
     <row r="65">
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-0.3201581692865763</v>
+        <v>-0.3201583796553739</v>
       </c>
     </row>
     <row r="66">
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.006739453326456868</v>
+        <v>0.006739971141816792</v>
       </c>
     </row>
     <row r="67">
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-0.188142645455245</v>
+        <v>-0.1881427605859263</v>
       </c>
     </row>
     <row r="68">
@@ -5121,7 +5121,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.1984195361864451</v>
+        <v>0.1984193343680376</v>
       </c>
     </row>
     <row r="69">
@@ -5136,7 +5136,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-0.168969954550624</v>
+        <v>-0.1689698670395005</v>
       </c>
     </row>
     <row r="70">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-0.1957732395604797</v>
+        <v>-0.1957731128449735</v>
       </c>
     </row>
     <row r="71">
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0.1122013345021275</v>
+        <v>0.1122011592615861</v>
       </c>
     </row>
     <row r="72">
@@ -5181,7 +5181,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.2538340326238617</v>
+        <v>0.2538341742905792</v>
       </c>
     </row>
     <row r="73">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-0.136220466658155</v>
+        <v>-0.1362205642538448</v>
       </c>
     </row>
     <row r="74">
@@ -5211,7 +5211,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.3368686043227049</v>
+        <v>0.3368688659330197</v>
       </c>
     </row>
     <row r="75">
@@ -5226,7 +5226,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.1883094486906212</v>
+        <v>0.1883092161517261</v>
       </c>
     </row>
     <row r="76">
@@ -5256,7 +5256,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-0.0008382849217655197</v>
+        <v>-0.0008381472836533899</v>
       </c>
     </row>
     <row r="78">
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.363436671024731</v>
+        <v>0.3634366209600322</v>
       </c>
     </row>
     <row r="79">
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.1180947111783819</v>
+        <v>0.1180945982127071</v>
       </c>
     </row>
     <row r="80">
@@ -5316,7 +5316,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0.05619639406771304</v>
+        <v>0.05619647586122234</v>
       </c>
     </row>
     <row r="82">
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-0.1186506332668394</v>
+        <v>-0.1186507015199146</v>
       </c>
     </row>
     <row r="83">
@@ -5346,7 +5346,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-0.0624297173404752</v>
+        <v>-0.0624299809416361</v>
       </c>
     </row>
     <row r="84">
@@ -5361,7 +5361,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>0.146885644002696</v>
+        <v>0.1468857790179774</v>
       </c>
     </row>
     <row r="85">
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>0.05884105488915115</v>
+        <v>0.05884106450555349</v>
       </c>
     </row>
     <row r="86">
@@ -5391,7 +5391,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>0.2425268114256502</v>
+        <v>0.2425270032073543</v>
       </c>
     </row>
     <row r="87">
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>0.2858093415179341</v>
+        <v>0.2858092172967774</v>
       </c>
     </row>
     <row r="88">
@@ -5421,7 +5421,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>0.1421276597389094</v>
+        <v>0.1421278666884103</v>
       </c>
     </row>
     <row r="89">
@@ -5436,7 +5436,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-0.04371539540089564</v>
+        <v>-0.04371539170313565</v>
       </c>
     </row>
     <row r="90">
@@ -5451,7 +5451,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>0.2688711393283107</v>
+        <v>0.2688710270916701</v>
       </c>
     </row>
     <row r="91">
@@ -5481,7 +5481,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-0.05269877881153473</v>
+        <v>-0.05269871694819739</v>
       </c>
     </row>
     <row r="93">
@@ -5496,7 +5496,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>0.02008221224001749</v>
+        <v>0.02008208031891745</v>
       </c>
     </row>
     <row r="94">
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>0.01734106599608709</v>
+        <v>0.01734106710624794</v>
       </c>
     </row>
     <row r="95">
@@ -5526,7 +5526,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>0.09330822424722918</v>
+        <v>0.09330816719098234</v>
       </c>
     </row>
     <row r="96">
@@ -5541,7 +5541,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>0.04135289270640019</v>
+        <v>0.04135312769620292</v>
       </c>
     </row>
     <row r="97">
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-0.02864379346153278</v>
+        <v>-0.02864401138199291</v>
       </c>
     </row>
     <row r="98">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-0.1058287148205893</v>
+        <v>-0.1058285561594333</v>
       </c>
     </row>
     <row r="99">
@@ -5586,7 +5586,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>0.04039309306242167</v>
+        <v>0.04039296321972285</v>
       </c>
     </row>
     <row r="100">
@@ -5601,7 +5601,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-0.1324047519202285</v>
+        <v>-0.1324046988533616</v>
       </c>
     </row>
     <row r="101">
@@ -5646,7 +5646,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>0.16917037363203</v>
+        <v>0.1691704867095978</v>
       </c>
     </row>
     <row r="104">
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>0.1259088530315122</v>
+        <v>0.1259087441380393</v>
       </c>
     </row>
     <row r="105">
@@ -5676,7 +5676,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>-0.02074555918313137</v>
+        <v>-0.02074547328268472</v>
       </c>
     </row>
     <row r="106">
@@ -5691,7 +5691,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>0.07119086207604353</v>
+        <v>0.07119068039067433</v>
       </c>
     </row>
     <row r="107">
@@ -5706,7 +5706,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>0.08533291274421861</v>
+        <v>0.08533300162257662</v>
       </c>
     </row>
     <row r="108">
@@ -6273,7 +6273,7 @@
         <v>3.495221238938055</v>
       </c>
       <c r="C2" t="n">
-        <v>4.847036963910896</v>
+        <v>4.847037080431163</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>3.422856966733567</v>
       </c>
       <c r="C3" t="n">
-        <v>3.957808638228077</v>
+        <v>3.957808721770739</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>3.697222222222224</v>
       </c>
       <c r="C6" t="n">
-        <v>12.37256045848575</v>
+        <v>12.37256016259983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>-0.8680000000000002</v>
       </c>
       <c r="C7" t="n">
-        <v>-8.887043413688216</v>
+        <v>-8.887042544526659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>21.97</v>
       </c>
       <c r="C8" t="n">
-        <v>38.39884098304449</v>
+        <v>38.39885382872792</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>-2.2</v>
       </c>
       <c r="C9" t="n">
-        <v>-32.01581692865763</v>
+        <v>-32.01583796553739</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>3.495221238938055</v>
       </c>
       <c r="C10" t="n">
-        <v>4.847036963910896</v>
+        <v>4.847037080431163</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>3.992318974200495</v>
       </c>
       <c r="C11" t="n">
-        <v>13.47440125568114</v>
+        <v>13.47440142378295</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>2.614250975720806</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.04823758466202541</v>
+        <v>-0.0482374382237372</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>8.093367320642244</v>
       </c>
       <c r="C13" t="n">
-        <v>0.06682697879962607</v>
+        <v>0.06682952564226774</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>0.8754864682719924</v>
       </c>
       <c r="C14" t="n">
-        <v>0.359721880916027</v>
+        <v>0.3597218850757939</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>14.35776078315886</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6802039332048143</v>
+        <v>0.6802039139380652</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>92.0046082949309</v>
       </c>
       <c r="C16" t="n">
-        <v>2.540768823291434</v>
+        <v>2.540769011019441</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/Project_1_May2026_Update.xlsx
+++ b/Project_1_May2026_Update.xlsx
@@ -485,7 +485,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-12T16:40:04</t>
+          <t>2026-06-12T16:45:01</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4131,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.02285929685021193</v>
+        <v>0.02285929269854603</v>
       </c>
     </row>
     <row r="3">
@@ -4146,7 +4146,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.07052562470952384</v>
+        <v>-0.07052605608550622</v>
       </c>
     </row>
     <row r="4">
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.07476813959401474</v>
+        <v>0.07476825653475538</v>
       </c>
     </row>
     <row r="5">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.04250447489194809</v>
+        <v>-0.0425039492189323</v>
       </c>
     </row>
     <row r="6">
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.3839885382872792</v>
+        <v>0.3839881172764594</v>
       </c>
     </row>
     <row r="7">
@@ -4206,7 +4206,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.002509685278008655</v>
+        <v>0.00250948391640704</v>
       </c>
     </row>
     <row r="8">
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.1241695546462829</v>
+        <v>0.1241698388455315</v>
       </c>
     </row>
     <row r="9">
@@ -4236,7 +4236,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.04264380498718268</v>
+        <v>0.0426437999119289</v>
       </c>
     </row>
     <row r="10">
@@ -4251,7 +4251,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.05599305070825578</v>
+        <v>0.05599178869589605</v>
       </c>
     </row>
     <row r="11">
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.1568492438443789</v>
+        <v>0.1568504943397173</v>
       </c>
     </row>
     <row r="12">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.02949597520951819</v>
+        <v>-0.02949606864849486</v>
       </c>
     </row>
     <row r="13">
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.03525248782048929</v>
+        <v>-0.03525249121455731</v>
       </c>
     </row>
     <row r="14">
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.2702843443308522</v>
+        <v>0.2702844711013088</v>
       </c>
     </row>
     <row r="15">
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.04242177889535137</v>
+        <v>-0.04242161930278476</v>
       </c>
     </row>
     <row r="17">
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.02888722818772815</v>
+        <v>-0.0288874733673059</v>
       </c>
     </row>
     <row r="18">
@@ -4371,7 +4371,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.1213426956799988</v>
+        <v>0.1213428777127814</v>
       </c>
     </row>
     <row r="19">
@@ -4386,7 +4386,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.06004776351854657</v>
+        <v>-0.06004798849684123</v>
       </c>
     </row>
     <row r="20">
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.03360075655618111</v>
+        <v>0.03360084344043912</v>
       </c>
     </row>
     <row r="21">
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.1462871894254973</v>
+        <v>0.1462875160142236</v>
       </c>
     </row>
     <row r="22">
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.001759297122216452</v>
+        <v>0.001759021901640123</v>
       </c>
     </row>
     <row r="23">
@@ -4446,7 +4446,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.2497686673607447</v>
+        <v>-0.2497688216809697</v>
       </c>
     </row>
     <row r="24">
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.2248259008642258</v>
+        <v>-0.2248255968109131</v>
       </c>
     </row>
     <row r="25">
@@ -4476,7 +4476,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.1823190318263749</v>
+        <v>-0.1823190103222162</v>
       </c>
     </row>
     <row r="26">
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.07677889655705639</v>
+        <v>0.07677874123501627</v>
       </c>
     </row>
     <row r="27">
@@ -4506,7 +4506,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.07311291750783333</v>
+        <v>0.07311311845011881</v>
       </c>
     </row>
     <row r="28">
@@ -4521,7 +4521,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.1652085475935621</v>
+        <v>0.1652084542407335</v>
       </c>
     </row>
     <row r="29">
@@ -4536,7 +4536,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.008020011943399297</v>
+        <v>0.008019689679491959</v>
       </c>
     </row>
     <row r="30">
@@ -4551,7 +4551,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.2516024481115456</v>
+        <v>-0.2516023421696284</v>
       </c>
     </row>
     <row r="31">
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.2137713567816002</v>
+        <v>0.2137714429675359</v>
       </c>
     </row>
     <row r="32">
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.02733934597857735</v>
+        <v>0.02733981398583518</v>
       </c>
     </row>
     <row r="33">
@@ -4596,7 +4596,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-0.00717119740444272</v>
+        <v>-0.007172105242657989</v>
       </c>
     </row>
     <row r="34">
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.04019030521676048</v>
+        <v>0.04019066779037428</v>
       </c>
     </row>
     <row r="35">
@@ -4626,7 +4626,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.1548226459888284</v>
+        <v>0.1548229938985013</v>
       </c>
     </row>
     <row r="36">
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.07820120572670053</v>
+        <v>0.07820119079120702</v>
       </c>
     </row>
     <row r="37">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.086433778525842</v>
+        <v>0.08643349751164076</v>
       </c>
     </row>
     <row r="38">
@@ -4671,7 +4671,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.00480219782459379</v>
+        <v>0.004802361259457877</v>
       </c>
     </row>
     <row r="39">
@@ -4686,7 +4686,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.1422832609445948</v>
+        <v>0.1422830871367302</v>
       </c>
     </row>
     <row r="40">
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-0.02337295602496314</v>
+        <v>-0.02337281563258986</v>
       </c>
     </row>
     <row r="41">
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.1088010812327445</v>
+        <v>0.1088010733200719</v>
       </c>
     </row>
     <row r="42">
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.2146575382268885</v>
+        <v>0.2146569338393018</v>
       </c>
     </row>
     <row r="43">
@@ -4746,7 +4746,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.07010843675235567</v>
+        <v>0.07010911502193151</v>
       </c>
     </row>
     <row r="44">
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.1181168851353178</v>
+        <v>0.1181166594507639</v>
       </c>
     </row>
     <row r="45">
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-0.07337114246742593</v>
+        <v>-0.07337135489685598</v>
       </c>
     </row>
     <row r="48">
@@ -4821,7 +4821,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.06921179734475302</v>
+        <v>0.06921196604474256</v>
       </c>
     </row>
     <row r="49">
@@ -4836,7 +4836,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-0.02585556396201738</v>
+        <v>-0.02585542286987719</v>
       </c>
     </row>
     <row r="50">
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-0.004704069239626296</v>
+        <v>-0.004703922160598006</v>
       </c>
     </row>
     <row r="51">
@@ -4866,7 +4866,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.05579405627172118</v>
+        <v>0.05579367536488289</v>
       </c>
     </row>
     <row r="52">
@@ -4881,7 +4881,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-0.02670541766719159</v>
+        <v>-0.02670528175968867</v>
       </c>
     </row>
     <row r="53">
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.1248426157068663</v>
+        <v>0.1248427591747725</v>
       </c>
     </row>
     <row r="54">
@@ -4911,7 +4911,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.08228110940569455</v>
+        <v>0.08228109891116242</v>
       </c>
     </row>
     <row r="55">
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.2313404772121077</v>
+        <v>0.2313398607081685</v>
       </c>
     </row>
     <row r="56">
@@ -4941,7 +4941,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-0.02494867460315708</v>
+        <v>-0.02494830132515324</v>
       </c>
     </row>
     <row r="57">
@@ -4956,7 +4956,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.1480073232301915</v>
+        <v>0.1480076176984868</v>
       </c>
     </row>
     <row r="58">
@@ -4971,7 +4971,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-0.07439560639689813</v>
+        <v>-0.07439584381792541</v>
       </c>
     </row>
     <row r="59">
@@ -5001,7 +5001,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.278053372066061</v>
+        <v>0.2780536714533202</v>
       </c>
     </row>
     <row r="61">
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-0.0999201901568485</v>
+        <v>-0.09992034243966474</v>
       </c>
     </row>
     <row r="62">
@@ -5031,7 +5031,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-0.1673522934414061</v>
+        <v>-0.167352477745868</v>
       </c>
     </row>
     <row r="63">
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-0.004125014290136009</v>
+        <v>-0.00412485865168144</v>
       </c>
     </row>
     <row r="64">
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.1189666130487661</v>
+        <v>0.1189666915139864</v>
       </c>
     </row>
     <row r="65">
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-0.3201583796553739</v>
+        <v>-0.3201582870820033</v>
       </c>
     </row>
     <row r="66">
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.006739971141816792</v>
+        <v>0.006739557167566579</v>
       </c>
     </row>
     <row r="67">
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-0.1881427605859263</v>
+        <v>-0.1881426966829738</v>
       </c>
     </row>
     <row r="68">
@@ -5121,7 +5121,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.1984193343680376</v>
+        <v>0.198419485607179</v>
       </c>
     </row>
     <row r="69">
@@ -5136,7 +5136,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-0.1689698670395005</v>
+        <v>-0.1689700249961064</v>
       </c>
     </row>
     <row r="70">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-0.1957731128449735</v>
+        <v>-0.1957731500562142</v>
       </c>
     </row>
     <row r="71">
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0.1122011592615861</v>
+        <v>0.1122012645604944</v>
       </c>
     </row>
     <row r="72">
@@ -5181,7 +5181,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.2538341742905792</v>
+        <v>0.253834351917176</v>
       </c>
     </row>
     <row r="73">
@@ -5211,7 +5211,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.3368688659330197</v>
+        <v>0.3368689967381773</v>
       </c>
     </row>
     <row r="75">
@@ -5226,7 +5226,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.1883092161517261</v>
+        <v>0.1883090020379035</v>
       </c>
     </row>
     <row r="76">
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.1964591677895673</v>
+        <v>0.1964593486442521</v>
       </c>
     </row>
     <row r="77">
@@ -5256,7 +5256,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-0.0008381472836533899</v>
+        <v>-0.0008383536831267913</v>
       </c>
     </row>
     <row r="78">
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.3634366209600322</v>
+        <v>0.3634365332711422</v>
       </c>
     </row>
     <row r="79">
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.1180945982127071</v>
+        <v>0.1180947231099752</v>
       </c>
     </row>
     <row r="80">
@@ -5301,7 +5301,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.10476655284878</v>
+        <v>0.1047667430412556</v>
       </c>
     </row>
     <row r="81">
@@ -5316,7 +5316,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0.05619647586122234</v>
+        <v>0.05619638947121319</v>
       </c>
     </row>
     <row r="82">
@@ -5346,7 +5346,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-0.0624299809416361</v>
+        <v>-0.06242989307458247</v>
       </c>
     </row>
     <row r="84">
@@ -5361,7 +5361,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>0.1468857790179774</v>
+        <v>0.1468858589700071</v>
       </c>
     </row>
     <row r="85">
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>0.05884106450555349</v>
+        <v>0.0588409731740891</v>
       </c>
     </row>
     <row r="86">
@@ -5391,7 +5391,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>0.2425270032073543</v>
+        <v>0.2425269073164948</v>
       </c>
     </row>
     <row r="87">
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>0.2858092172967774</v>
+        <v>0.2858094657390908</v>
       </c>
     </row>
     <row r="88">
@@ -5421,7 +5421,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>0.1421278666884103</v>
+        <v>0.1421275493987519</v>
       </c>
     </row>
     <row r="89">
@@ -5436,7 +5436,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-0.04371539170313565</v>
+        <v>-0.04371531081375535</v>
       </c>
     </row>
     <row r="90">
@@ -5481,7 +5481,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-0.05269871694819739</v>
+        <v>-0.05269877881153473</v>
       </c>
     </row>
     <row r="93">
@@ -5496,7 +5496,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>0.02008208031891745</v>
+        <v>0.02008221224001749</v>
       </c>
     </row>
     <row r="94">
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>0.01734106710624794</v>
+        <v>0.01734100197691202</v>
       </c>
     </row>
     <row r="95">
@@ -5526,7 +5526,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>0.09330816719098234</v>
+        <v>0.09330841890274821</v>
       </c>
     </row>
     <row r="96">
@@ -5541,7 +5541,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>0.04135312769620292</v>
+        <v>0.04135265771665142</v>
       </c>
     </row>
     <row r="97">
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-0.02864401138199291</v>
+        <v>-0.02864379662791638</v>
       </c>
     </row>
     <row r="98">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-0.1058285561594333</v>
+        <v>-0.1058286130610341</v>
       </c>
     </row>
     <row r="99">
@@ -5586,7 +5586,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>0.04039296321972285</v>
+        <v>0.04039309306242167</v>
       </c>
     </row>
     <row r="100">
@@ -5601,7 +5601,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-0.1324046988533616</v>
+        <v>-0.1324047519202285</v>
       </c>
     </row>
     <row r="101">
@@ -5631,7 +5631,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>0.2406355273027898</v>
+        <v>0.240635387014742</v>
       </c>
     </row>
     <row r="103">
@@ -5646,7 +5646,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>0.1691704867095978</v>
+        <v>0.169170505838987</v>
       </c>
     </row>
     <row r="104">
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>0.1259087441380393</v>
+        <v>0.1259088530315122</v>
       </c>
     </row>
     <row r="105">
@@ -5691,7 +5691,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>0.07119068039067433</v>
+        <v>0.07119076811091918</v>
       </c>
     </row>
     <row r="107">
@@ -5706,7 +5706,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>0.08533300162257662</v>
+        <v>0.08533291274421861</v>
       </c>
     </row>
     <row r="108">
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>0.05367240806636397</v>
+        <v>0.05367232174856373</v>
       </c>
     </row>
     <row r="110">
@@ -5751,7 +5751,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>0.02488273841277922</v>
+        <v>0.02488282237211026</v>
       </c>
     </row>
     <row r="111">
@@ -5781,7 +5781,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>-0.0157459214714587</v>
+        <v>-0.01574583525101958</v>
       </c>
     </row>
     <row r="113">
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>0.1443854586470354</v>
+        <v>0.1443853583991317</v>
       </c>
     </row>
     <row r="114">
@@ -6237,7 +6237,7 @@
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -6273,7 +6273,7 @@
         <v>3.495221238938055</v>
       </c>
       <c r="C2" t="n">
-        <v>4.847037080431163</v>
+        <v>4.847037055005384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>3.422856966733567</v>
       </c>
       <c r="C3" t="n">
-        <v>3.957808721770739</v>
+        <v>3.957808554685438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>3.697222222222224</v>
       </c>
       <c r="C6" t="n">
-        <v>12.37256016259983</v>
+        <v>12.37256092324548</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>-0.8680000000000002</v>
       </c>
       <c r="C7" t="n">
-        <v>-8.887042544526659</v>
+        <v>-8.887044004532793</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>21.97</v>
       </c>
       <c r="C8" t="n">
-        <v>38.39885382872792</v>
+        <v>38.39881172764594</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>-2.2</v>
       </c>
       <c r="C9" t="n">
-        <v>-32.01583796553739</v>
+        <v>-32.01582870820033</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>3.495221238938055</v>
       </c>
       <c r="C10" t="n">
-        <v>4.847037080431163</v>
+        <v>4.847037055005384</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>3.992318974200495</v>
       </c>
       <c r="C11" t="n">
-        <v>13.47440142378295</v>
+        <v>13.47440253106332</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>2.614250975720806</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.0482374382237372</v>
+        <v>-0.04823758942923902</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>8.093367320642244</v>
       </c>
       <c r="C13" t="n">
-        <v>0.06682952564226774</v>
+        <v>0.06682689875137893</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>0.8754864682719924</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3597218850757939</v>
+        <v>0.3597218536281092</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>14.35776078315886</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6802039139380652</v>
+        <v>0.680203885160091</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>92.0046082949309</v>
       </c>
       <c r="C16" t="n">
-        <v>2.540769011019441</v>
+        <v>2.540768749812224</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/Project_1_May2026_Update.xlsx
+++ b/Project_1_May2026_Update.xlsx
@@ -485,7 +485,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-12T16:45:01</t>
+          <t>2026-06-12T16:57:48</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4131,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.02285929269854603</v>
+        <v>0.02285920188941115</v>
       </c>
     </row>
     <row r="3">
@@ -4146,7 +4146,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.07052605608550622</v>
+        <v>-0.07052579600768338</v>
       </c>
     </row>
     <row r="4">
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.07476825653475538</v>
+        <v>0.07476824225161893</v>
       </c>
     </row>
     <row r="5">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.0425039492189323</v>
+        <v>-0.04250429714935544</v>
       </c>
     </row>
     <row r="6">
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.3839881172764594</v>
+        <v>0.3839885598228099</v>
       </c>
     </row>
     <row r="7">
@@ -4206,7 +4206,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.00250948391640704</v>
+        <v>0.002509416515391605</v>
       </c>
     </row>
     <row r="8">
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.1241698388455315</v>
+        <v>0.1241698974355474</v>
       </c>
     </row>
     <row r="9">
@@ -4236,7 +4236,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0426437999119289</v>
+        <v>0.04264331877660665</v>
       </c>
     </row>
     <row r="10">
@@ -4251,7 +4251,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.05599178869589605</v>
+        <v>0.05599283519639009</v>
       </c>
     </row>
     <row r="11">
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.1568504943397173</v>
+        <v>0.1568495278524773</v>
       </c>
     </row>
     <row r="12">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.02949606864849486</v>
+        <v>-0.02949542008770178</v>
       </c>
     </row>
     <row r="13">
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.03525249121455731</v>
+        <v>-0.03525295563810926</v>
       </c>
     </row>
     <row r="14">
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.01545979379661466</v>
+        <v>-0.0154597152339655</v>
       </c>
     </row>
     <row r="16">
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.04242161930278476</v>
+        <v>-0.04242177551025128</v>
       </c>
     </row>
     <row r="17">
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.0288874733673059</v>
+        <v>-0.02888739244319738</v>
       </c>
     </row>
     <row r="18">
@@ -4371,7 +4371,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.1213428777127814</v>
+        <v>0.1213427060924364</v>
       </c>
     </row>
     <row r="19">
@@ -4386,7 +4386,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.06004798849684123</v>
+        <v>-0.06004792116263957</v>
       </c>
     </row>
     <row r="20">
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.03360084344043912</v>
+        <v>0.03360076476281404</v>
       </c>
     </row>
     <row r="21">
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.1462875160142236</v>
+        <v>0.1462878541255916</v>
       </c>
     </row>
     <row r="22">
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.001759021901640123</v>
+        <v>0.001758746802028588</v>
       </c>
     </row>
     <row r="23">
@@ -4446,7 +4446,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.2497688216809697</v>
+        <v>-0.2497686501646835</v>
       </c>
     </row>
     <row r="24">
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.2248255968109131</v>
+        <v>-0.2248257591155258</v>
       </c>
     </row>
     <row r="25">
@@ -4476,7 +4476,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.1823190103222162</v>
+        <v>-0.1823190318263749</v>
       </c>
     </row>
     <row r="26">
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.07677874123501627</v>
+        <v>0.07677889655705639</v>
       </c>
     </row>
     <row r="27">
@@ -4521,7 +4521,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.1652084542407335</v>
+        <v>0.1652082045717633</v>
       </c>
     </row>
     <row r="29">
@@ -4536,7 +4536,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.008019689679491959</v>
+        <v>0.008019798532787226</v>
       </c>
     </row>
     <row r="30">
@@ -4551,7 +4551,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.2516023421696284</v>
+        <v>-0.2516022094867382</v>
       </c>
     </row>
     <row r="31">
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.2137714429675359</v>
+        <v>0.213770930741247</v>
       </c>
     </row>
     <row r="32">
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.02733981398583518</v>
+        <v>0.02733994058411771</v>
       </c>
     </row>
     <row r="33">
@@ -4596,7 +4596,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-0.007172105242657989</v>
+        <v>-0.007171537435493702</v>
       </c>
     </row>
     <row r="34">
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.04019066779037428</v>
+        <v>0.04019042453783594</v>
       </c>
     </row>
     <row r="35">
@@ -4626,7 +4626,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.1548229938985013</v>
+        <v>0.1548230871034944</v>
       </c>
     </row>
     <row r="36">
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.07820119079120702</v>
+        <v>0.07820108036172746</v>
       </c>
     </row>
     <row r="37">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.08643349751164076</v>
+        <v>0.08643340128852106</v>
       </c>
     </row>
     <row r="38">
@@ -4671,7 +4671,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.004802361259457877</v>
+        <v>0.00480227973776759</v>
       </c>
     </row>
     <row r="39">
@@ -4686,7 +4686,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.1422830871367302</v>
+        <v>0.1422834232087378</v>
       </c>
     </row>
     <row r="40">
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-0.02337281563258986</v>
+        <v>-0.02337330783586811</v>
       </c>
     </row>
     <row r="41">
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.1088010733200719</v>
+        <v>0.1088014686011025</v>
       </c>
     </row>
     <row r="42">
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.2146569338393018</v>
+        <v>0.2146568541701963</v>
       </c>
     </row>
     <row r="43">
@@ -4746,7 +4746,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.07010911502193151</v>
+        <v>0.07010889902743078</v>
       </c>
     </row>
     <row r="44">
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.1181166594507639</v>
+        <v>0.1181168851353178</v>
       </c>
     </row>
     <row r="45">
@@ -4776,7 +4776,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.2599920805477076</v>
+        <v>0.2599923513290716</v>
       </c>
     </row>
     <row r="46">
@@ -4791,7 +4791,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.01166394474764676</v>
+        <v>0.01166365569811623</v>
       </c>
     </row>
     <row r="47">
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-0.07337135489685598</v>
+        <v>-0.07337093523337779</v>
       </c>
     </row>
     <row r="48">
@@ -4821,7 +4821,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.06921196604474256</v>
+        <v>0.0692114046840453</v>
       </c>
     </row>
     <row r="49">
@@ -4836,7 +4836,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-0.02585542286987719</v>
+        <v>-0.02585521215556541</v>
       </c>
     </row>
     <row r="50">
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-0.004703922160598006</v>
+        <v>-0.004703995182432807</v>
       </c>
     </row>
     <row r="51">
@@ -4866,7 +4866,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.05579367536488289</v>
+        <v>0.0557937490785787</v>
       </c>
     </row>
     <row r="52">
@@ -4881,7 +4881,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-0.02670528175968867</v>
+        <v>-0.02670500062208081</v>
       </c>
     </row>
     <row r="53">
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.1248427591747725</v>
+        <v>0.1248422839939012</v>
       </c>
     </row>
     <row r="54">
@@ -4911,7 +4911,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.08228109891116242</v>
+        <v>0.08228129547572216</v>
       </c>
     </row>
     <row r="55">
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.2313398607081685</v>
+        <v>0.2313400691415173</v>
       </c>
     </row>
     <row r="56">
@@ -4941,7 +4941,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-0.02494830132515324</v>
+        <v>-0.02494867699092596</v>
       </c>
     </row>
     <row r="57">
@@ -4956,7 +4956,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.1480076176984868</v>
+        <v>0.1480075340702305</v>
       </c>
     </row>
     <row r="58">
@@ -4971,7 +4971,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-0.07439584381792541</v>
+        <v>-0.07439577103852923</v>
       </c>
     </row>
     <row r="59">
@@ -4986,7 +4986,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.2341669114563416</v>
+        <v>0.234167210207564</v>
       </c>
     </row>
     <row r="60">
@@ -5001,7 +5001,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.2780536714533202</v>
+        <v>0.278053629830463</v>
       </c>
     </row>
     <row r="61">
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-0.09992034243966474</v>
+        <v>-0.09992050642572081</v>
       </c>
     </row>
     <row r="62">
@@ -5031,7 +5031,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-0.167352477745868</v>
+        <v>-0.1673523585057887</v>
       </c>
     </row>
     <row r="63">
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-0.00412485865168144</v>
+        <v>-0.00412493647091472</v>
       </c>
     </row>
     <row r="64">
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-0.3201582870820033</v>
+        <v>-0.3201582169590758</v>
       </c>
     </row>
     <row r="66">
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.006739557167566579</v>
+        <v>0.006739556472408426</v>
       </c>
     </row>
     <row r="67">
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-0.1881426966829738</v>
+        <v>-0.1881427286344534</v>
       </c>
     </row>
     <row r="68">
@@ -5121,7 +5121,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.198419485607179</v>
+        <v>0.1984195361864451</v>
       </c>
     </row>
     <row r="69">
@@ -5136,7 +5136,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-0.1689700249961064</v>
+        <v>-0.1689700072028205</v>
       </c>
     </row>
     <row r="70">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-0.1957731500562142</v>
+        <v>-0.1957731886064759</v>
       </c>
     </row>
     <row r="71">
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0.1122012645604944</v>
+        <v>0.1122012557211716</v>
       </c>
     </row>
     <row r="72">
@@ -5181,7 +5181,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.253834351917176</v>
+        <v>0.2538341214371438</v>
       </c>
     </row>
     <row r="73">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-0.1362205642538448</v>
+        <v>-0.136220466658155</v>
       </c>
     </row>
     <row r="74">
@@ -5211,7 +5211,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.3368689967381773</v>
+        <v>0.3368688659330197</v>
       </c>
     </row>
     <row r="75">
@@ -5226,7 +5226,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.1883090020379035</v>
+        <v>0.1883090204628883</v>
       </c>
     </row>
     <row r="76">
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.1964593486442521</v>
+        <v>0.196459611838171</v>
       </c>
     </row>
     <row r="77">
@@ -5256,7 +5256,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-0.0008383536831267913</v>
+        <v>-0.0008383535677374265</v>
       </c>
     </row>
     <row r="78">
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.3634365332711422</v>
+        <v>0.3634363454528924</v>
       </c>
     </row>
     <row r="79">
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.1180947231099752</v>
+        <v>0.1180948241440796</v>
       </c>
     </row>
     <row r="80">
@@ -5301,7 +5301,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.1047667430412556</v>
+        <v>0.10476655284878</v>
       </c>
     </row>
     <row r="81">
@@ -5316,7 +5316,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0.05619638947121319</v>
+        <v>0.05619647586122234</v>
       </c>
     </row>
     <row r="82">
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-0.1186507015199146</v>
+        <v>-0.1186506240783486</v>
       </c>
     </row>
     <row r="83">
@@ -5346,7 +5346,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-0.06242989307458247</v>
+        <v>-0.06243006332314394</v>
       </c>
     </row>
     <row r="84">
@@ -5361,7 +5361,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>0.1468858589700071</v>
+        <v>0.1468858727358351</v>
       </c>
     </row>
     <row r="85">
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>0.0588409731740891</v>
+        <v>0.05884122312748907</v>
       </c>
     </row>
     <row r="86">
@@ -5391,7 +5391,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>0.2425269073164948</v>
+        <v>0.2425267155348205</v>
       </c>
     </row>
     <row r="87">
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>0.2858094657390908</v>
+        <v>0.2858095899602473</v>
       </c>
     </row>
     <row r="88">
@@ -5421,7 +5421,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>0.1421275493987519</v>
+        <v>0.1421275356679097</v>
       </c>
     </row>
     <row r="89">
@@ -5436,7 +5436,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-0.04371531081375535</v>
+        <v>-0.04371530711600258</v>
       </c>
     </row>
     <row r="90">
@@ -5451,7 +5451,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>0.2688710270916701</v>
+        <v>0.2688709148550492</v>
       </c>
     </row>
     <row r="91">
@@ -5466,7 +5466,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>0.1268505324471054</v>
+        <v>0.1268504627363709</v>
       </c>
     </row>
     <row r="92">
@@ -5481,7 +5481,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-0.05269877881153473</v>
+        <v>-0.05269872020831612</v>
       </c>
     </row>
     <row r="93">
@@ -5496,7 +5496,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>0.02008221224001749</v>
+        <v>0.02008214693519572</v>
       </c>
     </row>
     <row r="94">
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>0.01734100197691202</v>
+        <v>0.01734106710624794</v>
       </c>
     </row>
     <row r="95">
@@ -5526,7 +5526,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>0.09330841890274821</v>
+        <v>0.09330829304686517</v>
       </c>
     </row>
     <row r="96">
@@ -5541,7 +5541,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>0.04135265771665142</v>
+        <v>0.04135289270640019</v>
       </c>
     </row>
     <row r="97">
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-0.02864379662791638</v>
+        <v>-0.02864379346153278</v>
       </c>
     </row>
     <row r="98">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-0.1058286130610341</v>
+        <v>-0.1058287148205893</v>
       </c>
     </row>
     <row r="99">
@@ -5631,7 +5631,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>0.240635387014742</v>
+        <v>0.2406355273027898</v>
       </c>
     </row>
     <row r="103">
@@ -5646,7 +5646,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>0.169170505838987</v>
+        <v>0.16917037363203</v>
       </c>
     </row>
     <row r="104">
@@ -5676,7 +5676,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>-0.02074547328268472</v>
+        <v>-0.02074555918313137</v>
       </c>
     </row>
     <row r="106">
@@ -5691,7 +5691,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>0.07119076811091918</v>
+        <v>0.07119086207604353</v>
       </c>
     </row>
     <row r="107">
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>0.05367232174856373</v>
+        <v>0.05367240806636397</v>
       </c>
     </row>
     <row r="110">
@@ -5751,7 +5751,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>0.02488282237211026</v>
+        <v>0.02488273841277922</v>
       </c>
     </row>
     <row r="111">
@@ -5781,7 +5781,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>-0.01574583525101958</v>
+        <v>-0.0157459214714587</v>
       </c>
     </row>
     <row r="113">
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>0.1443853583991317</v>
+        <v>0.1443854586470354</v>
       </c>
     </row>
     <row r="114">
@@ -6273,7 +6273,7 @@
         <v>3.495221238938055</v>
       </c>
       <c r="C2" t="n">
-        <v>4.847037055005384</v>
+        <v>4.847036934996997</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>3.697222222222224</v>
       </c>
       <c r="C6" t="n">
-        <v>12.37256092324548</v>
+        <v>12.37255992947925</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>-0.8680000000000002</v>
       </c>
       <c r="C7" t="n">
-        <v>-8.887044004532793</v>
+        <v>-8.887042529933115</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>21.97</v>
       </c>
       <c r="C8" t="n">
-        <v>38.39881172764594</v>
+        <v>38.39885598228099</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>-2.2</v>
       </c>
       <c r="C9" t="n">
-        <v>-32.01582870820033</v>
+        <v>-32.01582169590758</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>3.495221238938055</v>
       </c>
       <c r="C10" t="n">
-        <v>4.847037055005384</v>
+        <v>4.847036934996997</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>3.992318974200495</v>
       </c>
       <c r="C11" t="n">
-        <v>13.47440253106332</v>
+        <v>13.47440194154188</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>2.614250975720806</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.04823758942923902</v>
+        <v>-0.04823705072344576</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>8.093367320642244</v>
       </c>
       <c r="C13" t="n">
-        <v>0.06682689875137893</v>
+        <v>0.06682730214109478</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>0.8754864682719924</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3597218536281092</v>
+        <v>0.359721860459979</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>14.35776078315886</v>
       </c>
       <c r="C15" t="n">
-        <v>0.680203885160091</v>
+        <v>0.6802039768348236</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>92.0046082949309</v>
       </c>
       <c r="C16" t="n">
-        <v>2.540768749812224</v>
+        <v>2.540768967319162</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/Project_1_May2026_Update.xlsx
+++ b/Project_1_May2026_Update.xlsx
@@ -485,7 +485,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-12T16:57:48</t>
+          <t>2026-06-12T18:59:10</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4131,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.02285920188941115</v>
+        <v>0.02285938558352174</v>
       </c>
     </row>
     <row r="3">
@@ -4146,7 +4146,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.07052579600768338</v>
+        <v>-0.07052570096673094</v>
       </c>
     </row>
     <row r="4">
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.07476824225161893</v>
+        <v>0.0747680369364303</v>
       </c>
     </row>
     <row r="5">
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.3839885598228099</v>
+        <v>0.3839881885572425</v>
       </c>
     </row>
     <row r="7">
@@ -4206,7 +4206,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.002509416515391605</v>
+        <v>0.002509752510758467</v>
       </c>
     </row>
     <row r="8">
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.1241698974355474</v>
+        <v>0.1241698222324648</v>
       </c>
     </row>
     <row r="9">
@@ -4236,7 +4236,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.04264331877660665</v>
+        <v>0.04264367582165884</v>
       </c>
     </row>
     <row r="10">
@@ -4251,7 +4251,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.05599283519639009</v>
+        <v>0.05599270187473326</v>
       </c>
     </row>
     <row r="11">
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.1568495278524773</v>
+        <v>0.1568496020380632</v>
       </c>
     </row>
     <row r="12">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.02949542008770178</v>
+        <v>-0.02949587901447681</v>
       </c>
     </row>
     <row r="13">
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.03525295563810926</v>
+        <v>-0.03525286614753786</v>
       </c>
     </row>
     <row r="14">
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.2702844711013088</v>
+        <v>0.2702840988871744</v>
       </c>
     </row>
     <row r="15">
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.0154597152339655</v>
+        <v>-0.01545940705602855</v>
       </c>
     </row>
     <row r="16">
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.04242177551025128</v>
+        <v>-0.04242185869163462</v>
       </c>
     </row>
     <row r="17">
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.02888739244319738</v>
+        <v>-0.0288868972695232</v>
       </c>
     </row>
     <row r="18">
@@ -4371,7 +4371,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.1213427060924364</v>
+        <v>0.1213424070122675</v>
       </c>
     </row>
     <row r="19">
@@ -4386,7 +4386,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.06004792116263957</v>
+        <v>-0.0600478400430251</v>
       </c>
     </row>
     <row r="20">
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.03360076476281404</v>
+        <v>0.03360084070488822</v>
       </c>
     </row>
     <row r="21">
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.1462878541255916</v>
+        <v>0.1462875832582031</v>
       </c>
     </row>
     <row r="22">
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.2248257591155258</v>
+        <v>-0.2248253933945861</v>
       </c>
     </row>
     <row r="25">
@@ -4476,7 +4476,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.1823190318263749</v>
+        <v>-0.182319417601463</v>
       </c>
     </row>
     <row r="26">
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.07677889655705639</v>
+        <v>0.07677882443358564</v>
       </c>
     </row>
     <row r="27">
@@ -4506,7 +4506,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.07311311845011881</v>
+        <v>0.07311332428959028</v>
       </c>
     </row>
     <row r="28">
@@ -4521,7 +4521,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.1652082045717633</v>
+        <v>0.1652084336170239</v>
       </c>
     </row>
     <row r="29">
@@ -4536,7 +4536,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.008019798532787226</v>
+        <v>0.008019367415653678</v>
       </c>
     </row>
     <row r="30">
@@ -4551,7 +4551,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.2516022094867382</v>
+        <v>-0.2516020768038197</v>
       </c>
     </row>
     <row r="31">
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.213770930741247</v>
+        <v>0.2137708445553539</v>
       </c>
     </row>
     <row r="32">
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.02733994058411771</v>
+        <v>0.02733970658040663</v>
       </c>
     </row>
     <row r="33">
@@ -4596,7 +4596,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-0.007171537435493702</v>
+        <v>-0.007171425180814595</v>
       </c>
     </row>
     <row r="34">
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.04019042453783594</v>
+        <v>0.04019019972646065</v>
       </c>
     </row>
     <row r="35">
@@ -4626,7 +4626,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.1548230871034944</v>
+        <v>0.1548229177671563</v>
       </c>
     </row>
     <row r="36">
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.07820108036172746</v>
+        <v>0.0782014041825243</v>
       </c>
     </row>
     <row r="37">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.08643340128852106</v>
+        <v>0.08643368230268056</v>
       </c>
     </row>
     <row r="38">
@@ -4671,7 +4671,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.00480227973776759</v>
+        <v>0.004802279346277638</v>
       </c>
     </row>
     <row r="39">
@@ -4686,7 +4686,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.1422834232087378</v>
+        <v>0.1422832494008599</v>
       </c>
     </row>
     <row r="40">
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-0.02337330783586811</v>
+        <v>-0.02337281231242416</v>
       </c>
     </row>
     <row r="41">
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.1088014686011025</v>
+        <v>0.1088009120426605</v>
       </c>
     </row>
     <row r="42">
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.2146568541701963</v>
+        <v>0.2146573273781289</v>
       </c>
     </row>
     <row r="43">
@@ -4746,7 +4746,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.07010889902743078</v>
+        <v>0.07010844432387153</v>
       </c>
     </row>
     <row r="44">
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.1181168851353178</v>
+        <v>0.1181168970558806</v>
       </c>
     </row>
     <row r="45">
@@ -4776,7 +4776,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.2599923513290716</v>
+        <v>0.2599919234937875</v>
       </c>
     </row>
     <row r="46">
@@ -4791,7 +4791,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.01166365569811623</v>
+        <v>0.01166387561856563</v>
       </c>
     </row>
     <row r="47">
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-0.07337093523337779</v>
+        <v>-0.07337102162935827</v>
       </c>
     </row>
     <row r="48">
@@ -4821,7 +4821,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.0692114046840453</v>
+        <v>0.06921165508942528</v>
       </c>
     </row>
     <row r="49">
@@ -4836,7 +4836,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-0.02585521215556541</v>
+        <v>-0.02585528547347249</v>
       </c>
     </row>
     <row r="50">
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-0.004703995182432807</v>
+        <v>-0.004703995872668454</v>
       </c>
     </row>
     <row r="51">
@@ -4866,7 +4866,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.0557937490785787</v>
+        <v>0.05579397844522749</v>
       </c>
     </row>
     <row r="52">
@@ -4881,7 +4881,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-0.02670500062208081</v>
+        <v>-0.02670499875758392</v>
       </c>
     </row>
     <row r="53">
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.1248422839939012</v>
+        <v>0.1248422750384746</v>
       </c>
     </row>
     <row r="54">
@@ -4911,7 +4911,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.08228129547572216</v>
+        <v>0.08228109891116242</v>
       </c>
     </row>
     <row r="55">
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.2313400691415173</v>
+        <v>0.2313400964045229</v>
       </c>
     </row>
     <row r="56">
@@ -4941,7 +4941,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-0.02494867699092596</v>
+        <v>-0.02494858367144315</v>
       </c>
     </row>
     <row r="57">
@@ -4956,7 +4956,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.1480075340702305</v>
+        <v>0.1480077303824465</v>
       </c>
     </row>
     <row r="58">
@@ -4971,7 +4971,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-0.07439577103852923</v>
+        <v>-0.07439592931918593</v>
       </c>
     </row>
     <row r="59">
@@ -4986,7 +4986,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.234167210207564</v>
+        <v>0.2341670254606225</v>
       </c>
     </row>
     <row r="60">
@@ -5001,7 +5001,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.278053629830463</v>
+        <v>0.2780539708405791</v>
       </c>
     </row>
     <row r="61">
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-0.09992050642572081</v>
+        <v>-0.09992049472240971</v>
       </c>
     </row>
     <row r="62">
@@ -5031,7 +5031,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-0.1673523585057887</v>
+        <v>-0.1673524668571839</v>
       </c>
     </row>
     <row r="63">
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-0.00412493647091472</v>
+        <v>-0.004124858329358494</v>
       </c>
     </row>
     <row r="64">
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.1189666915139864</v>
+        <v>0.1189666037140253</v>
       </c>
     </row>
     <row r="65">
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-0.3201582169590758</v>
+        <v>-0.3201583572049309</v>
       </c>
     </row>
     <row r="66">
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.006739556472408426</v>
+        <v>0.006739557862724732</v>
       </c>
     </row>
     <row r="67">
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-0.1881427286344534</v>
+        <v>-0.1881425622760196</v>
       </c>
     </row>
     <row r="68">
@@ -5121,7 +5121,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.1984195361864451</v>
+        <v>0.1984196623852867</v>
       </c>
     </row>
     <row r="69">
@@ -5136,7 +5136,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-0.1689700072028205</v>
+        <v>-0.1689700420617292</v>
       </c>
     </row>
     <row r="70">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-0.1957731886064759</v>
+        <v>-0.1957731762027266</v>
       </c>
     </row>
     <row r="71">
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0.1122012557211716</v>
+        <v>0.1122011681009001</v>
       </c>
     </row>
     <row r="72">
@@ -5211,7 +5211,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.3368688659330197</v>
+        <v>0.3368687351278623</v>
       </c>
     </row>
     <row r="75">
@@ -5226,7 +5226,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.1883090204628883</v>
+        <v>0.1883091367323053</v>
       </c>
     </row>
     <row r="76">
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.196459611838171</v>
+        <v>0.1964594471597627</v>
       </c>
     </row>
     <row r="77">
@@ -5256,7 +5256,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-0.0008383535677374265</v>
+        <v>-0.0008382848640754448</v>
       </c>
     </row>
     <row r="78">
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.3634363454528924</v>
+        <v>0.3634364393620109</v>
       </c>
     </row>
     <row r="79">
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.1180948241440796</v>
+        <v>0.1180947231099752</v>
       </c>
     </row>
     <row r="80">
@@ -5301,7 +5301,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.10476655284878</v>
+        <v>0.1047669237667384</v>
       </c>
     </row>
     <row r="81">
@@ -5316,7 +5316,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0.05619647586122234</v>
+        <v>0.05619621669123753</v>
       </c>
     </row>
     <row r="82">
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-0.1186506240783486</v>
+        <v>-0.1186505466367824</v>
       </c>
     </row>
     <row r="83">
@@ -5346,7 +5346,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-0.06243006332314394</v>
+        <v>-0.06243014570463745</v>
       </c>
     </row>
     <row r="84">
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>0.05884122312748907</v>
+        <v>0.05884105969735187</v>
       </c>
     </row>
     <row r="86">
@@ -5391,7 +5391,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>0.2425267155348205</v>
+        <v>0.2425269073164948</v>
       </c>
     </row>
     <row r="87">
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>0.2858095899602473</v>
+        <v>0.2858093415179341</v>
       </c>
     </row>
     <row r="88">
@@ -5421,7 +5421,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>0.1421275356679097</v>
+        <v>0.1421276597389094</v>
       </c>
     </row>
     <row r="89">
@@ -5436,7 +5436,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-0.04371530711600258</v>
+        <v>-0.04371531081375535</v>
       </c>
     </row>
     <row r="90">
@@ -5451,7 +5451,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>0.2688709148550492</v>
+        <v>0.2688709386377386</v>
       </c>
     </row>
     <row r="91">
@@ -5466,7 +5466,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>0.1268504627363709</v>
+        <v>0.1268506110006893</v>
       </c>
     </row>
     <row r="92">
@@ -5481,7 +5481,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-0.05269872020831612</v>
+        <v>-0.05269871694819739</v>
       </c>
     </row>
     <row r="93">
@@ -5496,7 +5496,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>0.02008214693519572</v>
+        <v>0.02008208031891745</v>
       </c>
     </row>
     <row r="94">
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>0.01734106710624794</v>
+        <v>0.01734113112542701</v>
       </c>
     </row>
     <row r="95">
@@ -5526,7 +5526,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>0.09330829304686517</v>
+        <v>0.09330809839135434</v>
       </c>
     </row>
     <row r="96">
@@ -5541,7 +5541,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>0.04135289270640019</v>
+        <v>0.04135301258146518</v>
       </c>
     </row>
     <row r="97">
@@ -6237,7 +6237,7 @@
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -6273,7 +6273,7 @@
         <v>3.495221238938055</v>
       </c>
       <c r="C2" t="n">
-        <v>4.847036934996997</v>
+        <v>4.847036772240028</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>3.422856966733567</v>
       </c>
       <c r="C3" t="n">
-        <v>3.957808554685438</v>
+        <v>3.957808638228077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>3.697222222222224</v>
       </c>
       <c r="C6" t="n">
-        <v>12.37255992947925</v>
+        <v>12.37255820866685</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>-0.8680000000000002</v>
       </c>
       <c r="C7" t="n">
-        <v>-8.887042529933115</v>
+        <v>-8.887039849238926</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>21.97</v>
       </c>
       <c r="C8" t="n">
-        <v>38.39885598228099</v>
+        <v>38.39881885572425</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>-2.2</v>
       </c>
       <c r="C9" t="n">
-        <v>-32.01582169590758</v>
+        <v>-32.01583572049309</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>3.495221238938055</v>
       </c>
       <c r="C10" t="n">
-        <v>4.847036934996997</v>
+        <v>4.847036772240028</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>3.992318974200495</v>
       </c>
       <c r="C11" t="n">
-        <v>13.47440194154188</v>
+        <v>13.4743997567906</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>2.614250975720806</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.04823705072344576</v>
+        <v>-0.0482376446328611</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>8.093367320642244</v>
       </c>
       <c r="C13" t="n">
-        <v>0.06682730214109478</v>
+        <v>0.06682718153920009</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>0.8754864682719924</v>
       </c>
       <c r="C14" t="n">
-        <v>0.359721860459979</v>
+        <v>0.3597219067066272</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>14.35776078315886</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6802039768348236</v>
+        <v>0.6802039861971346</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>92.0046082949309</v>
       </c>
       <c r="C16" t="n">
-        <v>2.540768967319162</v>
+        <v>2.54076938034105</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/Project_1_May2026_Update.xlsx
+++ b/Project_1_May2026_Update.xlsx
@@ -485,7 +485,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-12T18:59:10</t>
+          <t>2026-06-12T19:20:04</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4131,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.02285938558352174</v>
+        <v>0.02285947846851455</v>
       </c>
     </row>
     <row r="3">
@@ -4146,7 +4146,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.07052570096673094</v>
+        <v>-0.07052561218703712</v>
       </c>
     </row>
     <row r="4">
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0747680369364303</v>
+        <v>0.07476793427886541</v>
       </c>
     </row>
     <row r="5">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.04250429714935544</v>
+        <v>-0.0425041194067628</v>
       </c>
     </row>
     <row r="6">
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.3839881885572425</v>
+        <v>0.3839884885419578</v>
       </c>
     </row>
     <row r="7">
@@ -4206,7 +4206,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.002509752510758467</v>
+        <v>0.002509416178806623</v>
       </c>
     </row>
     <row r="8">
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.1241698222324648</v>
+        <v>0.1241696132363102</v>
       </c>
     </row>
     <row r="9">
@@ -4236,7 +4236,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.04264367582165884</v>
+        <v>0.04264391892696051</v>
       </c>
     </row>
     <row r="10">
@@ -4251,7 +4251,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.05599270187473326</v>
+        <v>0.0559926954833152</v>
       </c>
     </row>
     <row r="11">
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.1568496020380632</v>
+        <v>0.15684926079897</v>
       </c>
     </row>
     <row r="12">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.02949587901447681</v>
+        <v>-0.02949588452660679</v>
       </c>
     </row>
     <row r="13">
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.03525286614753786</v>
+        <v>-0.03525219898404675</v>
       </c>
     </row>
     <row r="14">
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.2702840988871744</v>
+        <v>0.2702839640196344</v>
       </c>
     </row>
     <row r="15">
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.01545940705602855</v>
+        <v>-0.01545955810866706</v>
       </c>
     </row>
     <row r="16">
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.04242185869163462</v>
+        <v>-0.04242192833258129</v>
       </c>
     </row>
     <row r="17">
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.0288868972695232</v>
+        <v>-0.02888722578051672</v>
       </c>
     </row>
     <row r="18">
@@ -4371,7 +4371,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.1213424070122675</v>
+        <v>0.1213427710777206</v>
       </c>
     </row>
     <row r="19">
@@ -4386,7 +4386,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.0600478400430251</v>
+        <v>-0.06004806042616784</v>
       </c>
     </row>
     <row r="20">
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.03360084070488822</v>
+        <v>0.03360059920092984</v>
       </c>
     </row>
     <row r="21">
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.1462875832582031</v>
+        <v>0.1462877868816175</v>
       </c>
     </row>
     <row r="22">
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.001758746802028588</v>
+        <v>0.001759021901640123</v>
       </c>
     </row>
     <row r="23">
@@ -4446,7 +4446,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.2497686501646835</v>
+        <v>-0.2497688216809697</v>
       </c>
     </row>
     <row r="24">
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.2248253933945861</v>
+        <v>-0.2248255968109131</v>
       </c>
     </row>
     <row r="25">
@@ -4476,7 +4476,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.182319417601463</v>
+        <v>-0.182319128270181</v>
       </c>
     </row>
     <row r="26">
@@ -4506,7 +4506,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.07311332428959028</v>
+        <v>0.07311319032805774</v>
       </c>
     </row>
     <row r="28">
@@ -4521,7 +4521,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.1652084336170239</v>
+        <v>0.1652083294062485</v>
       </c>
     </row>
     <row r="29">
@@ -4536,7 +4536,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.008019367415653678</v>
+        <v>0.008019904808493239</v>
       </c>
     </row>
     <row r="30">
@@ -4551,7 +4551,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.2516020768038197</v>
+        <v>-0.2516023685699601</v>
       </c>
     </row>
     <row r="31">
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.2137708445553539</v>
+        <v>0.2137713567816002</v>
       </c>
     </row>
     <row r="32">
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.02733970658040663</v>
+        <v>0.0273394629803918</v>
       </c>
     </row>
     <row r="33">
@@ -4596,7 +4596,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-0.007171425180814595</v>
+        <v>-0.007171538252247034</v>
       </c>
     </row>
     <row r="34">
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.04019019972646065</v>
+        <v>0.04019042914811277</v>
       </c>
     </row>
     <row r="35">
@@ -4626,7 +4626,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.1548229177671563</v>
+        <v>0.1548228836198227</v>
       </c>
     </row>
     <row r="36">
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0782014041825243</v>
+        <v>0.07820129375297236</v>
       </c>
     </row>
     <row r="37">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.08643368230268056</v>
+        <v>0.08643349751164076</v>
       </c>
     </row>
     <row r="38">
@@ -4671,7 +4671,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.004802279346277638</v>
+        <v>0.004802361259457877</v>
       </c>
     </row>
     <row r="39">
@@ -4686,7 +4686,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.1422832494008599</v>
+        <v>0.1422834116649898</v>
       </c>
     </row>
     <row r="40">
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-0.02337281231242416</v>
+        <v>-0.02337309309711155</v>
       </c>
     </row>
     <row r="41">
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.1088009120426605</v>
+        <v>0.1088012187721632</v>
       </c>
     </row>
     <row r="42">
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.2146573273781289</v>
+        <v>0.2146569056806928</v>
       </c>
     </row>
     <row r="43">
@@ -4746,7 +4746,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.07010844432387153</v>
+        <v>0.07010878345862448</v>
       </c>
     </row>
     <row r="44">
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.1181168970558806</v>
+        <v>0.1181167842135795</v>
       </c>
     </row>
     <row r="45">
@@ -4776,7 +4776,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.2599919234937875</v>
+        <v>0.2599922845356388</v>
       </c>
     </row>
     <row r="46">
@@ -4791,7 +4791,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.01166387561856563</v>
+        <v>0.01166380064063821</v>
       </c>
     </row>
     <row r="47">
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-0.07337102162935827</v>
+        <v>-0.07337114766282293</v>
       </c>
     </row>
     <row r="48">
@@ -4821,7 +4821,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.06921165508942528</v>
+        <v>0.06921134413415575</v>
       </c>
     </row>
     <row r="49">
@@ -4836,7 +4836,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-0.02585528547347249</v>
+        <v>-0.02585514807700895</v>
       </c>
     </row>
     <row r="50">
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-0.004703995872668454</v>
+        <v>-0.004703922850822995</v>
       </c>
     </row>
     <row r="51">
@@ -4866,7 +4866,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.05579397844522749</v>
+        <v>0.0557940521589344</v>
       </c>
     </row>
     <row r="52">
@@ -4881,7 +4881,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-0.02670499875758392</v>
+        <v>-0.02670520634787643</v>
       </c>
     </row>
     <row r="53">
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.1248422750384746</v>
+        <v>0.1248423646832617</v>
       </c>
     </row>
     <row r="54">
@@ -4911,7 +4911,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.08228109891116242</v>
+        <v>0.08228142302058505</v>
       </c>
     </row>
     <row r="55">
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.2313400964045229</v>
+        <v>0.2313394526377714</v>
       </c>
     </row>
     <row r="56">
@@ -4941,7 +4941,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-0.02494858367144315</v>
+        <v>-0.02494820800560771</v>
       </c>
     </row>
     <row r="57">
@@ -4956,7 +4956,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.1480077303824465</v>
+        <v>0.1480076176984868</v>
       </c>
     </row>
     <row r="58">
@@ -4971,7 +4971,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-0.07439592931918593</v>
+        <v>-0.07439584381792541</v>
       </c>
     </row>
     <row r="59">
@@ -4986,7 +4986,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.2341670254606225</v>
+        <v>0.2341670038298038</v>
       </c>
     </row>
     <row r="60">
@@ -5001,7 +5001,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.2780539708405791</v>
+        <v>0.2780534261014624</v>
       </c>
     </row>
     <row r="61">
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-0.09992049472240971</v>
+        <v>-0.09992041270609098</v>
       </c>
     </row>
     <row r="62">
@@ -5031,7 +5031,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-0.1673524668571839</v>
+        <v>-0.1673522501543653</v>
       </c>
     </row>
     <row r="63">
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.1189666037140253</v>
+        <v>0.1189665252488112</v>
       </c>
     </row>
     <row r="65">
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-0.3201583572049309</v>
+        <v>-0.3201582394095088</v>
       </c>
     </row>
     <row r="66">
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.006739557862724732</v>
+        <v>0.006739557167566579</v>
       </c>
     </row>
     <row r="67">
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-0.1881425622760196</v>
+        <v>-0.1881425429997872</v>
       </c>
     </row>
     <row r="68">
@@ -5121,7 +5121,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.1984196623852867</v>
+        <v>0.1984192587484812</v>
       </c>
     </row>
     <row r="69">
@@ -5136,7 +5136,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-0.1689700420617292</v>
+        <v>-0.1689699723439044</v>
       </c>
     </row>
     <row r="70">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-0.1957731762027266</v>
+        <v>-0.1957730742947046</v>
       </c>
     </row>
     <row r="71">
@@ -5181,7 +5181,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.2538341214371438</v>
+        <v>0.2538345464373262</v>
       </c>
     </row>
     <row r="73">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-0.136220466658155</v>
+        <v>-0.1362208159385478</v>
       </c>
     </row>
     <row r="74">
@@ -5211,7 +5211,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.3368687351278623</v>
+        <v>0.3368690841728628</v>
       </c>
     </row>
     <row r="75">
@@ -5226,7 +5226,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.1883091367323053</v>
+        <v>0.1883090998823127</v>
       </c>
     </row>
     <row r="76">
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.1964594471597627</v>
+        <v>0.1964592501287579</v>
       </c>
     </row>
     <row r="77">
@@ -5256,7 +5256,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-0.0008382848640754448</v>
+        <v>-0.0008383536831267913</v>
       </c>
     </row>
     <row r="78">
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.3634364393620109</v>
+        <v>0.3634363955175532</v>
       </c>
     </row>
     <row r="79">
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.1180947231099752</v>
+        <v>0.1180949371097999</v>
       </c>
     </row>
     <row r="80">
@@ -5301,7 +5301,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.1047669237667384</v>
+        <v>0.1047664624860469</v>
       </c>
     </row>
     <row r="81">
@@ -5316,7 +5316,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0.05619621669123753</v>
+        <v>0.05619648045772951</v>
       </c>
     </row>
     <row r="82">
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-0.1186505466367824</v>
+        <v>-0.1186505558252673</v>
       </c>
     </row>
     <row r="83">
@@ -5346,7 +5346,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-0.06243014570463745</v>
+        <v>-0.06243006332314394</v>
       </c>
     </row>
     <row r="84">
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>0.05884105969735187</v>
+        <v>0.05884114141242036</v>
       </c>
     </row>
     <row r="86">
@@ -5391,7 +5391,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>0.2425269073164948</v>
+        <v>0.2425266570775326</v>
       </c>
     </row>
     <row r="87">
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>0.2858093415179341</v>
+        <v>0.2858097496850216</v>
       </c>
     </row>
     <row r="88">
@@ -5421,7 +5421,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>0.1421276597389094</v>
+        <v>0.1421274390586158</v>
       </c>
     </row>
     <row r="89">
@@ -5451,7 +5451,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>0.2688709386377386</v>
+        <v>0.2688710270916701</v>
       </c>
     </row>
     <row r="91">
@@ -5466,7 +5466,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>0.1268506110006893</v>
+        <v>0.1268505324471054</v>
       </c>
     </row>
     <row r="92">
@@ -5526,7 +5526,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>0.09330809839135434</v>
+        <v>0.09330797253547929</v>
       </c>
     </row>
     <row r="96">
@@ -5541,7 +5541,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>0.04135301258146518</v>
+        <v>0.04135301734180707</v>
       </c>
     </row>
     <row r="97">
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-0.02864379346153278</v>
+        <v>-0.02864379662791638</v>
       </c>
     </row>
     <row r="98">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-0.1058287148205893</v>
+        <v>-0.1058286130610341</v>
       </c>
     </row>
     <row r="99">
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>0.05367240806636397</v>
+        <v>0.05367232174856373</v>
       </c>
     </row>
     <row r="110">
@@ -5751,7 +5751,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>0.02488273841277922</v>
+        <v>0.02488282237211026</v>
       </c>
     </row>
     <row r="111">
@@ -6273,7 +6273,7 @@
         <v>3.495221238938055</v>
       </c>
       <c r="C2" t="n">
-        <v>4.847036772240028</v>
+        <v>4.847036853460228</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>3.422856966733567</v>
       </c>
       <c r="C3" t="n">
-        <v>3.957808638228077</v>
+        <v>3.957808721770739</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>3.697222222222224</v>
       </c>
       <c r="C6" t="n">
-        <v>12.37255820866685</v>
+        <v>12.37255821599764</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>-0.8680000000000002</v>
       </c>
       <c r="C7" t="n">
-        <v>-8.887039849238926</v>
+        <v>-8.887039633170533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>21.97</v>
       </c>
       <c r="C8" t="n">
-        <v>38.39881885572425</v>
+        <v>38.39884885419578</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>-2.2</v>
       </c>
       <c r="C9" t="n">
-        <v>-32.01583572049309</v>
+        <v>-32.01582394095088</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>3.495221238938055</v>
       </c>
       <c r="C10" t="n">
-        <v>4.847036772240028</v>
+        <v>4.847036853460228</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>3.992318974200495</v>
       </c>
       <c r="C11" t="n">
-        <v>13.4743997567906</v>
+        <v>13.47439979390154</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>2.614250975720806</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.0482376446328611</v>
+        <v>-0.048237383625256</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>8.093367320642244</v>
       </c>
       <c r="C13" t="n">
-        <v>0.06682718153920009</v>
+        <v>0.06682923659618512</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>0.8754864682719924</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3597219067066272</v>
+        <v>0.3597219117436294</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>14.35776078315886</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6802039861971346</v>
+        <v>0.6802039762800973</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>92.0046082949309</v>
       </c>
       <c r="C16" t="n">
-        <v>2.54076938034105</v>
+        <v>2.540769443619561</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/Project_1_May2026_Update.xlsx
+++ b/Project_1_May2026_Update.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="LSQ_Returns" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SP500TR_Returns" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="NVIDIA_Returns" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Verification" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Updated_Table_2" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Updated_Table_4" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Regression" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Serial_Correlation" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Newey_West" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LSQ_Returns" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP500TR_Returns" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NVIDIA_Returns" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Updated_Table_2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Updated_Table_4" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regression" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Serial_Correlation" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Newey_West" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -473,7 +473,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>data/LSQ_latest_spartan.pdf</t>
+          <t>data\LSQ_latest_spartan.pdf</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-12T19:20:04</t>
+          <t>2026-06-12T15:23:43</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4131,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.02285947846851455</v>
+        <v>0.02285966216268376</v>
       </c>
     </row>
     <row r="3">
@@ -4146,7 +4146,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.07052561218703712</v>
+        <v>-0.0705258722648533</v>
       </c>
     </row>
     <row r="4">
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.07476793427886541</v>
+        <v>0.07476823511005271</v>
       </c>
     </row>
     <row r="5">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.0425041194067628</v>
+        <v>-0.04250438224323216</v>
       </c>
     </row>
     <row r="6">
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.3839884885419578</v>
+        <v>0.3839886526392016</v>
       </c>
     </row>
     <row r="7">
@@ -4206,7 +4206,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.002509416178806623</v>
+        <v>0.002509148089431923</v>
       </c>
     </row>
     <row r="8">
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.1241696132363102</v>
+        <v>0.1241705244242364</v>
       </c>
     </row>
     <row r="9">
@@ -4236,7 +4236,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.04264391892696051</v>
+        <v>0.04264294650610112</v>
       </c>
     </row>
     <row r="10">
@@ -4251,7 +4251,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0559926954833152</v>
+        <v>0.05599317763857115</v>
       </c>
     </row>
     <row r="11">
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.15684926079897</v>
+        <v>0.1568494769886124</v>
       </c>
     </row>
     <row r="12">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.02949588452660679</v>
+        <v>-0.02949597245344471</v>
       </c>
     </row>
     <row r="13">
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.03525219898404675</v>
+        <v>-0.03525258070522685</v>
       </c>
     </row>
     <row r="14">
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.2702839640196344</v>
+        <v>0.2702840449401422</v>
       </c>
     </row>
     <row r="15">
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.01545955810866706</v>
+        <v>-0.01545971887763486</v>
       </c>
     </row>
     <row r="16">
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.04242192833258129</v>
+        <v>-0.04242178566555299</v>
       </c>
     </row>
     <row r="17">
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.02888722578051672</v>
+        <v>-0.0288869830080688</v>
       </c>
     </row>
     <row r="18">
@@ -4371,7 +4371,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.1213427710777206</v>
+        <v>0.121342685267563</v>
       </c>
     </row>
     <row r="19">
@@ -4386,7 +4386,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.06004806042616784</v>
+        <v>-0.06004814154578675</v>
       </c>
     </row>
     <row r="20">
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.03360059920092984</v>
+        <v>0.03360093032472533</v>
       </c>
     </row>
     <row r="21">
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.1462877868816175</v>
+        <v>0.14628737000368</v>
       </c>
     </row>
     <row r="22">
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.001759021901640123</v>
+        <v>0.001759159693233814</v>
       </c>
     </row>
     <row r="23">
@@ -4446,7 +4446,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.2497688216809697</v>
+        <v>-0.2497685644382728</v>
       </c>
     </row>
     <row r="24">
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.2248255968109131</v>
+        <v>-0.2248259008642258</v>
       </c>
     </row>
     <row r="25">
@@ -4476,7 +4476,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.182319128270181</v>
+        <v>-0.1823190908003643</v>
       </c>
     </row>
     <row r="26">
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.07677882443358564</v>
+        <v>0.07677890209461724</v>
       </c>
     </row>
     <row r="27">
@@ -4506,7 +4506,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.07311319032805774</v>
+        <v>0.07311298938575894</v>
       </c>
     </row>
     <row r="28">
@@ -4521,7 +4521,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.1652083294062485</v>
+        <v>0.1652084227590536</v>
       </c>
     </row>
     <row r="29">
@@ -4536,7 +4536,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.008019904808493239</v>
+        <v>0.008019691397869622</v>
       </c>
     </row>
     <row r="30">
@@ -4551,7 +4551,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.2516023685699601</v>
+        <v>-0.2516020768038197</v>
       </c>
     </row>
     <row r="31">
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.2137713567816002</v>
+        <v>0.2137712705956767</v>
       </c>
     </row>
     <row r="32">
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0273394629803918</v>
+        <v>0.02733969698402072</v>
       </c>
     </row>
     <row r="33">
@@ -4596,7 +4596,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-0.007171538252247034</v>
+        <v>-0.0071719921713288</v>
       </c>
     </row>
     <row r="34">
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.04019042914811277</v>
+        <v>0.04019055307952191</v>
       </c>
     </row>
     <row r="35">
@@ -4626,7 +4626,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.1548228836198227</v>
+        <v>0.1548226801361059</v>
       </c>
     </row>
     <row r="36">
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.07820129375297236</v>
+        <v>0.07820150714433938</v>
       </c>
     </row>
     <row r="37">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.08643349751164076</v>
+        <v>0.08643350516687431</v>
       </c>
     </row>
     <row r="38">
@@ -4671,7 +4671,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.004802361259457877</v>
+        <v>0.00480244317265166</v>
       </c>
     </row>
     <row r="39">
@@ -4686,7 +4686,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.1422834116649898</v>
+        <v>0.1422832494008599</v>
       </c>
     </row>
     <row r="40">
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-0.02337309309711155</v>
+        <v>-0.02337281231242416</v>
       </c>
     </row>
     <row r="41">
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.1088012187721632</v>
+        <v>0.1088009847686955</v>
       </c>
     </row>
     <row r="42">
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.2146569056806928</v>
+        <v>0.2146569853497966</v>
       </c>
     </row>
     <row r="43">
@@ -4746,7 +4746,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.07010878345862448</v>
+        <v>0.07010899945310189</v>
       </c>
     </row>
     <row r="44">
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.1181167842135795</v>
+        <v>0.1181163566856096</v>
       </c>
     </row>
     <row r="45">
@@ -4776,7 +4776,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.2599922845356388</v>
+        <v>0.2599924217301743</v>
       </c>
     </row>
     <row r="46">
@@ -4791,7 +4791,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.01166380064063821</v>
+        <v>0.01166423129057348</v>
       </c>
     </row>
     <row r="47">
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-0.07337114766282293</v>
+        <v>-0.07337161735437492</v>
       </c>
     </row>
     <row r="48">
@@ -4821,7 +4821,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.06921134413415575</v>
+        <v>0.06921196604474256</v>
       </c>
     </row>
     <row r="49">
@@ -4836,7 +4836,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-0.02585514807700895</v>
+        <v>-0.02585527992983927</v>
       </c>
     </row>
     <row r="50">
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-0.004703922850822995</v>
+        <v>-0.004704361672023816</v>
       </c>
     </row>
     <row r="51">
@@ -4866,7 +4866,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.0557940521589344</v>
+        <v>0.0557940603845084</v>
       </c>
     </row>
     <row r="52">
@@ -4881,7 +4881,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-0.02670520634787643</v>
+        <v>-0.02670534971344485</v>
       </c>
     </row>
     <row r="53">
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.1248423646832617</v>
+        <v>0.1248426157068663</v>
       </c>
     </row>
     <row r="54">
@@ -4911,7 +4911,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.08228142302058505</v>
+        <v>0.08228098186082344</v>
       </c>
     </row>
     <row r="55">
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.2313394526377714</v>
+        <v>0.2313400330823481</v>
       </c>
     </row>
     <row r="56">
@@ -4941,7 +4941,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-0.02494820800560771</v>
+        <v>-0.02494830371288737</v>
       </c>
     </row>
     <row r="57">
@@ -4956,7 +4956,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.1480076176984868</v>
+        <v>0.1480076322263386</v>
       </c>
     </row>
     <row r="58">
@@ -4971,7 +4971,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-0.07439584381792541</v>
+        <v>-0.07439567917632861</v>
       </c>
     </row>
     <row r="59">
@@ -4986,7 +4986,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.2341670038298038</v>
+        <v>0.2341667974520816</v>
       </c>
     </row>
     <row r="60">
@@ -5001,7 +5001,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.2780534261014624</v>
+        <v>0.2780539708405791</v>
       </c>
     </row>
     <row r="61">
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-0.09992041270609098</v>
+        <v>-0.09992061184862888</v>
       </c>
     </row>
     <row r="62">
@@ -5031,7 +5031,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-0.1673522501543653</v>
+        <v>-0.1673523585057887</v>
       </c>
     </row>
     <row r="63">
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.1189665252488112</v>
+        <v>0.1189666821792394</v>
       </c>
     </row>
     <row r="65">
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-0.3201582394095088</v>
+        <v>-0.3201581243857232</v>
       </c>
     </row>
     <row r="66">
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.006739557167566579</v>
+        <v>0.00673914249837182</v>
       </c>
     </row>
     <row r="67">
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-0.1881425429997872</v>
+        <v>-0.1881426135037536</v>
       </c>
     </row>
     <row r="68">
@@ -5121,7 +5121,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.1984192587484812</v>
+        <v>0.1984196118060286</v>
       </c>
     </row>
     <row r="69">
@@ -5136,7 +5136,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-0.1689699723439044</v>
+        <v>-0.1689700072028205</v>
       </c>
     </row>
     <row r="70">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-0.1957730742947046</v>
+        <v>-0.1957731252487188</v>
       </c>
     </row>
     <row r="71">
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0.1122011681009001</v>
+        <v>0.1122010893199503</v>
       </c>
     </row>
     <row r="72">
@@ -5181,7 +5181,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.2538345464373262</v>
+        <v>0.2538342102504385</v>
       </c>
     </row>
     <row r="73">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-0.1362208159385478</v>
+        <v>-0.136220466658155</v>
       </c>
     </row>
     <row r="74">
@@ -5211,7 +5211,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.3368690841728628</v>
+        <v>0.3368687351278623</v>
       </c>
     </row>
     <row r="75">
@@ -5226,7 +5226,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.1883090998823127</v>
+        <v>0.1883092345767339</v>
       </c>
     </row>
     <row r="76">
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.1964592501287579</v>
+        <v>0.1964593486442521</v>
       </c>
     </row>
     <row r="77">
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.3634363955175532</v>
+        <v>0.363436671024731</v>
       </c>
     </row>
     <row r="79">
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.1180949371097999</v>
+        <v>0.1180945091101937</v>
       </c>
     </row>
     <row r="80">
@@ -5301,7 +5301,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.1047664624860469</v>
+        <v>0.1047668428710162</v>
       </c>
     </row>
     <row r="81">
@@ -5316,7 +5316,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0.05619648045772951</v>
+        <v>0.05619630767771078</v>
       </c>
     </row>
     <row r="82">
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-0.1186505558252673</v>
+        <v>-0.1186507107084115</v>
       </c>
     </row>
     <row r="83">
@@ -5346,7 +5346,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-0.06243006332314394</v>
+        <v>-0.06242972282599102</v>
       </c>
     </row>
     <row r="84">
@@ -5361,7 +5361,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>0.1468858727358351</v>
+        <v>0.1468857514863415</v>
       </c>
     </row>
     <row r="85">
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>0.05884114141242036</v>
+        <v>0.05884105488915115</v>
       </c>
     </row>
     <row r="86">
@@ -5391,7 +5391,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>0.2425266570775326</v>
+        <v>0.2425267342515915</v>
       </c>
     </row>
     <row r="87">
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>0.2858097496850216</v>
+        <v>0.2858096698226296</v>
       </c>
     </row>
     <row r="88">
@@ -5436,7 +5436,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-0.04371531081375535</v>
+        <v>-0.04371522622661506</v>
       </c>
     </row>
     <row r="90">
@@ -5451,7 +5451,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>0.2688710270916701</v>
+        <v>0.2688710033089727</v>
       </c>
     </row>
     <row r="91">
@@ -5466,7 +5466,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>0.1268505324471054</v>
+        <v>0.1268503841828028</v>
       </c>
     </row>
     <row r="92">
@@ -5481,7 +5481,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-0.05269871694819739</v>
+        <v>-0.052698658344975</v>
       </c>
     </row>
     <row r="93">
@@ -5496,7 +5496,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>0.02008208031891745</v>
+        <v>0.02008214562373478</v>
       </c>
     </row>
     <row r="94">
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>0.01734113112542701</v>
+        <v>0.01734106599608709</v>
       </c>
     </row>
     <row r="95">
@@ -5526,7 +5526,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>0.09330797253547929</v>
+        <v>0.09330822424722918</v>
       </c>
     </row>
     <row r="96">
@@ -5541,7 +5541,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>0.04135301734180707</v>
+        <v>0.04135289270640019</v>
       </c>
     </row>
     <row r="97">
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-0.02864379662791638</v>
+        <v>-0.02864379346153278</v>
       </c>
     </row>
     <row r="98">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-0.1058286130610341</v>
+        <v>-0.1058287148205893</v>
       </c>
     </row>
     <row r="99">
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>0.05367232174856373</v>
+        <v>0.05367240806636397</v>
       </c>
     </row>
     <row r="110">
@@ -5751,7 +5751,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>0.02488282237211026</v>
+        <v>0.02488273841277922</v>
       </c>
     </row>
     <row r="111">
@@ -6237,7 +6237,7 @@
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -6273,7 +6273,7 @@
         <v>3.495221238938055</v>
       </c>
       <c r="C2" t="n">
-        <v>4.847036853460228</v>
+        <v>4.847037161994041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>3.422856966733567</v>
       </c>
       <c r="C3" t="n">
-        <v>3.957808721770739</v>
+        <v>3.957808805313401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>3.697222222222224</v>
       </c>
       <c r="C6" t="n">
-        <v>12.37255821599764</v>
+        <v>12.37256091799214</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>-0.8680000000000002</v>
       </c>
       <c r="C7" t="n">
-        <v>-8.887039633170533</v>
+        <v>-8.887043692702484</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>21.97</v>
       </c>
       <c r="C8" t="n">
-        <v>38.39884885419578</v>
+        <v>38.39886526392016</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>-2.2</v>
       </c>
       <c r="C9" t="n">
-        <v>-32.01582394095088</v>
+        <v>-32.01581243857233</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>3.495221238938055</v>
       </c>
       <c r="C10" t="n">
-        <v>4.847036853460228</v>
+        <v>4.847037161994041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>3.992318974200495</v>
       </c>
       <c r="C11" t="n">
-        <v>13.47439979390154</v>
+        <v>13.4744020813298</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>2.614250975720806</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.048237383625256</v>
+        <v>-0.04823653960140341</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>8.093367320642244</v>
       </c>
       <c r="C13" t="n">
-        <v>0.06682923659618512</v>
+        <v>0.06682762078836069</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>0.8754864682719924</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3597219117436294</v>
+        <v>0.3597218735746442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>14.35776078315886</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6802039762800973</v>
+        <v>0.6802040455549085</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>92.0046082949309</v>
       </c>
       <c r="C16" t="n">
-        <v>2.540769443619561</v>
+        <v>2.540768837884408</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/Project_1_May2026_Update.xlsx
+++ b/Project_1_May2026_Update.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LSQ_Returns" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP500TR_Returns" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NVIDIA_Returns" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Updated_Table_2" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Updated_Table_4" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regression" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Serial_Correlation" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Newey_West" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="LSQ_Returns" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SP500TR_Returns" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="NVIDIA_Returns" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Verification" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Updated_Table_2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Updated_Table_4" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Regression" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Serial_Correlation" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Newey_West" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -473,7 +473,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>data\LSQ_latest_spartan.pdf</t>
+          <t>data/LSQ_latest_spartan.pdf</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-12T15:23:43</t>
+          <t>2026-06-12T19:25:40</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4131,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.02285966216268376</v>
+        <v>0.02285948054436449</v>
       </c>
     </row>
     <row r="3">
@@ -4146,7 +4146,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.0705258722648533</v>
+        <v>-0.07052579600768338</v>
       </c>
     </row>
     <row r="4">
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.07476823511005271</v>
+        <v>0.07476833776766578</v>
       </c>
     </row>
     <row r="5">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.04250438224323216</v>
+        <v>-0.04250429337194372</v>
       </c>
     </row>
     <row r="6">
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.3839886526392016</v>
+        <v>0.3839885241823804</v>
       </c>
     </row>
     <row r="7">
@@ -4206,7 +4206,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.002509148089431923</v>
+        <v>0.002509215153848832</v>
       </c>
     </row>
     <row r="8">
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.1241705244242364</v>
+        <v>0.1241703154279787</v>
       </c>
     </row>
     <row r="9">
@@ -4236,7 +4236,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.04264294650610112</v>
+        <v>0.04264295158125098</v>
       </c>
     </row>
     <row r="10">
@@ -4251,7 +4251,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.05599317763857115</v>
+        <v>0.05599284158782702</v>
       </c>
     </row>
     <row r="11">
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.1568494769886124</v>
+        <v>0.1568496529019743</v>
       </c>
     </row>
     <row r="12">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.02949597245344471</v>
+        <v>-0.02949560696569009</v>
       </c>
     </row>
     <row r="13">
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.03525258070522685</v>
+        <v>-0.03525296242633347</v>
       </c>
     </row>
     <row r="14">
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.2702840449401422</v>
+        <v>0.2702848244392311</v>
       </c>
     </row>
     <row r="15">
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.01545971887763486</v>
+        <v>-0.01545979258205243</v>
       </c>
     </row>
     <row r="16">
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.04242178566555299</v>
+        <v>-0.04242201489908204</v>
       </c>
     </row>
     <row r="17">
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.0288869830080688</v>
+        <v>-0.02888706633942995</v>
       </c>
     </row>
     <row r="18">
@@ -4371,7 +4371,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.121342685267563</v>
+        <v>0.1213426956799988</v>
       </c>
     </row>
     <row r="19">
@@ -4386,7 +4386,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.06004814154578675</v>
+        <v>-0.0600478400430251</v>
       </c>
     </row>
     <row r="20">
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.03360093032472533</v>
+        <v>0.0336006778785618</v>
       </c>
     </row>
     <row r="21">
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.14628737000368</v>
+        <v>0.1462874487702335</v>
       </c>
     </row>
     <row r="22">
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.001759159693233814</v>
+        <v>0.001759090857867296</v>
       </c>
     </row>
     <row r="23">
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.2248259008642258</v>
+        <v>-0.2248258094340077</v>
       </c>
     </row>
     <row r="25">
@@ -4476,7 +4476,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.1823190908003643</v>
+        <v>-0.182319128270181</v>
       </c>
     </row>
     <row r="26">
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.07677890209461724</v>
+        <v>0.07677896868052714</v>
       </c>
     </row>
     <row r="27">
@@ -4506,7 +4506,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.07311298938575894</v>
+        <v>0.07311304657218942</v>
       </c>
     </row>
     <row r="28">
@@ -4521,7 +4521,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.1652084227590536</v>
+        <v>0.1652085790752187</v>
       </c>
     </row>
     <row r="29">
@@ -4536,7 +4536,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.008019691397869622</v>
+        <v>0.008019474550537087</v>
       </c>
     </row>
     <row r="30">
@@ -4551,7 +4551,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.2516020768038197</v>
+        <v>-0.2516021563454617</v>
       </c>
     </row>
     <row r="31">
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.02733969698402072</v>
+        <v>0.0273394629803918</v>
       </c>
     </row>
     <row r="33">
@@ -4596,7 +4596,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-0.0071719921713288</v>
+        <v>-0.007171310475901138</v>
       </c>
     </row>
     <row r="34">
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.04019055307952191</v>
+        <v>0.04019019050596073</v>
       </c>
     </row>
     <row r="35">
@@ -4626,7 +4626,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.1548226801361059</v>
+        <v>0.1548228836198227</v>
       </c>
     </row>
     <row r="36">
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.07820150714433938</v>
+        <v>0.07820100727091472</v>
       </c>
     </row>
     <row r="37">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.08643350516687431</v>
+        <v>0.0864336976131832</v>
       </c>
     </row>
     <row r="38">
@@ -4671,7 +4671,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.00480244317265166</v>
+        <v>0.00480236165095449</v>
       </c>
     </row>
     <row r="39">
@@ -4686,7 +4686,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.1422832494008599</v>
+        <v>0.1422831798125233</v>
       </c>
     </row>
     <row r="40">
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-0.02337281231242416</v>
+        <v>-0.02337288665882298</v>
       </c>
     </row>
     <row r="41">
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.1088009847686955</v>
+        <v>0.1088012266848462</v>
       </c>
     </row>
     <row r="42">
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.2146569853497966</v>
+        <v>0.2146571165293971</v>
       </c>
     </row>
     <row r="43">
@@ -4746,7 +4746,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.07010899945310189</v>
+        <v>0.07010899188152453</v>
       </c>
     </row>
     <row r="44">
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.1181163566856096</v>
+        <v>0.1181167484519368</v>
       </c>
     </row>
     <row r="45">
@@ -4776,7 +4776,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.2599924217301743</v>
+        <v>0.2599917628323942</v>
       </c>
     </row>
     <row r="46">
@@ -4791,7 +4791,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.01166423129057348</v>
+        <v>0.01166416049041263</v>
       </c>
     </row>
     <row r="47">
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-0.07337161735437492</v>
+        <v>-0.07337141531583402</v>
       </c>
     </row>
     <row r="48">
@@ -4821,7 +4821,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.06921196604474256</v>
+        <v>0.06921165508942528</v>
       </c>
     </row>
     <row r="49">
@@ -4836,7 +4836,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-0.02585527992983927</v>
+        <v>-0.02585528547347249</v>
       </c>
     </row>
     <row r="50">
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-0.004704361672023816</v>
+        <v>-0.004704069239626296</v>
       </c>
     </row>
     <row r="51">
@@ -4866,7 +4866,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.0557940603845084</v>
+        <v>0.05579420369914567</v>
       </c>
     </row>
     <row r="52">
@@ -4881,7 +4881,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-0.02670534971344485</v>
+        <v>-0.02670548375639825</v>
       </c>
     </row>
     <row r="53">
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.1248426157068663</v>
+        <v>0.1248424632835168</v>
       </c>
     </row>
     <row r="54">
@@ -4911,7 +4911,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.08228098186082344</v>
+        <v>0.08228117842540117</v>
       </c>
     </row>
     <row r="55">
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.2313400330823481</v>
+        <v>0.2313400058193438</v>
       </c>
     </row>
     <row r="56">
@@ -4941,7 +4941,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-0.02494830371288737</v>
+        <v>-0.02494830132515324</v>
       </c>
     </row>
     <row r="57">
@@ -4956,7 +4956,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.1480076322263386</v>
+        <v>0.1480076176984868</v>
       </c>
     </row>
     <row r="58">
@@ -4971,7 +4971,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-0.07439567917632861</v>
+        <v>-0.07439592931918593</v>
       </c>
     </row>
     <row r="59">
@@ -4986,7 +4986,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.2341667974520816</v>
+        <v>0.2341670254606225</v>
       </c>
     </row>
     <row r="60">
@@ -5001,7 +5001,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.2780539708405791</v>
+        <v>0.2780538211469497</v>
       </c>
     </row>
     <row r="61">
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-0.09992061184862888</v>
+        <v>-0.09992062355195375</v>
       </c>
     </row>
     <row r="62">
@@ -5031,7 +5031,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-0.1673523585057887</v>
+        <v>-0.1673522501543653</v>
       </c>
     </row>
     <row r="63">
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-0.3201581243857232</v>
+        <v>-0.3201584048774139</v>
       </c>
     </row>
     <row r="66">
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.00673914249837182</v>
+        <v>0.006739764154670258</v>
       </c>
     </row>
     <row r="67">
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-0.1881426135037536</v>
+        <v>-0.188142779862177</v>
       </c>
     </row>
     <row r="68">
@@ -5121,7 +5121,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.1984196118060286</v>
+        <v>0.198419485607179</v>
       </c>
     </row>
     <row r="69">
@@ -5136,7 +5136,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-0.1689700072028205</v>
+        <v>-0.1689698670395005</v>
       </c>
     </row>
     <row r="70">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-0.1957731252487188</v>
+        <v>-0.1957732395604797</v>
       </c>
     </row>
     <row r="71">
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0.1122010893199503</v>
+        <v>0.1122012557211716</v>
       </c>
     </row>
     <row r="72">
@@ -5181,7 +5181,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.2538342102504385</v>
+        <v>0.2538342631038712</v>
       </c>
     </row>
     <row r="73">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-0.136220466658155</v>
+        <v>-0.1362206772406498</v>
       </c>
     </row>
     <row r="74">
@@ -5211,7 +5211,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.3368687351278623</v>
+        <v>0.3368693024127341</v>
       </c>
     </row>
     <row r="75">
@@ -5226,7 +5226,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.1883092345767339</v>
+        <v>0.1883088857685222</v>
       </c>
     </row>
     <row r="76">
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.1964593486442521</v>
+        <v>0.1964592663050548</v>
       </c>
     </row>
     <row r="77">
@@ -5256,7 +5256,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-0.0008383536831267913</v>
+        <v>-0.0008382849217655197</v>
       </c>
     </row>
     <row r="78">
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.363436671024731</v>
+        <v>0.3634365332711422</v>
       </c>
     </row>
     <row r="79">
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.1180945091101937</v>
+        <v>0.1180947231099752</v>
       </c>
     </row>
     <row r="80">
@@ -5301,7 +5301,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.1047668428710162</v>
+        <v>0.104766562315773</v>
       </c>
     </row>
     <row r="81">
@@ -5316,7 +5316,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0.05619630767771078</v>
+        <v>0.05619656225124547</v>
       </c>
     </row>
     <row r="82">
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-0.1186507107084115</v>
+        <v>-0.1186507015199146</v>
       </c>
     </row>
     <row r="83">
@@ -5346,7 +5346,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-0.06242972282599102</v>
+        <v>-0.0624299809416361</v>
       </c>
     </row>
     <row r="84">
@@ -5361,7 +5361,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>0.1468857514863415</v>
+        <v>0.1468859664536928</v>
       </c>
     </row>
     <row r="85">
@@ -5391,7 +5391,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>0.2425267342515915</v>
+        <v>0.2425266570775326</v>
       </c>
     </row>
     <row r="87">
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>0.2858096698226296</v>
+        <v>0.2858097496850216</v>
       </c>
     </row>
     <row r="88">
@@ -5436,7 +5436,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-0.04371522622661506</v>
+        <v>-0.04371531081375535</v>
       </c>
     </row>
     <row r="90">
@@ -5451,7 +5451,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>0.2688710033089727</v>
+        <v>0.2688709386377386</v>
       </c>
     </row>
     <row r="91">
@@ -5466,7 +5466,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>0.1268503841828028</v>
+        <v>0.1268506110006893</v>
       </c>
     </row>
     <row r="92">
@@ -5481,7 +5481,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-0.052698658344975</v>
+        <v>-0.05269877881153473</v>
       </c>
     </row>
     <row r="93">
@@ -5496,7 +5496,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>0.02008214562373478</v>
+        <v>0.02008214693519572</v>
       </c>
     </row>
     <row r="94">
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>0.01734106599608709</v>
+        <v>0.01734113112542701</v>
       </c>
     </row>
     <row r="95">
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-0.02864379346153278</v>
+        <v>-0.02864390400496653</v>
       </c>
     </row>
     <row r="98">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-0.1058287148205893</v>
+        <v>-0.1058286130610341</v>
       </c>
     </row>
     <row r="99">
@@ -5631,7 +5631,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>0.2406355273027898</v>
+        <v>0.240635387014742</v>
       </c>
     </row>
     <row r="103">
@@ -5646,7 +5646,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>0.16917037363203</v>
+        <v>0.169170505838987</v>
       </c>
     </row>
     <row r="104">
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>0.1259088530315122</v>
+        <v>0.1259089497475856</v>
       </c>
     </row>
     <row r="105">
@@ -5676,7 +5676,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>-0.02074555918313137</v>
+        <v>-0.02074555740107875</v>
       </c>
     </row>
     <row r="106">
@@ -5691,7 +5691,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>0.07119086207604353</v>
+        <v>0.07119068039067433</v>
       </c>
     </row>
     <row r="107">
@@ -5706,7 +5706,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>0.08533291274421861</v>
+        <v>0.08533300162257662</v>
       </c>
     </row>
     <row r="108">
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>0.05367240806636397</v>
+        <v>0.05367232174856373</v>
       </c>
     </row>
     <row r="110">
@@ -5751,7 +5751,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>0.02488273841277922</v>
+        <v>0.02488282237211026</v>
       </c>
     </row>
     <row r="111">
@@ -5781,7 +5781,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>-0.0157459214714587</v>
+        <v>-0.01574583525101958</v>
       </c>
     </row>
     <row r="113">
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>0.1443854586470354</v>
+        <v>0.1443853583991317</v>
       </c>
     </row>
     <row r="114">
@@ -6273,7 +6273,7 @@
         <v>3.495221238938055</v>
       </c>
       <c r="C2" t="n">
-        <v>4.847037161994041</v>
+        <v>4.847037469855275</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>3.697222222222224</v>
       </c>
       <c r="C6" t="n">
-        <v>12.37256091799214</v>
+        <v>12.37256151496673</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>-0.8680000000000002</v>
       </c>
       <c r="C7" t="n">
-        <v>-8.887043692702484</v>
+        <v>-8.887043912473107</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>21.97</v>
       </c>
       <c r="C8" t="n">
-        <v>38.39886526392016</v>
+        <v>38.39885241823804</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>-2.2</v>
       </c>
       <c r="C9" t="n">
-        <v>-32.01581243857233</v>
+        <v>-32.01584048774139</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>3.495221238938055</v>
       </c>
       <c r="C10" t="n">
-        <v>4.847037161994041</v>
+        <v>4.847037469855275</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>3.992318974200495</v>
       </c>
       <c r="C11" t="n">
-        <v>13.4744020813298</v>
+        <v>13.4744041453342</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>2.614250975720806</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.04823653960140341</v>
+        <v>-0.04823684136550973</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>8.093367320642244</v>
       </c>
       <c r="C13" t="n">
-        <v>0.06682762078836069</v>
+        <v>0.06682822787090004</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>0.8754864682719924</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3597218735746442</v>
+        <v>0.3597218413204318</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>14.35776078315886</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6802040455549085</v>
+        <v>0.6802039163545515</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>92.0046082949309</v>
       </c>
       <c r="C16" t="n">
-        <v>2.540768837884408</v>
+        <v>2.540768897644693</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/Project_1_May2026_Update.xlsx
+++ b/Project_1_May2026_Update.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_and_Method" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LSQ_Returns" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP500TR_Returns" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NVIDIA_Returns" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Updated_Table_2" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Updated_Table_4" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regression" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Serial_Correlation" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Newey_West" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Source_and_Method" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="LSQ_Returns" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SP500TR_Returns" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="NVIDIA_Returns" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Verification" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Updated_Table_2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Updated_Table_4" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Regression" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Serial_Correlation" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Newey_West" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Source_and_Method'!$A$1:$B$8</definedName>
@@ -504,7 +504,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>data\LSQ_latest_spartan.pdf</t>
+          <t>data/LSQ_latest_spartan.pdf</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18T02:40:56</t>
+          <t>2026-07-10T15:31:37</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2.62549090385437</v>
+        <v>2.628551244735718</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -6636,10 +6636,10 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.685508012771606</v>
+        <v>2.68863844871521</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.02285938558352174</v>
+        <v>0.02285943791274025</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2.685508012771606</v>
+        <v>2.68863844871521</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -6672,10 +6672,10 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2.499260902404785</v>
+        <v>2.50217342376709</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-0.06935265487240272</v>
+        <v>-0.06935295634012228</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.499260902404785</v>
+        <v>2.50217342376709</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -6708,10 +6708,10 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2.682739973068237</v>
+        <v>2.685867547988892</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.07341333211226919</v>
+        <v>0.07341382594706225</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2.682739973068237</v>
+        <v>2.685867547988892</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -6744,10 +6744,10 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2.568711996078491</v>
+        <v>2.571706056594849</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-0.04250429714935544</v>
+        <v>-0.04250451273352041</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2.568711996078491</v>
+        <v>2.571706056594849</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -6780,10 +6780,10 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>3.558810949325562</v>
+        <v>3.562959671020508</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.385445684357997</v>
+        <v>0.3854459229054199</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3.558810949325562</v>
+        <v>3.562959671020508</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -6816,10 +6816,10 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3.563989400863647</v>
+        <v>3.568142890930176</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.001455107228740982</v>
+        <v>0.001454751214790884</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>3.563989400863647</v>
+        <v>3.568142890930176</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -6852,10 +6852,10 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>4.006529331207275</v>
+        <v>4.011197566986084</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.1241698222324648</v>
+        <v>0.124169544101528</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>4.006529331207275</v>
+        <v>4.011197566986084</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>4.181060791015625</v>
+        <v>4.185932159423828</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.04356175766614401</v>
+        <v>0.0435617018408383</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>4.181060791015625</v>
+        <v>4.185932159423828</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -6924,10 +6924,10 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>4.411284446716309</v>
+        <v>4.416426658630371</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.05506345571329518</v>
+        <v>0.05506407902183241</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4.411284446716309</v>
+        <v>4.416426658630371</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -6960,10 +6960,10 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>5.103192329406738</v>
+        <v>5.109140396118164</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.1568495278524773</v>
+        <v>0.1568493696446027</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>5.103192329406738</v>
+        <v>5.109140396118164</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>4.956112384796143</v>
+        <v>4.961888313293457</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-0.02882116430593051</v>
+        <v>-0.02882130288229823</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>4.956112384796143</v>
+        <v>4.961888313293457</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -7032,10 +7032,10 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>4.778075218200684</v>
+        <v>4.783644199371338</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0.03592274605023549</v>
+        <v>-0.03592263724368461</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4.778075218200684</v>
+        <v>4.783644199371338</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -7068,10 +7068,10 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>6.069512844085693</v>
+        <v>6.076587677001953</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.2702840719136557</v>
+        <v>0.2702842067143147</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>6.069512844085693</v>
+        <v>6.076587677001953</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -7104,10 +7104,10 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>5.979396343231201</v>
+        <v>5.986364841461182</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-0.01484740261194184</v>
+        <v>-0.0148476151972986</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5.979396343231201</v>
+        <v>5.986364841461182</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -7140,10 +7140,10 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>5.722183704376221</v>
+        <v>5.728850841522217</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.04301648930600666</v>
+        <v>-0.04301675670607963</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>5.722183704376221</v>
+        <v>5.728850841522217</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -7176,10 +7176,10 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5.556884288787842</v>
+        <v>5.563360691070557</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.02888747096007438</v>
+        <v>-0.02888714596166508</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>5.556884288787842</v>
+        <v>5.563360691070557</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -7212,10 +7212,10 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>6.235026359558105</v>
+        <v>6.242292404174805</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.1220363850545809</v>
+        <v>0.1220362566450102</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>6.235026359558105</v>
+        <v>6.242292404174805</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
@@ -7248,10 +7248,10 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5.857002735137939</v>
+        <v>5.863829135894775</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>-0.06062903388382113</v>
+        <v>-0.06062889140324723</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -7276,7 +7276,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5.857002735137939</v>
+        <v>5.863829135894775</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -7284,10 +7284,10 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>6.053802013397217</v>
+        <v>6.060858249664307</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.0336006806140996</v>
+        <v>0.03360075970894849</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6.053802013397217</v>
+        <v>6.060858249664307</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
@@ -7320,10 +7320,10 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>6.943193912506104</v>
+        <v>6.951286315917969</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.1469145996417855</v>
+        <v>0.1469145176432696</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.943193912506104</v>
+        <v>6.951286315917969</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
@@ -7356,10 +7356,10 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>6.95160436630249</v>
+        <v>6.959707736968994</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.001211323477692039</v>
+        <v>0.001211491034650791</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>6.95160436630249</v>
+        <v>6.959707736968994</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -7392,10 +7392,10 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>5.215311050415039</v>
+        <v>5.221388339996338</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-0.249768718758512</v>
+        <v>-0.2497690223023227</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>5.215311050415039</v>
+        <v>5.221388339996338</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
@@ -7428,10 +7428,10 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>4.046821117401123</v>
+        <v>4.05153751373291</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-0.2240499026267909</v>
+        <v>-0.2240497641790513</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>4.046821117401123</v>
+        <v>4.05153751373291</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
@@ -7464,10 +7464,10 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>3.305700540542603</v>
+        <v>3.309553384780884</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>-0.1831364805505585</v>
+        <v>-0.1831364331286653</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3.305700540542603</v>
+        <v>3.309553384780884</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
@@ -7500,10 +7500,10 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>3.559508323669434</v>
+        <v>3.56365704536438</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.07677881889603055</v>
+        <v>0.07677883721471357</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.559508323669434</v>
+        <v>3.56365704536438</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
@@ -7536,10 +7536,10 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.823691368103027</v>
+        <v>3.828147411346436</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.07421897082719897</v>
+        <v>0.07421880461985131</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>3.823691368103027</v>
+        <v>3.828147411346436</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
@@ -7572,10 +7572,10 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>4.450810432434082</v>
+        <v>4.455998420715332</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.1640088082323901</v>
+        <v>0.1640090994165946</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>4.450810432434082</v>
+        <v>4.455998420715332</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
@@ -7608,10 +7608,10 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.486503124237061</v>
+        <v>4.491733074188232</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.008019369133962062</v>
+        <v>0.008019449312812732</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>4.486503124237061</v>
+        <v>4.491733074188232</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
@@ -7644,10 +7644,10 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3.361522197723389</v>
+        <v>3.365440368652344</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-0.2507478308521132</v>
+        <v>-0.2507479155447004</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>3.361522197723389</v>
+        <v>3.365440368652344</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -7680,10 +7680,10 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>4.075467109680176</v>
+        <v>4.080217838287354</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.2123873858219085</v>
+        <v>0.2123875009918048</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>4.075467109680176</v>
+        <v>4.080217838287354</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -7716,10 +7716,10 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>4.186890125274658</v>
+        <v>4.191769123077393</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.02733993738529428</v>
+        <v>0.02733954146841877</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>4.186890125274658</v>
+        <v>4.191769123077393</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
@@ -7752,10 +7752,10 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>4.160977363586426</v>
+        <v>4.165826797485352</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>-0.006189023574276975</v>
+        <v>-0.006188872724219974</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>4.160977363586426</v>
+        <v>4.165826797485352</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
@@ -7788,10 +7788,10 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>4.323929786682129</v>
+        <v>4.328968524932861</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.03916205469458545</v>
+        <v>0.03916190839858924</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>4.323929786682129</v>
+        <v>4.328968524932861</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
@@ -7824,10 +7824,10 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>4.993372917175293</v>
+        <v>4.999191284179688</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.1548228494725041</v>
+        <v>0.1548227378847067</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>4.993372917175293</v>
+        <v>4.999191284179688</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
@@ -7860,10 +7860,10 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>5.387832641601562</v>
+        <v>5.394112586975098</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.07899664835155384</v>
+        <v>0.07899703778992584</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>5.387832641601562</v>
+        <v>5.394112586975098</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
@@ -7896,10 +7896,10 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>5.849206924438477</v>
+        <v>5.856024265289307</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.08563263069354887</v>
+        <v>0.08563256158752863</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>5.849206924438477</v>
+        <v>5.856024265289307</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
@@ -7932,10 +7932,10 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>5.877297401428223</v>
+        <v>5.88414478302002</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.00480244199814206</v>
+        <v>0.004801981080815088</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>5.877297401428223</v>
+        <v>5.88414478302002</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
@@ -7968,10 +7968,10 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>6.717552185058594</v>
+        <v>6.725380897521973</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.1429661843258405</v>
+        <v>0.1429665899672494</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -7996,7 +7996,7 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>6.717552185058594</v>
+        <v>6.725380897521973</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -8004,10 +8004,10 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>6.556620597839355</v>
+        <v>6.564263343811035</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>-0.02395687934917534</v>
+        <v>-0.02395664367059158</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6.556620597839355</v>
+        <v>6.564263343811035</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>7.269988536834717</v>
+        <v>7.278463363647461</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.1088011618714742</v>
+        <v>0.1088012443178095</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>7.269988536834717</v>
+        <v>7.278463363647461</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -8076,10 +8076,10 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>8.830545425415039</v>
+        <v>8.840836524963379</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2146574070472709</v>
+        <v>0.214657007015965</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>8.830545425415039</v>
+        <v>8.840836524963379</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -8112,10 +8112,10 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>9.453958511352539</v>
+        <v>9.464973449707031</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.07059734771798643</v>
+        <v>0.07059704395407729</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>9.453958511352539</v>
+        <v>9.464973449707031</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>10.56580352783203</v>
+        <v>10.57811832427979</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.1176062931886535</v>
+        <v>0.1176067614439225</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>10.56580352783203</v>
+        <v>10.57811832427979</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>13.31282901763916</v>
+        <v>13.32834720611572</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2599921040147133</v>
+        <v>0.2599922592587551</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>13.31282901763916</v>
+        <v>13.32834720611572</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -8220,10 +8220,10 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>13.47213935852051</v>
+        <v>13.48784160614014</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.01196667820718389</v>
+        <v>0.01196655500925359</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>13.47213935852051</v>
+        <v>13.48784160614014</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -8256,10 +8256,10 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>12.47993659973145</v>
+        <v>12.49448299407959</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>-0.07364849281799779</v>
+        <v>-0.0736484488080239</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>12.47993659973145</v>
+        <v>12.49448299407959</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -8292,10 +8292,10 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>13.34369564056396</v>
+        <v>13.35924911499023</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.06921181321154357</v>
+        <v>0.06921183704202938</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>13.34369564056396</v>
+        <v>13.35924911499023</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -8328,10 +8328,10 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>13.00252914428711</v>
+        <v>13.01768684387207</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>-0.0255676167582638</v>
+        <v>-0.0255674752509033</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>13.00252914428711</v>
+        <v>13.01768684387207</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -8364,10 +8364,10 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>12.93754482269287</v>
+        <v>12.95262145996094</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>-0.004997821644782907</v>
+        <v>-0.00499822930843985</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>12.93754482269287</v>
+        <v>12.95262145996094</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -8400,10 +8400,10 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>13.65937995910645</v>
+        <v>13.67529964447021</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.05579382690504398</v>
+        <v>0.05579397087633686</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>13.65937995910645</v>
+        <v>13.67529964447021</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -8436,10 +8436,10 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>13.29919147491455</v>
+        <v>13.31469058990479</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>-0.02636931436640821</v>
+        <v>-0.02636937134399442</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>13.29919147491455</v>
+        <v>13.31469058990479</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -8472,10 +8472,10 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>14.9543342590332</v>
+        <v>14.97176265716553</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.1244543916252838</v>
+        <v>0.1244544179282046</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>14.9543342590332</v>
+        <v>14.97176265716553</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -8508,10 +8508,10 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>16.18479537963867</v>
+        <v>16.20365524291992</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.08228123695056544</v>
+        <v>0.08228106562755366</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>16.18479537963867</v>
+        <v>16.20365524291992</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -8544,10 +8544,10 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>19.93355178833008</v>
+        <v>19.95678520202637</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2316221070924096</v>
+        <v>0.2316224273375818</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>19.93355178833008</v>
+        <v>19.95678520202637</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -8580,10 +8580,10 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>19.43178939819336</v>
+        <v>19.45443153381348</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>-0.02517175039675923</v>
+        <v>-0.02517207371465235</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -8608,7 +8608,7 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>19.43178939819336</v>
+        <v>19.45443153381348</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -8616,10 +8616,10 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>22.3117733001709</v>
+        <v>22.33777809143066</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.1482099174173481</v>
+        <v>0.1482102703749366</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -8644,7 +8644,7 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>22.3117733001709</v>
+        <v>22.33777809143066</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -8652,10 +8652,10 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>20.64823341369629</v>
+        <v>20.67229652404785</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>-0.0745588377980636</v>
+        <v>-0.07455896287293373</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>20.64823341369629</v>
+        <v>20.67229652404785</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
@@ -8688,10 +8688,10 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>25.48336219787598</v>
+        <v>25.51306533813477</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.2341667050786278</v>
+        <v>0.2341669590727717</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -8716,7 +8716,7 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>25.48336219787598</v>
+        <v>25.51306533813477</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>32.5691032409668</v>
+        <v>32.60707092285156</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.2780536174179329</v>
+        <v>0.2780538320541703</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>32.5691032409668</v>
+        <v>32.60707092285156</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
@@ -8760,10 +8760,10 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>29.31837844848633</v>
+        <v>29.35254859924316</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>-0.0998100797688396</v>
+        <v>-0.09981032430998205</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>29.31837844848633</v>
+        <v>29.35254859924316</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
@@ -8796,10 +8796,10 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>24.40888786315918</v>
+        <v>24.43733787536621</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>-0.1674543697549078</v>
+        <v>-0.1674543083459433</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>24.40888786315918</v>
+        <v>24.43733787536621</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -8832,10 +8832,10 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>24.30820274353027</v>
+        <v>24.33654022216797</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>-0.004124936793243772</v>
+        <v>-0.004124739515913078</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>24.30820274353027</v>
+        <v>24.33654022216797</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
@@ -8868,10 +8868,10 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>27.20470237731934</v>
+        <v>27.23641204833984</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1191572928837767</v>
+        <v>0.1191571110642262</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>27.20470237731934</v>
+        <v>27.23641204833984</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>18.49174499511719</v>
+        <v>18.51329612731934</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>-0.3202739460758143</v>
+        <v>-0.3202740473135195</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>18.49174499511719</v>
+        <v>18.51329612731934</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
@@ -8940,10 +8940,10 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>18.61636543273926</v>
+        <v>18.63806915283203</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.006739247034553975</v>
+        <v>0.006739644018796564</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>18.61636543273926</v>
+        <v>18.63806915283203</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
@@ -8976,10 +8976,10 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>15.11703205108643</v>
+        <v>15.13465309143066</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>-0.187970814942148</v>
+        <v>-0.1879709766432016</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>15.11703205108643</v>
+        <v>15.13465309143066</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
@@ -9012,10 +9012,10 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>18.11271286010742</v>
+        <v>18.13382720947266</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1981659362034429</v>
+        <v>0.1981660299660348</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>18.11271286010742</v>
+        <v>18.13382720947266</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
@@ -9048,10 +9048,10 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>15.05221176147461</v>
+        <v>15.0697546005249</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>-0.1689697795283583</v>
+        <v>-0.1689699903695542</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>15.05221176147461</v>
+        <v>15.0697546005249</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
@@ -9084,10 +9084,10 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>12.10898971557617</v>
+        <v>12.12310409545898</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>-0.1955341907580299</v>
+        <v>-0.1955340735915687</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>12.10898971557617</v>
+        <v>12.12310409545898</v>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
@@ -9120,10 +9120,10 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>13.46363162994385</v>
+        <v>13.47932434082031</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1118707626471229</v>
+        <v>0.1118707085810915</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>13.46363162994385</v>
+        <v>13.47932434082031</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
@@ -9156,10 +9156,10 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>16.88547897338867</v>
+        <v>16.90515899658203</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.2541548549081252</v>
+        <v>0.2541547757988909</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>16.88547897338867</v>
+        <v>16.90515899658203</v>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
@@ -9192,10 +9192,10 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>14.5816011428833</v>
+        <v>14.59859466552734</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>-0.1364413668179776</v>
+        <v>-0.1364414455682458</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>14.5816011428833</v>
+        <v>14.59859466552734</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
@@ -9228,10 +9228,10 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>19.49368858337402</v>
+        <v>19.51640510559082</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.3368688659330197</v>
+        <v>0.3368687570781206</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>19.49368858337402</v>
+        <v>19.51640510559082</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -9264,10 +9264,10 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>23.16452789306641</v>
+        <v>23.19152641296387</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1883091183073071</v>
+        <v>0.1883093370674214</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>23.16452789306641</v>
+        <v>23.19152641296387</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -9300,10 +9300,10 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>27.72012329101562</v>
+        <v>27.75243186950684</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1966625617832167</v>
+        <v>0.1966625816398813</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>27.72012329101562</v>
+        <v>27.75243186950684</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
@@ -9336,10 +9336,10 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>27.69218254089355</v>
+        <v>27.72445487976074</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>-0.001007959085489563</v>
+        <v>-0.001008091466637717</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>27.69218254089355</v>
+        <v>27.72445487976074</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
@@ -9372,10 +9372,10 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>37.75653457641602</v>
+        <v>37.80053329467773</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.3634365771155903</v>
+        <v>0.3634364844544762</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>37.75653457641602</v>
+        <v>37.80053329467773</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
@@ -9408,10 +9408,10 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>42.21975708007812</v>
+        <v>42.26895141601562</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.1182105972842642</v>
+        <v>0.118210451860663</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>42.21975708007812</v>
+        <v>42.26895141601562</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
@@ -9444,10 +9444,10 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>46.63813781738281</v>
+        <v>46.69250106811523</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.1046519696672901</v>
+        <v>0.1046524577475925</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>46.63813781738281</v>
+        <v>46.69250106811523</v>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
@@ -9480,10 +9480,10 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>49.25904083251953</v>
+        <v>49.31644821166992</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.05619656225124547</v>
+        <v>0.05619632882219916</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>49.25904083251953</v>
+        <v>49.31644821166992</v>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
@@ -9516,10 +9516,10 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>43.41799926757812</v>
+        <v>43.46859741210938</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>-0.1185780613309324</v>
+        <v>-0.1185781014573704</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>43.41799926757812</v>
+        <v>43.46859741210938</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
@@ -9552,10 +9552,10 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>40.70405578613281</v>
+        <v>40.75150299072266</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>-0.06250733629432614</v>
+        <v>-0.06250706448213572</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>40.70405578613281</v>
+        <v>40.75150299072266</v>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
@@ -9588,10 +9588,10 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>46.68291473388672</v>
+        <v>46.73731994628906</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.1468860739373987</v>
+        <v>0.146885796014177</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>46.68291473388672</v>
+        <v>46.73731994628906</v>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
@@ -9624,10 +9624,10 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>49.43412780761719</v>
+        <v>49.49174499511719</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.05893404662955604</v>
+        <v>0.05893416764148074</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>49.43412780761719</v>
+        <v>49.49174499511719</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
@@ -9660,10 +9660,10 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>61.41783142089844</v>
+        <v>61.48941421508789</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.242417620068432</v>
+        <v>0.2424175834001081</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>61.41783142089844</v>
+        <v>61.48941421508789</v>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
@@ -9696,10 +9696,10 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>78.97163391113281</v>
+        <v>79.06366729736328</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.2858095456014653</v>
+        <v>0.2858094081170013</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>78.97163391113281</v>
+        <v>79.06366729736328</v>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
@@ -9732,10 +9732,10 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>90.19991302490234</v>
+        <v>90.30503845214844</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.1421811675620739</v>
+        <v>0.1421812513768894</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>90.19991302490234</v>
+        <v>90.30503845214844</v>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
@@ -9768,10 +9768,10 @@
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>86.25274658203125</v>
+        <v>86.35327911376953</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>-0.04376020231617472</v>
+        <v>-0.04376012021159703</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>86.25274658203125</v>
+        <v>86.35327911376953</v>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
@@ -9804,10 +9804,10 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>109.4436187744141</v>
+        <v>109.571174621582</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.2688711155456016</v>
+        <v>0.2688710347319083</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>109.4436187744141</v>
+        <v>109.571174621582</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
@@ -9840,10 +9840,10 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>123.3367156982422</v>
+        <v>123.4804611206055</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.1269429600319107</v>
+        <v>0.1269429350106077</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -9868,7 +9868,7 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>123.3367156982422</v>
+        <v>123.4804611206055</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
@@ -9876,10 +9876,10 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>116.8274459838867</v>
+        <v>116.9635848999023</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>-0.05277641517778997</v>
+        <v>-0.0527765782664027</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>116.8274459838867</v>
+        <v>116.9635848999023</v>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
@@ -9912,10 +9912,10 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>119.1735687255859</v>
+        <v>119.3124694824219</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.0200819483978345</v>
+        <v>0.02008218698605813</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>119.1735687255859</v>
+        <v>119.3124694824219</v>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
@@ -9948,10 +9948,10 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>121.2505416870117</v>
+        <v>121.3918609619141</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.01742813430558843</v>
+        <v>0.0174281153387621</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>121.2505416870117</v>
+        <v>121.3918609619141</v>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
@@ -9984,10 +9984,10 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>132.5528717041016</v>
+        <v>132.7073822021484</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>0.09321467648585813</v>
+        <v>0.09321482635301681</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>132.5528717041016</v>
+        <v>132.7073822021484</v>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
@@ -10020,10 +10020,10 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>138.0343322753906</v>
+        <v>138.1952056884766</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.04135301258146518</v>
+        <v>0.04135281244542011</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>138.0343322753906</v>
+        <v>138.1952056884766</v>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
@@ -10056,10 +10056,10 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>134.0897369384766</v>
+        <v>134.2460174560547</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>-0.02857691468412549</v>
+        <v>-0.02857688306006967</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>134.0897369384766</v>
+        <v>134.2460174560547</v>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
@@ -10092,10 +10092,10 @@
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>119.8909454345703</v>
+        <v>120.0306701660156</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>-0.1058902182082808</v>
+        <v>-0.1058902719009333</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>119.8909454345703</v>
+        <v>120.0306701660156</v>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
@@ -10128,10 +10128,10 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>124.7337112426758</v>
+        <v>124.8790817260742</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.04039309049196182</v>
+        <v>0.0403931058066469</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>124.7337112426758</v>
+        <v>124.8790817260742</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
@@ -10164,10 +10164,10 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>108.2283172607422</v>
+        <v>108.3544616699219</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>-0.1323250452303268</v>
+        <v>-0.1323249644996555</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>108.2283172607422</v>
+        <v>108.3544616699219</v>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
@@ -10200,10 +10200,10 @@
         </is>
       </c>
       <c r="F101" s="3" t="n">
-        <v>108.7675628662109</v>
+        <v>108.8943328857422</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0.004982481656530036</v>
+        <v>0.004982454875415376</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>108.7675628662109</v>
+        <v>108.8943328857422</v>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
@@ -10236,10 +10236,10 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>134.9409027099609</v>
+        <v>135.0981750488281</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>0.2406355273027898</v>
+        <v>0.2406354992833322</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -10264,7 +10264,7 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>134.9409027099609</v>
+        <v>135.0981750488281</v>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
@@ -10272,10 +10272,10 @@
         </is>
       </c>
       <c r="F103" s="3" t="n">
-        <v>157.7798614501953</v>
+        <v>157.9637603759766</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0.1692515633256428</v>
+        <v>0.1692516225247618</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>157.7798614501953</v>
+        <v>157.9637603759766</v>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
@@ -10308,10 +10308,10 @@
         </is>
       </c>
       <c r="F104" s="3" t="n">
-        <v>177.6334075927734</v>
+        <v>177.8404388427734</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>0.1258306729394936</v>
+        <v>0.1258306235524371</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>177.6334075927734</v>
+        <v>177.8404388427734</v>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
@@ -10344,10 +10344,10 @@
         </is>
       </c>
       <c r="F105" s="3" t="n">
-        <v>173.9483032226562</v>
+        <v>174.1510467529297</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>-0.02074555918313137</v>
+        <v>-0.02074551836382665</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>173.9483032226562</v>
+        <v>174.1510467529297</v>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
@@ -10380,10 +10380,10 @@
         </is>
       </c>
       <c r="F106" s="3" t="n">
-        <v>186.3423309326172</v>
+        <v>186.5595092773438</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.07125121360969189</v>
+        <v>0.07125115097366086</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>186.3423309326172</v>
+        <v>186.5595092773438</v>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
@@ -10416,10 +10416,10 @@
         </is>
       </c>
       <c r="F107" s="3" t="n">
-        <v>202.2320709228516</v>
+        <v>202.4677734375</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0.0852717678839181</v>
+        <v>0.08527179462348733</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>202.2320709228516</v>
+        <v>202.4677734375</v>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
@@ -10452,10 +10452,10 @@
         </is>
       </c>
       <c r="F108" s="3" t="n">
-        <v>176.7745361328125</v>
+        <v>176.9805603027344</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>-0.125882777513319</v>
+        <v>-0.1258828143464189</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>176.7745361328125</v>
+        <v>176.9805603027344</v>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
@@ -10488,10 +10488,10 @@
         </is>
       </c>
       <c r="F109" s="3" t="n">
-        <v>186.2728118896484</v>
+        <v>186.4899139404297</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>0.05373101785259271</v>
+        <v>0.0537310630129606</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>186.2728118896484</v>
+        <v>186.4899139404297</v>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
@@ -10524,10 +10524,10 @@
         </is>
       </c>
       <c r="F110" s="3" t="n">
-        <v>190.8971710205078</v>
+        <v>191.1196594238281</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0.02482573320254033</v>
+        <v>0.02482571515839349</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>190.8971710205078</v>
+        <v>191.1196594238281</v>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
@@ -10560,10 +10560,10 @@
         </is>
       </c>
       <c r="F111" s="3" t="n">
-        <v>176.9741516113281</v>
+        <v>177.180419921875</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>-0.07293465552553402</v>
+        <v>-0.07293461878268304</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>176.9741516113281</v>
+        <v>177.180419921875</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
@@ -10596,10 +10596,10 @@
         </is>
       </c>
       <c r="F112" s="3" t="n">
-        <v>174.1969757080078</v>
+        <v>174.3999938964844</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>-0.0156925510196515</v>
+        <v>-0.01569262578007558</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>174.1969757080078</v>
+        <v>174.3999938964844</v>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
@@ -10632,10 +10632,10 @@
         </is>
       </c>
       <c r="F113" s="3" t="n">
-        <v>199.3376770019531</v>
+        <v>199.5700073242188</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>0.1443234085538123</v>
+        <v>0.1443234765402235</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>199.3376770019531</v>
+        <v>199.5700073242188</v>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
@@ -10668,10 +10668,10 @@
         </is>
       </c>
       <c r="F114" s="3" t="n">
-        <v>210.8942108154297</v>
+        <v>211.1399993896484</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0.05797465881657349</v>
+        <v>0.05797460360179896</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -10808,13 +10808,13 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>5.797465881657349</v>
+        <v>5.797460360179896</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>5.797465881657349</v>
+        <v>5.797460360179896</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>5.797465881657349</v>
+        <v>5.797460360179896</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
@@ -11135,7 +11135,7 @@
         <v>3.495221238938055</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4.846929659457994</v>
+        <v>4.846929974563877</v>
       </c>
     </row>
     <row r="3">
@@ -11148,7 +11148,7 @@
         <v>3.422856966733567</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3.957808638228077</v>
+        <v>3.957808484702019</v>
       </c>
     </row>
     <row r="4">
@@ -11187,7 +11187,7 @@
         <v>3.697222222222224</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>12.37045427921837</v>
+        <v>12.37045679568402</v>
       </c>
     </row>
     <row r="7">
@@ -11200,7 +11200,7 @@
         <v>-0.8680000000000002</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-8.883502771604682</v>
+        <v>-8.883506473980374</v>
       </c>
     </row>
     <row r="8">
@@ -11213,7 +11213,7 @@
         <v>21.97</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>38.5445684357997</v>
+        <v>38.54459229054199</v>
       </c>
     </row>
     <row r="9">
@@ -11226,7 +11226,7 @@
         <v>-2.2</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>-32.02739460758143</v>
+        <v>-32.02740473135195</v>
       </c>
     </row>
     <row r="10">
@@ -11239,7 +11239,7 @@
         <v>3.495221238938055</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4.846929659457994</v>
+        <v>4.846929974563877</v>
       </c>
     </row>
     <row r="11">
@@ -11252,7 +11252,7 @@
         <v>4.010102220229272</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>13.535019476222</v>
+        <v>13.53502286281013</v>
       </c>
     </row>
     <row r="12">
@@ -11265,7 +11265,7 @@
         <v>2.649552522801262</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.04632325911844539</v>
+        <v>-0.04632348391823537</v>
       </c>
     </row>
     <row r="13">
@@ -11278,7 +11278,7 @@
         <v>8.518273050774795</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.1272024714396536</v>
+        <v>0.1272020743932543</v>
       </c>
     </row>
     <row r="14">
@@ -11291,7 +11291,7 @@
         <v>0.8716040257792284</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.3581028950843376</v>
+        <v>0.3581028287644549</v>
       </c>
     </row>
     <row r="15">
@@ -11304,7 +11304,7 @@
         <v>14.35776078315886</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.6804804586081132</v>
+        <v>0.6804802884945013</v>
       </c>
     </row>
     <row r="16">
@@ -11317,7 +11317,7 @@
         <v>92.0046082949309</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.541348794502089</v>
+        <v>2.541348252319989</v>
       </c>
     </row>
   </sheetData>

--- a/Project_1_May2026_Update.xlsx
+++ b/Project_1_May2026_Update.xlsx
@@ -1,34 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Source_and_Method" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="LSQ_Returns" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SP500TR_Returns" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="NVIDIA_Returns" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Verification" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Updated_Table_2" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Updated_Table_4" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Regression" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Serial_Correlation" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Newey_West" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_and_Method" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LSQ_Returns" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP500TR_Returns" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NVIDIA_Returns" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Updated_Table_2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Updated_Table_4" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regression" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Serial_Correlation" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Newey_West" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MPPM" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Source_and_Method'!$A$1:$B$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'LSQ_Returns'!$A$1:$C$114</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SP500TR_Returns'!$A$1:$H$114</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NVIDIA_Returns'!$A$1:$H$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'LSQ_Returns'!$A$1:$C$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SP500TR_Returns'!$A$1:$H$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NVIDIA_Returns'!$A$1:$H$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Verification'!$A$1:$I$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Updated_Table_2'!$A$1:$C$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Updated_Table_4'!$A$1:$C$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Regression'!$A$1:$D$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Serial_Correlation'!$A$1:$E$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Newey_West'!$A$1:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'MPPM'!$A$1:$I$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -480,7 +482,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Project 1 May 2026 update</t>
+          <t>Project 1 update through Jun 2026</t>
         </is>
       </c>
     </row>
@@ -504,7 +506,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>data/LSQ_latest_spartan.pdf</t>
+          <t>data\LSQ_latest_spartan.pdf</t>
         </is>
       </c>
     </row>
@@ -516,7 +518,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10T15:31:37</t>
+          <t>2026-07-20T12:35:47</t>
         </is>
       </c>
     </row>
@@ -574,9 +576,9 @@
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -618,19 +620,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.495221238938055</v>
+        <v>3.520614035087721</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.3772386842921072</v>
+        <v>0.3747761591438624</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9.265277884999726</v>
+        <v>9.393911403356611</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.5317281488808968</v>
+        <v>0.5288328374812032</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>6.573323692368519</v>
+        <v>6.657328716303208</v>
       </c>
     </row>
     <row r="3">
@@ -640,19 +642,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3.525269540287813</v>
+        <v>3.553834897000299</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.3947853253499741</v>
+        <v>0.3917940053800512</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>8.929586065952908</v>
+        <v>9.070671955669612</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.5895925187557978</v>
+        <v>0.5847909478065225</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>5.979162604924332</v>
+        <v>6.077103126049211</v>
       </c>
     </row>
     <row r="4">
@@ -662,23 +664,195 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.02263441138176098</v>
+        <v>-0.02540694158567561</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.0837408984724622</v>
+        <v>0.08345823680342875</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-0.2702910023016316</v>
+        <v>-0.3044270111471107</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.1067711854776375</v>
+        <v>0.1060104541983708</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-0.2119898854780591</v>
+        <v>-0.2396644913730222</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="33" customWidth="1" min="7" max="7"/>
+    <col width="39" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Series</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Paper Reported MPPM Percent</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Recomputed 113-Month MPPM Percent</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Current Observations</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Current Through</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Current Monthly Log CE Decimal</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Current Annualized MPPM Percent</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Current Minus Paper Percentage Points</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Rho</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Fund X</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>35.16</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>46.57265489959113</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>0.03262752823095071</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>47.0023852738126</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>11.8423852738126</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;P 500 TR</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>12.80668196833166</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0.009916832011085525</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>12.57120795593889</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>4.201207955938891</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>21.19</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>27.82294822884488</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0.01997540833046796</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>26.78749234118261</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>5.597492341182605</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -689,7 +863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C114"/>
+  <dimension ref="A1:C115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2409,8 +2583,23 @@
         <v>0.0764</v>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0.0639</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C114"/>
+  <autoFilter ref="A1:C115"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2421,7 +2610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H114"/>
+  <dimension ref="A1:H115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2508,7 +2697,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -2544,7 +2733,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2769,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2805,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -2652,7 +2841,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2877,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2913,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2949,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2985,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -2832,7 +3021,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -2868,7 +3057,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -2904,7 +3093,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -2940,7 +3129,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -2976,7 +3165,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3201,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3237,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3273,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3309,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3345,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3381,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3228,7 +3417,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3453,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3489,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3525,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3561,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3597,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3633,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3669,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3705,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3552,7 +3741,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3777,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3813,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3849,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3885,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3732,7 +3921,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3957,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3993,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3840,7 +4029,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3876,7 +4065,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3912,7 +4101,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3948,7 +4137,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3984,7 +4173,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4209,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4245,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4281,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4317,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4353,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4389,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4425,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4461,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4308,7 +4497,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4533,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4380,7 +4569,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4605,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4452,7 +4641,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4677,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4713,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4749,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4785,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4632,7 +4821,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4857,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4704,7 +4893,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4929,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4965,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4812,7 +5001,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4848,7 +5037,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4884,7 +5073,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4920,7 +5109,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4956,7 +5145,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4992,7 +5181,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5217,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5253,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5100,7 +5289,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5136,7 +5325,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5361,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5208,7 +5397,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5433,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5469,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5505,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5352,7 +5541,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5577,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5613,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5460,7 +5649,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5685,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5721,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5568,7 +5757,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5793,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5829,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5676,7 +5865,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5712,7 +5901,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5937,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5973,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5820,7 +6009,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5856,7 +6045,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5892,7 +6081,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5928,7 +6117,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5964,7 +6153,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6189,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6225,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6072,7 +6261,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6108,7 +6297,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6333,7 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6180,7 +6369,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6216,7 +6405,7 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6252,7 +6441,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6477,7 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6324,7 +6513,7 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6549,7 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6396,7 +6585,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6621,7 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6657,7 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6693,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6540,12 +6729,48 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>16935.349609375</v>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>16774.0703125</v>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>-0.009523233980697987</v>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H114"/>
+  <autoFilter ref="A1:H115"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6556,7 +6781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H114"/>
+  <dimension ref="A1:H115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6628,7 +6853,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2.628551244735718</v>
+        <v>2.625491857528687</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -6636,14 +6861,14 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.68863844871521</v>
+        <v>2.685507774353027</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.02285943791274025</v>
+        <v>0.0228589232346097</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6664,7 +6889,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2.68863844871521</v>
+        <v>2.685507774353027</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -6672,14 +6897,14 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2.50217342376709</v>
+        <v>2.499260902404785</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-0.06935295634012228</v>
+        <v>-0.06935257224980906</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6925,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.50217342376709</v>
+        <v>2.499260902404785</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -6708,14 +6933,14 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2.685867547988892</v>
+        <v>2.682740211486816</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.07341382594706225</v>
+        <v>0.07341342750790347</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6736,7 +6961,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2.685867547988892</v>
+        <v>2.682740211486816</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -6744,14 +6969,14 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2.571706056594849</v>
+        <v>2.568711996078491</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-0.04250451273352041</v>
+        <v>-0.04250438224323216</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6772,7 +6997,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2.571706056594849</v>
+        <v>2.568711996078491</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -6780,14 +7005,14 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>3.562959671020508</v>
+        <v>3.558811664581299</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.3854459229054199</v>
+        <v>0.3854459628071725</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6808,7 +7033,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3.562959671020508</v>
+        <v>3.558811664581299</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -6816,14 +7041,14 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3.568142890930176</v>
+        <v>3.563989877700806</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.001454751214790884</v>
+        <v>0.001455039942417358</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6844,7 +7069,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>3.568142890930176</v>
+        <v>3.563989877700806</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -6852,14 +7077,14 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>4.011197566986084</v>
+        <v>4.006530284881592</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.124169544101528</v>
+        <v>0.1241699394124758</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6880,7 +7105,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>4.011197566986084</v>
+        <v>4.006530284881592</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -6888,14 +7113,14 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>4.185932159423828</v>
+        <v>4.181059837341309</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.0435617018408383</v>
+        <v>0.04356127123718334</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6916,7 +7141,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>4.185932159423828</v>
+        <v>4.181059837341309</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -6924,14 +7149,14 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>4.416426658630371</v>
+        <v>4.411284923553467</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.05506407902183241</v>
+        <v>0.05506381041381037</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6952,7 +7177,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4.416426658630371</v>
+        <v>4.411284923553467</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -6960,14 +7185,14 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>5.109140396118164</v>
+        <v>5.103193759918213</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.1568493696446027</v>
+        <v>0.1568497270875411</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6988,7 +7213,7 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>5.109140396118164</v>
+        <v>5.103193759918213</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
@@ -6996,14 +7221,14 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>4.961888313293457</v>
+        <v>4.956112861633301</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-0.02882130288229823</v>
+        <v>-0.02882134310480688</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7024,7 +7249,7 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>4.961888313293457</v>
+        <v>4.956112861633301</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -7032,14 +7257,14 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>4.783644199371338</v>
+        <v>4.778075695037842</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0.03592263724368461</v>
+        <v>-0.03592274259403894</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7285,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4.783644199371338</v>
+        <v>4.778075695037842</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -7068,14 +7293,14 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>6.076587677001953</v>
+        <v>6.069513320922852</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.2702842067143147</v>
+        <v>0.2702840449401422</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7321,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>6.076587677001953</v>
+        <v>6.069513320922852</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -7104,14 +7329,14 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>5.986364841461182</v>
+        <v>5.979395389556885</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-0.0148476151972986</v>
+        <v>-0.01484763713349335</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7132,7 +7357,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5.986364841461182</v>
+        <v>5.979395389556885</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -7140,14 +7365,14 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>5.728850841522217</v>
+        <v>5.722182273864746</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.04301675670607963</v>
+        <v>-0.04301657591357244</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7168,7 +7393,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>5.728850841522217</v>
+        <v>5.722182273864746</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -7176,14 +7401,14 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5.563360691070557</v>
+        <v>5.556882858276367</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.02888714596166508</v>
+        <v>-0.02888747818176995</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7429,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>5.563360691070557</v>
+        <v>5.556882858276367</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -7212,14 +7437,14 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>6.242292404174805</v>
+        <v>6.235024929046631</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.1220362566450102</v>
+        <v>0.1220364164704759</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7465,7 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>6.242292404174805</v>
+        <v>6.235024929046631</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
@@ -7248,14 +7473,14 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5.863829135894775</v>
+        <v>5.857002735137939</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>-0.06062889140324723</v>
+        <v>-0.06062881836247813</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7276,7 +7501,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5.863829135894775</v>
+        <v>5.857002735137939</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -7284,14 +7509,14 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>6.060858249664307</v>
+        <v>6.053802967071533</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.03360075970894849</v>
+        <v>0.03360084344043912</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7312,7 +7537,7 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6.060858249664307</v>
+        <v>6.053802967071533</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
@@ -7320,14 +7545,14 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>6.951286315917969</v>
+        <v>6.943196773529053</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.1469145176432696</v>
+        <v>0.1469148915640635</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7348,7 +7573,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.951286315917969</v>
+        <v>6.943196773529053</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
@@ -7356,14 +7581,14 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>6.959707736968994</v>
+        <v>6.95160436630249</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.001211491034650791</v>
+        <v>0.001210910917214925</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7609,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>6.959707736968994</v>
+        <v>6.95160436630249</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -7392,14 +7617,14 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>5.221388339996338</v>
+        <v>5.215312957763672</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-0.2497690223023227</v>
+        <v>-0.2497684443831978</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7645,7 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>5.221388339996338</v>
+        <v>5.215312957763672</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
@@ -7428,14 +7653,14 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>4.05153751373291</v>
+        <v>4.046821117401123</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-0.2240497641790513</v>
+        <v>-0.2240501864079119</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7456,7 +7681,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>4.05153751373291</v>
+        <v>4.046821117401123</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
@@ -7464,14 +7689,14 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>3.309553384780884</v>
+        <v>3.305699586868286</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>-0.1831364331286653</v>
+        <v>-0.1831367162106703</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7717,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3.309553384780884</v>
+        <v>3.305699586868286</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
@@ -7500,14 +7725,14 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>3.56365704536438</v>
+        <v>3.559508562088013</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.07677883721471357</v>
+        <v>0.07677920166368679</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7528,7 +7753,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.56365704536438</v>
+        <v>3.559508562088013</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
@@ -7536,14 +7761,14 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.828147411346436</v>
+        <v>3.823691844940186</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.07421880461985131</v>
+        <v>0.07421903283671338</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7564,7 +7789,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>3.828147411346436</v>
+        <v>3.823691844940186</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
@@ -7572,14 +7797,14 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>4.455998420715332</v>
+        <v>4.450812339782715</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.1640090994165946</v>
+        <v>0.1640091618973911</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7600,7 +7825,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>4.455998420715332</v>
+        <v>4.450812339782715</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
@@ -7608,14 +7833,14 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.491733074188232</v>
+        <v>4.486504554748535</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.008019449312812732</v>
+        <v>0.008019258562485865</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7636,7 +7861,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>4.491733074188232</v>
+        <v>4.486504554748535</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
@@ -7644,14 +7869,14 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3.365440368652344</v>
+        <v>3.361522197723389</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-0.2507479155447004</v>
+        <v>-0.2507480697494133</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7672,7 +7897,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>3.365440368652344</v>
+        <v>3.361522197723389</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -7680,14 +7905,14 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>4.080217838287354</v>
+        <v>4.075467586517334</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.2123875009918048</v>
+        <v>0.2123875276734657</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7708,7 +7933,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>4.080217838287354</v>
+        <v>4.075467586517334</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -7716,14 +7941,14 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>4.191769123077393</v>
+        <v>4.186891078948975</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.02733954146841877</v>
+        <v>0.02734005118829974</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7969,7 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>4.191769123077393</v>
+        <v>4.186891078948975</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
@@ -7752,14 +7977,14 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>4.165826797485352</v>
+        <v>4.160977840423584</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>-0.006188872724219974</v>
+        <v>-0.006189136052685562</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7780,7 +8005,7 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>4.165826797485352</v>
+        <v>4.160977840423584</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
@@ -7788,14 +8013,14 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>4.328968524932861</v>
+        <v>4.323929786682129</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.03916190839858924</v>
+        <v>0.03916193560933667</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7816,7 +8041,7 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>4.328968524932861</v>
+        <v>4.323929786682129</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
@@ -7824,14 +8049,14 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>4.999191284179688</v>
+        <v>4.993370532989502</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.1548227378847067</v>
+        <v>0.1548222980792326</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7852,7 +8077,7 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>4.999191284179688</v>
+        <v>4.993370532989502</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
@@ -7860,14 +8085,14 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>5.394112586975098</v>
+        <v>5.387831687927246</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.07899703778992584</v>
+        <v>0.0789969725522417</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7888,7 +8113,7 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>5.394112586975098</v>
+        <v>5.387831687927246</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
@@ -7896,14 +8121,14 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>5.856024265289307</v>
+        <v>5.849206447601318</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.08563256158752863</v>
+        <v>0.08563273435357965</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7924,7 +8149,7 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>5.856024265289307</v>
+        <v>5.849206447601318</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
@@ -7932,14 +8157,14 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>5.88414478302002</v>
+        <v>5.87729549407959</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.004801981080815088</v>
+        <v>0.00480219782459379</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7960,7 +8185,7 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>5.88414478302002</v>
+        <v>5.87729549407959</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
@@ -7968,14 +8193,14 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>6.725380897521973</v>
+        <v>6.717551231384277</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.1429665899672494</v>
+        <v>0.1429663929865543</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7996,7 +8221,7 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>6.725380897521973</v>
+        <v>6.717551231384277</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -8004,14 +8229,14 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>6.564263343811035</v>
+        <v>6.556621551513672</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>-0.02395664367059158</v>
+        <v>-0.02395659881516721</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8032,7 +8257,7 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6.564263343811035</v>
+        <v>6.556621551513672</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -8040,14 +8265,14 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>7.278463363647461</v>
+        <v>7.269989013671875</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.1088012443178095</v>
+        <v>0.1088010733200719</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8068,7 +8293,7 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>7.278463363647461</v>
+        <v>7.269989013671875</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -8076,14 +8301,14 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>8.840836524963379</v>
+        <v>8.830546379089355</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.214657007015965</v>
+        <v>0.2146574585577379</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8104,7 +8329,7 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>8.840836524963379</v>
+        <v>8.830546379089355</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -8112,14 +8337,14 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>9.464973449707031</v>
+        <v>9.45395565032959</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.07059704395407729</v>
+        <v>0.07059690810485542</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8140,7 +8365,7 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>9.464973449707031</v>
+        <v>9.45395565032959</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -8148,14 +8373,14 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>10.57811832427979</v>
+        <v>10.5658016204834</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.1176067614439225</v>
+        <v>0.1176064296551937</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8176,7 +8401,7 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>10.57811832427979</v>
+        <v>10.5658016204834</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -8184,14 +8409,14 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>13.32834720611572</v>
+        <v>13.31282997131348</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2599922592587551</v>
+        <v>0.2599924217301743</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8212,7 +8437,7 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>13.32834720611572</v>
+        <v>13.31282997131348</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -8220,14 +8445,14 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>13.48784160614014</v>
+        <v>13.47214126586914</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.01196655500925359</v>
+        <v>0.01196674898567385</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8473,7 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>13.48784160614014</v>
+        <v>13.47214126586914</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -8256,14 +8481,14 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>12.49448299407959</v>
+        <v>12.47993946075439</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>-0.0736484488080239</v>
+        <v>-0.07364841160242508</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8509,7 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>12.49448299407959</v>
+        <v>12.47993946075439</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -8292,14 +8517,14 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>13.35924911499023</v>
+        <v>13.34369659423828</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.06921183704202938</v>
+        <v>0.06921164451158912</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8320,7 +8545,7 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>13.35924911499023</v>
+        <v>13.34369659423828</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -8328,14 +8553,14 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>13.01768684387207</v>
+        <v>13.00253200531006</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>-0.0255674752509033</v>
+        <v>-0.02556747199089759</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8581,7 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>13.01768684387207</v>
+        <v>13.00253200531006</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -8364,14 +8589,14 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>12.95262145996094</v>
+        <v>12.93754100799561</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>-0.00499822930843985</v>
+        <v>-0.004998333962024648</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8617,7 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>12.95262145996094</v>
+        <v>12.93754100799561</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -8400,14 +8625,14 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>13.67529964447021</v>
+        <v>13.65938282012939</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.05579397087633686</v>
+        <v>0.05579435935218902</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8428,7 +8653,7 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>13.67529964447021</v>
+        <v>13.65938282012939</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -8436,14 +8661,14 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>13.31469058990479</v>
+        <v>13.29919052124023</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>-0.02636937134399442</v>
+        <v>-0.02636958811626222</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8464,7 +8689,7 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>13.31469058990479</v>
+        <v>13.29919052124023</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -8472,14 +8697,14 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>14.97176265716553</v>
+        <v>14.95433521270752</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.1244544179282046</v>
+        <v>0.1244545439682092</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8725,7 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>14.97176265716553</v>
+        <v>14.95433521270752</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -8508,14 +8733,14 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>16.20365524291992</v>
+        <v>16.18479537963867</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.08228106562755366</v>
+        <v>0.08228116793085949</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8536,7 +8761,7 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>16.20365524291992</v>
+        <v>16.18479537963867</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -8544,14 +8769,14 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>19.95678520202637</v>
+        <v>19.93355178833008</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2316224273375818</v>
+        <v>0.2316221070924096</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8572,7 +8797,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>19.95678520202637</v>
+        <v>19.93355178833008</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -8580,14 +8805,14 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>19.45443153381348</v>
+        <v>19.43178749084473</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>-0.02517207371465235</v>
+        <v>-0.02517184608209688</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8608,7 +8833,7 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>19.45443153381348</v>
+        <v>19.43178749084473</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -8616,14 +8841,14 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>22.33777809143066</v>
+        <v>22.31176948547363</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.1482102703749366</v>
+        <v>0.1482098338089488</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8644,7 +8869,7 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>22.33777809143066</v>
+        <v>22.31176948547363</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -8652,14 +8877,14 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>20.67229652404785</v>
+        <v>20.64822959899902</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>-0.07455896287293373</v>
+        <v>-0.07455885054556877</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8905,7 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>20.67229652404785</v>
+        <v>20.64822959899902</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
@@ -8688,14 +8913,14 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>25.51306533813477</v>
+        <v>25.48336601257324</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.2341669590727717</v>
+        <v>0.2341671178340934</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8716,7 +8941,7 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>25.51306533813477</v>
+        <v>25.48336601257324</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
@@ -8724,14 +8949,14 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>32.60707092285156</v>
+        <v>32.56910705566406</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.2780538320541703</v>
+        <v>0.2780535757950808</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8752,7 +8977,7 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>32.60707092285156</v>
+        <v>32.56910705566406</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
@@ -8760,14 +8985,14 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>29.35254859924316</v>
+        <v>29.31838035583496</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>-0.09981032430998205</v>
+        <v>-0.09981012664158295</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8788,7 +9013,7 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>29.35254859924316</v>
+        <v>29.31838035583496</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
@@ -8796,14 +9021,14 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>24.43733787536621</v>
+        <v>24.40889167785645</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>-0.1674543083459433</v>
+        <v>-0.1674542938045153</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8824,7 +9049,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>24.43733787536621</v>
+        <v>24.40889167785645</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -8832,14 +9057,14 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>24.33654022216797</v>
+        <v>24.30820655822754</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>-0.004124739515913078</v>
+        <v>-0.004124936148585889</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8860,7 +9085,7 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>24.33654022216797</v>
+        <v>24.30820655822754</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
@@ -8868,14 +9093,14 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>27.23641204833984</v>
+        <v>27.2047061920166</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1191571110642262</v>
+        <v>0.1191572741843718</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8896,7 +9121,7 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>27.23641204833984</v>
+        <v>27.2047061920166</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
@@ -8904,14 +9129,14 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>18.51329612731934</v>
+        <v>18.49174118041992</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>-0.3202740473135195</v>
+        <v>-0.3202741816102964</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8932,7 +9157,7 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>18.51329612731934</v>
+        <v>18.49174118041992</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
@@ -8940,14 +9165,14 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>18.63806915283203</v>
+        <v>18.61637306213379</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.006739644018796564</v>
+        <v>0.006739867300643132</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8968,7 +9193,7 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>18.63806915283203</v>
+        <v>18.61637306213379</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
@@ -8976,14 +9201,14 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>15.13465309143066</v>
+        <v>15.11703300476074</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>-0.1879709766432016</v>
+        <v>-0.1879710965016489</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9004,7 +9229,7 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>15.13465309143066</v>
+        <v>15.11703300476074</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
@@ -9012,14 +9237,14 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>18.13382720947266</v>
+        <v>18.11271858215332</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1981660299660348</v>
+        <v>0.1981662391323191</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9040,7 +9265,7 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>18.13382720947266</v>
+        <v>18.11271858215332</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
@@ -9048,14 +9273,14 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>15.0697546005249</v>
+        <v>15.05220985412598</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>-0.1689699903695542</v>
+        <v>-0.168970147366111</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9076,7 +9301,7 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>15.0697546005249</v>
+        <v>15.05220985412598</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
@@ -9084,14 +9309,14 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>12.12310409545898</v>
+        <v>12.10898780822754</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>-0.1955340735915687</v>
+        <v>-0.195534215535247</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9112,7 +9337,7 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>12.12310409545898</v>
+        <v>12.10898780822754</v>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
@@ -9120,14 +9345,14 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>13.47932434082031</v>
+        <v>13.46363067626953</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1118707085810915</v>
+        <v>0.1118708590260178</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9148,7 +9373,7 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>13.47932434082031</v>
+        <v>13.46363067626953</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
@@ -9156,14 +9381,14 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>16.90515899658203</v>
+        <v>16.8854808807373</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.2541547757988909</v>
+        <v>0.2541550854108761</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9184,7 +9409,7 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>16.90515899658203</v>
+        <v>16.8854808807373</v>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
@@ -9192,14 +9417,14 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>14.59859466552734</v>
+        <v>14.58159923553467</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>-0.1364414455682458</v>
+        <v>-0.1364415773216663</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9220,7 +9445,7 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>14.59859466552734</v>
+        <v>14.58159923553467</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
@@ -9228,14 +9453,14 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>19.51640510559082</v>
+        <v>19.49368858337402</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.3368687570781206</v>
+        <v>0.3368690408023851</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9256,7 +9481,7 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>19.51640510559082</v>
+        <v>19.49368858337402</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -9264,14 +9489,14 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>23.19152641296387</v>
+        <v>23.16452598571777</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1883093370674214</v>
+        <v>0.1883090204628883</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9292,7 +9517,7 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>23.19152641296387</v>
+        <v>23.16452598571777</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -9300,14 +9525,14 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>27.75243186950684</v>
+        <v>27.72012519836426</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1966625816398813</v>
+        <v>0.1966627426546637</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9328,7 +9553,7 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>27.75243186950684</v>
+        <v>27.72012519836426</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
@@ -9336,14 +9561,14 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>27.72445487976074</v>
+        <v>27.69218635559082</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>-0.001008091466637717</v>
+        <v>-0.001007890208774564</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9364,7 +9589,7 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>27.72445487976074</v>
+        <v>27.69218635559082</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
@@ -9372,14 +9597,14 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>37.80053329467773</v>
+        <v>37.75652694702148</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.3634364844544762</v>
+        <v>0.3634361137902264</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9625,7 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>37.80053329467773</v>
+        <v>37.75652694702148</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
@@ -9408,14 +9633,14 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>42.26895141601562</v>
+        <v>42.21975326538086</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.118210451860663</v>
+        <v>0.1182107222049846</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9436,7 +9661,7 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>42.26895141601562</v>
+        <v>42.21975326538086</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
@@ -9444,14 +9669,14 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>46.69250106811523</v>
+        <v>46.63814544677734</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.1046524577475925</v>
+        <v>0.1046522501830784</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9472,7 +9697,7 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>46.69250106811523</v>
+        <v>46.63814544677734</v>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
@@ -9480,14 +9705,14 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>49.31644821166992</v>
+        <v>49.25904083251953</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.05619632882219916</v>
+        <v>0.05619638947121319</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9508,7 +9733,7 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>49.31644821166992</v>
+        <v>49.25904083251953</v>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
@@ -9516,14 +9741,14 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>43.46859741210938</v>
+        <v>43.41800308227539</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>-0.1185781014573704</v>
+        <v>-0.1185779838893664</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9544,7 +9769,7 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>43.46859741210938</v>
+        <v>43.41800308227539</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
@@ -9552,14 +9777,14 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>40.75150299072266</v>
+        <v>40.70405960083008</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>-0.06250706448213572</v>
+        <v>-0.06250733080244375</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9580,7 +9805,7 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>40.75150299072266</v>
+        <v>40.70405960083008</v>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
@@ -9588,14 +9813,14 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>46.73731994628906</v>
+        <v>46.68291473388672</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.146885796014177</v>
+        <v>0.1468859664536928</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9616,7 +9841,7 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>46.73731994628906</v>
+        <v>46.68291473388672</v>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
@@ -9624,14 +9849,14 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>49.49174499511719</v>
+        <v>49.43412399291992</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.05893416764148074</v>
+        <v>0.05893396491449421</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9652,7 +9877,7 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>49.49174499511719</v>
+        <v>49.43412399291992</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
@@ -9660,14 +9885,14 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>61.48941421508789</v>
+        <v>61.41783142089844</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.2424175834001081</v>
+        <v>0.2424177159424299</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9688,7 +9913,7 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>61.48941421508789</v>
+        <v>61.41783142089844</v>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
@@ -9696,14 +9921,14 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>79.06366729736328</v>
+        <v>78.97163391113281</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.2858094081170013</v>
+        <v>0.2858095456014653</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9724,7 +9949,7 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>79.06366729736328</v>
+        <v>78.97163391113281</v>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
@@ -9732,14 +9957,14 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>90.30503845214844</v>
+        <v>90.19991302490234</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.1421812513768894</v>
+        <v>0.1421811675620739</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9760,7 +9985,7 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>90.30503845214844</v>
+        <v>90.19991302490234</v>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
@@ -9768,14 +9993,14 @@
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>86.35327911376953</v>
+        <v>86.25274658203125</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>-0.04376012021159703</v>
+        <v>-0.04376020231617472</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9796,7 +10021,7 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>86.35327911376953</v>
+        <v>86.25274658203125</v>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
@@ -9804,14 +10029,14 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>109.571174621582</v>
+        <v>109.4436187744141</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.2688710347319083</v>
+        <v>0.2688711155456016</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9832,7 +10057,7 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>109.571174621582</v>
+        <v>109.4436187744141</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
@@ -9840,14 +10065,14 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>123.4804611206055</v>
+        <v>123.3367233276367</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.1269429350106077</v>
+        <v>0.1269430297426406</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9868,7 +10093,7 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>123.4804611206055</v>
+        <v>123.3367233276367</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
@@ -9876,14 +10101,14 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>116.9635848999023</v>
+        <v>116.8274383544922</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>-0.0527765782664027</v>
+        <v>-0.05277653562964368</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9904,7 +10129,7 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>116.9635848999023</v>
+        <v>116.8274383544922</v>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
@@ -9912,14 +10137,14 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>119.3124694824219</v>
+        <v>119.173583984375</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.02008218698605813</v>
+        <v>0.02008214562373478</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9940,7 +10165,7 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>119.3124694824219</v>
+        <v>119.173583984375</v>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
@@ -9948,14 +10173,14 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>121.3918609619141</v>
+        <v>121.2505493164062</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.0174281153387621</v>
+        <v>0.0174280680549439</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9976,7 +10201,7 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>121.3918609619141</v>
+        <v>121.2505493164062</v>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
@@ -9984,14 +10209,14 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>132.7073822021484</v>
+        <v>132.5528564453125</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>0.09321482635301681</v>
+        <v>0.09321448185288306</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10012,7 +10237,7 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>132.7073822021484</v>
+        <v>132.5528564453125</v>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
@@ -10020,14 +10245,14 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>138.1952056884766</v>
+        <v>138.0343170166016</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.04135281244542011</v>
+        <v>0.04135301734180707</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10048,7 +10273,7 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>138.1952056884766</v>
+        <v>138.0343170166016</v>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
@@ -10056,14 +10281,14 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>134.2460174560547</v>
+        <v>134.0897369384766</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>-0.02857688306006967</v>
+        <v>-0.02857680729967016</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10084,7 +10309,7 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>134.2460174560547</v>
+        <v>134.0897369384766</v>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
@@ -10092,14 +10317,14 @@
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>120.0306701660156</v>
+        <v>119.8909378051758</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>-0.1058902719009333</v>
+        <v>-0.1058902751059577</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10120,7 +10345,7 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>120.0306701660156</v>
+        <v>119.8909378051758</v>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
@@ -10128,14 +10353,14 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>124.8790817260742</v>
+        <v>124.7337036132812</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.0403931058066469</v>
+        <v>0.04039309306242167</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10381,7 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>124.8790817260742</v>
+        <v>124.7337036132812</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
@@ -10164,14 +10389,14 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>108.3544616699219</v>
+        <v>108.2283248901367</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>-0.1323249644996555</v>
+        <v>-0.1323249309931265</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10417,7 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>108.3544616699219</v>
+        <v>108.2283248901367</v>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
@@ -10200,14 +10425,14 @@
         </is>
       </c>
       <c r="F101" s="3" t="n">
-        <v>108.8943328857422</v>
+        <v>108.7675628662109</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0.004982454875415376</v>
+        <v>0.004982410811787075</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10228,7 +10453,7 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>108.8943328857422</v>
+        <v>108.7675628662109</v>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
@@ -10236,14 +10461,14 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>135.0981750488281</v>
+        <v>134.9409027099609</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>0.2406354992833322</v>
+        <v>0.2406355273027898</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10489,7 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>135.0981750488281</v>
+        <v>134.9409027099609</v>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
@@ -10272,14 +10497,14 @@
         </is>
       </c>
       <c r="F103" s="3" t="n">
-        <v>157.9637603759766</v>
+        <v>157.7798614501953</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0.1692516225247618</v>
+        <v>0.1692515633256428</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10300,7 +10525,7 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>157.9637603759766</v>
+        <v>157.7798614501953</v>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
@@ -10308,14 +10533,14 @@
         </is>
       </c>
       <c r="F104" s="3" t="n">
-        <v>177.8404388427734</v>
+        <v>177.6334075927734</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>0.1258306235524371</v>
+        <v>0.1258306729394936</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10336,7 +10561,7 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>177.8404388427734</v>
+        <v>177.6334075927734</v>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
@@ -10344,14 +10569,14 @@
         </is>
       </c>
       <c r="F105" s="3" t="n">
-        <v>174.1510467529297</v>
+        <v>173.9483032226562</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>-0.02074551836382665</v>
+        <v>-0.02074555918313137</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10372,7 +10597,7 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>174.1510467529297</v>
+        <v>173.9483032226562</v>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
@@ -10380,14 +10605,14 @@
         </is>
       </c>
       <c r="F106" s="3" t="n">
-        <v>186.5595092773438</v>
+        <v>186.3423309326172</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.07125115097366086</v>
+        <v>0.07125121360969189</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10408,7 +10633,7 @@
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>186.5595092773438</v>
+        <v>186.3423309326172</v>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
@@ -10416,14 +10641,14 @@
         </is>
       </c>
       <c r="F107" s="3" t="n">
-        <v>202.4677734375</v>
+        <v>202.2320709228516</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0.08527179462348733</v>
+        <v>0.0852717678839181</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10444,7 +10669,7 @@
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>202.4677734375</v>
+        <v>202.2320709228516</v>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
@@ -10452,14 +10677,14 @@
         </is>
       </c>
       <c r="F108" s="3" t="n">
-        <v>176.9805603027344</v>
+        <v>176.7745361328125</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>-0.1258828143464189</v>
+        <v>-0.125882777513319</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10480,7 +10705,7 @@
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>176.9805603027344</v>
+        <v>176.7745361328125</v>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
@@ -10488,14 +10713,14 @@
         </is>
       </c>
       <c r="F109" s="3" t="n">
-        <v>186.4899139404297</v>
+        <v>186.2728118896484</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>0.0537310630129606</v>
+        <v>0.05373101785259271</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10516,7 +10741,7 @@
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>186.4899139404297</v>
+        <v>186.2728118896484</v>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
@@ -10524,14 +10749,14 @@
         </is>
       </c>
       <c r="F110" s="3" t="n">
-        <v>191.1196594238281</v>
+        <v>190.8971710205078</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0.02482571515839349</v>
+        <v>0.02482573320254033</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10552,7 +10777,7 @@
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>191.1196594238281</v>
+        <v>190.8971710205078</v>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
@@ -10560,14 +10785,14 @@
         </is>
       </c>
       <c r="F111" s="3" t="n">
-        <v>177.180419921875</v>
+        <v>176.9741516113281</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>-0.07293461878268304</v>
+        <v>-0.07293465552553402</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10588,7 +10813,7 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>177.180419921875</v>
+        <v>176.9741516113281</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
@@ -10596,14 +10821,14 @@
         </is>
       </c>
       <c r="F112" s="3" t="n">
-        <v>174.3999938964844</v>
+        <v>174.1969757080078</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>-0.01569262578007558</v>
+        <v>-0.0156925510196515</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10624,7 +10849,7 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>174.3999938964844</v>
+        <v>174.1969757080078</v>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
@@ -10632,14 +10857,14 @@
         </is>
       </c>
       <c r="F113" s="3" t="n">
-        <v>199.5700073242188</v>
+        <v>199.3376770019531</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>0.1443234765402235</v>
+        <v>0.1443234085538123</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10660,7 +10885,7 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>199.5700073242188</v>
+        <v>199.3376770019531</v>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
@@ -10668,19 +10893,55 @@
         </is>
       </c>
       <c r="F114" s="3" t="n">
-        <v>211.1399993896484</v>
+        <v>210.8942108154297</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0.05797460360179896</v>
+        <v>0.05797465881657349</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>210.8942108154297</v>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>200.0899963378906</v>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>-0.05123049341072095</v>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H114"/>
+  <autoFilter ref="A1:H115"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10765,17 +11026,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>5.263305489604209</v>
+        <v>-0.9523233980697987</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>5.263305489604209</v>
+        <v>-0.9523233980697987</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>5.263305489604209</v>
+        <v>-0.9523233980697987</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0</v>
@@ -10787,7 +11048,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10804,17 +11065,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>5.797460360179896</v>
+        <v>-5.123049341072095</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>5.797460360179896</v>
+        <v>-5.123049341072095</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>5.797460360179896</v>
+        <v>-5.123049341072095</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
@@ -10826,7 +11087,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1780617600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10847,7 +11108,7 @@
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10874,10 +11135,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.495221238938055</v>
+        <v>3.520614035087721</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1.327549492803307</v>
+        <v>1.307550607795648</v>
       </c>
     </row>
     <row r="3">
@@ -10887,10 +11148,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3.422856966733567</v>
+        <v>3.448521353622169</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1.224931146566699</v>
+        <v>1.205625872082727</v>
       </c>
     </row>
     <row r="4">
@@ -10900,10 +11161,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>95.57522123893806</v>
+        <v>95.6140350877193</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>70.79646017699115</v>
+        <v>70.17543859649122</v>
       </c>
     </row>
     <row r="5">
@@ -10913,10 +11174,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>4.424778761061947</v>
+        <v>4.385964912280701</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>29.20353982300885</v>
+        <v>29.82456140350877</v>
       </c>
     </row>
     <row r="6">
@@ -10926,7 +11187,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3.697222222222224</v>
+        <v>3.721926605504589</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>3.616317163875842</v>
@@ -10942,7 +11203,7 @@
         <v>-0.8680000000000002</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-4.220978194645264</v>
+        <v>-4.124841288863633</v>
       </c>
     </row>
     <row r="8">
@@ -10978,10 +11239,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3.495221238938055</v>
+        <v>3.520614035087721</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1.327549492803307</v>
+        <v>1.307550607795648</v>
       </c>
     </row>
     <row r="11">
@@ -10991,10 +11252,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>4.010102220229272</v>
+        <v>4.001514378174758</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>4.543739913577447</v>
+        <v>4.528627069815164</v>
       </c>
     </row>
     <row r="12">
@@ -11004,10 +11265,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2.649552522801262</v>
+        <v>2.626664430542024</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.4507028811013239</v>
+        <v>-0.438794641537164</v>
       </c>
     </row>
     <row r="13">
@@ -11017,10 +11278,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>8.518273050774795</v>
+        <v>8.443105350916397</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.5164587239200782</v>
+        <v>0.5239364253231313</v>
       </c>
     </row>
     <row r="14">
@@ -11030,10 +11291,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.8716040257792284</v>
+        <v>0.8798204135639283</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.2921711009110292</v>
+        <v>0.2887300251572749</v>
       </c>
     </row>
     <row r="15">
@@ -11043,10 +11304,10 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>14.35776078315886</v>
+        <v>14.52592048115421</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.4733519514863244</v>
+        <v>0.4680407905555371</v>
       </c>
     </row>
     <row r="16">
@@ -11056,10 +11317,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>92.0046082949309</v>
+        <v>93.47695852534564</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.07696630589219</v>
+        <v>2.062862778510679</v>
       </c>
     </row>
     <row r="17">
@@ -11069,7 +11330,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>3.525269540287813</v>
+        <v>3.553834897000299</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>0</v>
@@ -11082,7 +11343,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.02263441138176098</v>
+        <v>-0.02540694158567561</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>1</v>
@@ -11105,7 +11366,7 @@
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11132,10 +11393,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.495221238938055</v>
+        <v>3.520614035087721</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4.846929974563877</v>
+        <v>4.759474108721161</v>
       </c>
     </row>
     <row r="3">
@@ -11145,10 +11406,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3.422856966733567</v>
+        <v>3.448521353622169</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3.957808484702019</v>
+        <v>3.874489132034076</v>
       </c>
     </row>
     <row r="4">
@@ -11158,10 +11419,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>95.57522123893806</v>
+        <v>95.6140350877193</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>64.60176991150442</v>
+        <v>64.03508771929825</v>
       </c>
     </row>
     <row r="5">
@@ -11171,10 +11432,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>4.424778761061947</v>
+        <v>4.385964912280701</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>35.39823008849557</v>
+        <v>35.96491228070175</v>
       </c>
     </row>
     <row r="6">
@@ -11184,10 +11445,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3.697222222222224</v>
+        <v>3.721926605504589</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>12.37045679568402</v>
+        <v>12.3704578842066</v>
       </c>
     </row>
     <row r="7">
@@ -11200,7 +11461,7 @@
         <v>-0.8680000000000002</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-8.883506473980374</v>
+        <v>-8.791789686655342</v>
       </c>
     </row>
     <row r="8">
@@ -11213,7 +11474,7 @@
         <v>21.97</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>38.54459229054199</v>
+        <v>38.54459628071724</v>
       </c>
     </row>
     <row r="9">
@@ -11226,7 +11487,7 @@
         <v>-2.2</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>-32.02740473135195</v>
+        <v>-32.02741816102964</v>
       </c>
     </row>
     <row r="10">
@@ -11236,10 +11497,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3.495221238938055</v>
+        <v>3.520614035087721</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4.846929974563877</v>
+        <v>4.759474108721161</v>
       </c>
     </row>
     <row r="11">
@@ -11249,10 +11510,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>4.010102220229272</v>
+        <v>4.001514378174758</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>13.53502286281013</v>
+        <v>13.50731721943351</v>
       </c>
     </row>
     <row r="12">
@@ -11262,10 +11523,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2.649552522801262</v>
+        <v>2.626664430542024</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.04632348391823537</v>
+        <v>-0.03004063066969971</v>
       </c>
     </row>
     <row r="13">
@@ -11275,10 +11536,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>8.518273050774795</v>
+        <v>8.443105350916397</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.1272020743932543</v>
+        <v>0.1259009991169342</v>
       </c>
     </row>
     <row r="14">
@@ -11288,10 +11549,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.8716040257792284</v>
+        <v>0.8798204135639283</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.3581028287644549</v>
+        <v>0.3523626513985706</v>
       </c>
     </row>
     <row r="15">
@@ -11301,10 +11562,10 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>14.35776078315886</v>
+        <v>14.52592048115421</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.6804802884945013</v>
+        <v>0.6696209906580181</v>
       </c>
     </row>
     <row r="16">
@@ -11314,10 +11575,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>92.0046082949309</v>
+        <v>93.47695852534564</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.541348252319989</v>
+        <v>2.505229331977628</v>
       </c>
     </row>
   </sheetData>
@@ -11338,7 +11599,7 @@
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11370,13 +11631,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.525269540287813</v>
+        <v>3.553834897000299</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.3947853253499741</v>
+        <v>0.3917940053800512</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>8.929586065952908</v>
+        <v>9.070671955669612</v>
       </c>
     </row>
     <row r="3">
@@ -11386,13 +11647,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.02263441138176098</v>
+        <v>-0.02540694158567561</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.0837408984724622</v>
+        <v>0.08345823680342875</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>-0.2702910023016316</v>
+        <v>-0.3044270111471107</v>
       </c>
     </row>
   </sheetData>
@@ -11451,16 +11712,16 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.3470172364434945</v>
+        <v>0.3520359755657159</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.000185547850893166</v>
+        <v>0.000139934911654884</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>7.559406236993584e-05</v>
+        <v>6.230754539099949e-05</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.0001458329375608759</v>
+        <v>7.123636759103555e-05</v>
       </c>
     </row>
     <row r="3">
@@ -11470,16 +11731,16 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.1380651276989634</v>
+        <v>-0.1416351891195366</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.13696764466289</v>
+        <v>0.1254749098985961</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.5006736962768379</v>
+        <v>0.4456255431559045</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.3521077833512497</v>
+        <v>0.3138843342034664</v>
       </c>
     </row>
     <row r="4">
@@ -11489,16 +11750,16 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.01301373953790651</v>
+        <v>0.01316612202744002</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.8885190013988011</v>
+        <v>0.8867407299564685</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.9880414469195714</v>
+        <v>0.9769962252070046</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.8567336779209422</v>
+        <v>0.8757247539116003</v>
       </c>
     </row>
   </sheetData>

--- a/Project_1_May2026_Update.xlsx
+++ b/Project_1_May2026_Update.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_and_Method" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LSQ_Returns" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP500TR_Returns" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NVIDIA_Returns" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Updated_Table_2" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Updated_Table_4" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regression" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Serial_Correlation" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Newey_West" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MPPM" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Source_and_Method" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="LSQ_Returns" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SP500TR_Returns" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="NVIDIA_Returns" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Verification" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Updated_Table_2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Updated_Table_4" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Regression" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Serial_Correlation" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Newey_West" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="MPPM" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Source_and_Method'!$A$1:$B$8</definedName>
@@ -506,7 +506,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>data\LSQ_latest_spartan.pdf</t>
+          <t>data/LSQ_latest_spartan.pdf</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20T12:35:47</t>
+          <t>2026-07-25T14:28:05</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
         <v>21.19</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>27.82294822884488</v>
+        <v>27.82295583188716</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>114</v>
@@ -839,13 +839,13 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.01997540833046796</v>
+        <v>0.01997541333835227</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>26.78749234118261</v>
+        <v>26.78749981121109</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>5.597492341182605</v>
+        <v>5.59749981121109</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3</v>
@@ -6790,7 +6790,7 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2.625491857528687</v>
+        <v>2.625490665435791</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -6861,10 +6861,10 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.685507774353027</v>
+        <v>2.685508012771606</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.0228589232346097</v>
+        <v>0.02285947846851455</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2.685507774353027</v>
+        <v>2.685508012771606</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -6897,10 +6897,10 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2.499260902404785</v>
+        <v>2.499259471893311</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-0.06935257224980906</v>
+        <v>-0.06935318755056563</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.499260902404785</v>
+        <v>2.499259471893311</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>2.682740211486816</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.07341342750790347</v>
+        <v>0.07341404190198397</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -6969,10 +6969,10 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2.568711996078491</v>
+        <v>2.568711280822754</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-0.04250438224323216</v>
+        <v>-0.04250464885709748</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2.568711996078491</v>
+        <v>2.568711280822754</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -7005,10 +7005,10 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>3.558811664581299</v>
+        <v>3.558812141418457</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.3854459628071725</v>
+        <v>0.3854465342164011</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -7033,7 +7033,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3.558811664581299</v>
+        <v>3.558812141418457</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -7041,10 +7041,10 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3.563989877700806</v>
+        <v>3.563989400863647</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.001455039942417358</v>
+        <v>0.00145477177200104</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>3.563989877700806</v>
+        <v>3.563989400863647</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -7077,10 +7077,10 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>4.006530284881592</v>
+        <v>4.006529808044434</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.1241699394124758</v>
+        <v>0.1241699560255558</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>4.006530284881592</v>
+        <v>4.006529808044434</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -7113,10 +7113,10 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>4.181059837341309</v>
+        <v>4.18105936050415</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.04356127123718334</v>
+        <v>0.04356127642162821</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>4.181059837341309</v>
+        <v>4.18105936050415</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -7149,10 +7149,10 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>4.411284923553467</v>
+        <v>4.411284446716309</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.05506381041381037</v>
+        <v>0.055063816693671</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4.411284923553467</v>
+        <v>4.411284446716309</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>5.103193759918213</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.1568497270875411</v>
+        <v>0.1568498521370461</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -7257,10 +7257,10 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>4.778075695037842</v>
+        <v>4.778074264526367</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0.03592274259403894</v>
+        <v>-0.03592303122981355</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4.778075695037842</v>
+        <v>4.778074264526367</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -7293,10 +7293,10 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>6.069513320922852</v>
+        <v>6.069514274597168</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.2702840449401422</v>
+        <v>0.2702846248453648</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -7321,7 +7321,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>6.069513320922852</v>
+        <v>6.069514274597168</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>5.979395389556885</v>
+        <v>5.979394435882568</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-0.01484763713349335</v>
+        <v>-0.01484794905117526</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5.979395389556885</v>
+        <v>5.979394435882568</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>5.722182273864746</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.04301657591357244</v>
+        <v>-0.04301642328097344</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -7401,10 +7401,10 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5.556882858276367</v>
+        <v>5.556884288787842</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.02888747818176995</v>
+        <v>-0.02888722818772815</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>5.556882858276367</v>
+        <v>5.556884288787842</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -7437,10 +7437,10 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>6.235024929046631</v>
+        <v>6.235025405883789</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.1220364164704759</v>
+        <v>0.1220362134342508</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>6.235024929046631</v>
+        <v>6.235025405883789</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5.857002735137939</v>
+        <v>5.857003211975098</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>-0.06062881836247813</v>
+        <v>-0.06062881372575712</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5.857002735137939</v>
+        <v>5.857003211975098</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -7509,10 +7509,10 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>6.053802967071533</v>
+        <v>6.0538010597229</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.03360084344043912</v>
+        <v>0.03360043363907228</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6.053802967071533</v>
+        <v>6.0538010597229</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
@@ -7545,10 +7545,10 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>6.943196773529053</v>
+        <v>6.94319486618042</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.1469148915640635</v>
+        <v>0.1469149378519929</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>6.943196773529053</v>
+        <v>6.94319486618042</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
@@ -7581,10 +7581,10 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>6.95160436630249</v>
+        <v>6.951603889465332</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.001210910917214925</v>
+        <v>0.001211117280586649</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>6.95160436630249</v>
+        <v>6.951603889465332</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -7617,10 +7617,10 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>5.215312957763672</v>
+        <v>5.215310573577881</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-0.2497684443831978</v>
+        <v>-0.2497687358911059</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>5.215312957763672</v>
+        <v>5.215310573577881</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>4.046821117401123</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-0.2240501864079119</v>
+        <v>-0.2240498316814782</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -7689,10 +7689,10 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>3.305699586868286</v>
+        <v>3.305700063705444</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>-0.1831367162106703</v>
+        <v>-0.1831365983806144</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3.305699586868286</v>
+        <v>3.305700063705444</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>3.559508562088013</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.07677920166368679</v>
+        <v>0.07677904634156918</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -7797,10 +7797,10 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>4.450812339782715</v>
+        <v>4.450811862945557</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.1640091618973911</v>
+        <v>0.1640090371914322</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>4.450812339782715</v>
+        <v>4.450811862945557</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         <v>4.486504554748535</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.008019258562485865</v>
+        <v>0.008019366556499818</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -7869,10 +7869,10 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3.361522197723389</v>
+        <v>3.361522436141968</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-0.2507480697494133</v>
+        <v>-0.2507480166081368</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>3.361522197723389</v>
+        <v>3.361522436141968</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>4.075467586517334</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.2123875276734657</v>
+        <v>0.2123874416839424</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>4.186891078948975</v>
+        <v>4.1868896484375</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.02734005118829974</v>
+        <v>0.02733970018281529</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>4.186891078948975</v>
+        <v>4.1868896484375</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>4.160977840423584</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>-0.006189136052685562</v>
+        <v>-0.006188796502813454</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -8013,10 +8013,10 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>4.323929786682129</v>
+        <v>4.323929309844971</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.03916193560933667</v>
+        <v>0.03916182101195664</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>4.323929786682129</v>
+        <v>4.323929309844971</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
@@ -8049,10 +8049,10 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>4.993370532989502</v>
+        <v>4.993372917175293</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.1548222980792326</v>
+        <v>0.1548229768248279</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>4.993370532989502</v>
+        <v>4.993372917175293</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
@@ -8085,10 +8085,10 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>5.387831687927246</v>
+        <v>5.387832164764404</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.0789969725522417</v>
+        <v>0.07899655285755292</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>5.387831687927246</v>
+        <v>5.387832164764404</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>5.849206447601318</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.08563273435357965</v>
+        <v>0.08563263827225942</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -8157,10 +8157,10 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>5.87729549407959</v>
+        <v>5.877295017242432</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.00480219782459379</v>
+        <v>0.004802116302910164</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>5.87729549407959</v>
+        <v>5.877295017242432</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
@@ -8193,10 +8193,10 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>6.717551231384277</v>
+        <v>6.717551708221436</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.1429663929865543</v>
+        <v>0.142966566849871</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>6.717551231384277</v>
+        <v>6.717551708221436</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -8229,10 +8229,10 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>6.556621551513672</v>
+        <v>6.556620121002197</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>-0.02395659881516721</v>
+        <v>-0.02395688104972504</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6.556621551513672</v>
+        <v>6.556620121002197</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -8268,7 +8268,7 @@
         <v>7.269989013671875</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.1088010733200719</v>
+        <v>0.1088013152362772</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -8301,10 +8301,10 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>8.830546379089355</v>
+        <v>8.830545425415039</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2146574585577379</v>
+        <v>0.2146573273781289</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>8.830546379089355</v>
+        <v>8.830545425415039</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -8337,10 +8337,10 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>9.45395565032959</v>
+        <v>9.453956604003906</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.07059690810485542</v>
+        <v>0.07059713172355564</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>9.45395565032959</v>
+        <v>9.453956604003906</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -8373,10 +8373,10 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>10.5658016204834</v>
+        <v>10.56580352783203</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.1176064296551937</v>
+        <v>0.1176065186672466</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -8401,7 +8401,7 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>10.5658016204834</v>
+        <v>10.56580352783203</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -8409,10 +8409,10 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>13.31282997131348</v>
+        <v>13.31282901763916</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2599924217301743</v>
+        <v>0.2599921040147133</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>13.31282997131348</v>
+        <v>13.31282901763916</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -8445,10 +8445,10 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>13.47214126586914</v>
+        <v>13.47213935852051</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.01196674898567385</v>
+        <v>0.01196667820718389</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>13.47214126586914</v>
+        <v>13.47213935852051</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -8481,10 +8481,10 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>12.47993946075439</v>
+        <v>12.47993755340576</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>-0.07364841160242508</v>
+        <v>-0.07364842202936572</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>12.47993946075439</v>
+        <v>12.47993755340576</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>13.34369659423828</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.06921164451158912</v>
+        <v>0.0692118079226125</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -8589,10 +8589,10 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>12.93754100799561</v>
+        <v>12.93754386901855</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>-0.004998333962024648</v>
+        <v>-0.004998113926192538</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>12.93754100799561</v>
+        <v>12.93754386901855</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -8625,10 +8625,10 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>13.65938282012939</v>
+        <v>13.65937805175781</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.05579435935218902</v>
+        <v>0.05579375730410696</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>13.65938282012939</v>
+        <v>13.65937805175781</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -8661,10 +8661,10 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>13.29919052124023</v>
+        <v>13.29919242858887</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>-0.02636958811626222</v>
+        <v>-0.02636910859368102</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -8689,7 +8689,7 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>13.29919052124023</v>
+        <v>13.29919242858887</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -8697,10 +8697,10 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>14.95433521270752</v>
+        <v>14.95433712005615</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.1244545439682092</v>
+        <v>0.1244545261191403</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>14.95433521270752</v>
+        <v>14.95433712005615</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -8733,10 +8733,10 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>16.18479537963867</v>
+        <v>16.1847972869873</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.08228116793085949</v>
+        <v>0.08228115743632047</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>16.18479537963867</v>
+        <v>16.1847972869873</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -8769,10 +8769,10 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>19.93355178833008</v>
+        <v>19.93354988098145</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2316221070924096</v>
+        <v>0.2316218440998432</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>19.93355178833008</v>
+        <v>19.93354988098145</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>19.43178749084473</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>-0.02517184608209688</v>
+        <v>-0.02517175280532691</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -8841,10 +8841,10 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>22.31176948547363</v>
+        <v>22.31177520751953</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.1482098338089488</v>
+        <v>0.148210128277273</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>22.31176948547363</v>
+        <v>22.31177520751953</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -8877,10 +8877,10 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>20.64822959899902</v>
+        <v>20.64823532104492</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>-0.07455885054556877</v>
+        <v>-0.07455883142431274</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>20.64822959899902</v>
+        <v>20.64823532104492</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
@@ -8913,10 +8913,10 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>25.48336601257324</v>
+        <v>25.48336029052734</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.2341671178340934</v>
+        <v>0.2341664987009522</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>25.48336601257324</v>
+        <v>25.48336029052734</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
@@ -8949,10 +8949,10 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>32.56910705566406</v>
+        <v>32.5691032409668</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.2780535757950808</v>
+        <v>0.2780537130761895</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>32.56910705566406</v>
+        <v>32.5691032409668</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
@@ -8985,10 +8985,10 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>29.31838035583496</v>
+        <v>29.31838226318359</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>-0.09981012664158295</v>
+        <v>-0.09980996264257924</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>29.31838035583496</v>
+        <v>29.31838226318359</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
@@ -9021,10 +9021,10 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>24.40889167785645</v>
+        <v>24.40888977050781</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>-0.1674542938045153</v>
+        <v>-0.1674544130233561</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>24.40889167785645</v>
+        <v>24.40888977050781</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -9057,10 +9057,10 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>24.30820655822754</v>
+        <v>24.30820465087891</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>-0.004124936148585889</v>
+        <v>-0.00412493647091472</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>24.30820655822754</v>
+        <v>24.30820465087891</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
@@ -9093,10 +9093,10 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>27.2047061920166</v>
+        <v>27.20470428466797</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1191572741843718</v>
+        <v>0.1191572835340735</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>27.2047061920166</v>
+        <v>27.20470428466797</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>18.49174118041992</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>-0.3202741816102964</v>
+        <v>-0.3202741339540492</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -9165,10 +9165,10 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>18.61637306213379</v>
+        <v>18.61637115478516</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.006739867300643132</v>
+        <v>0.006739764154670258</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>18.61637306213379</v>
+        <v>18.61637115478516</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
@@ -9201,10 +9201,10 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>15.11703300476074</v>
+        <v>15.11703109741211</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>-0.1879710965016489</v>
+        <v>-0.1879711157603117</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>15.11703300476074</v>
+        <v>15.11703109741211</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
@@ -9237,10 +9237,10 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>18.11271858215332</v>
+        <v>18.11271476745605</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1981662391323191</v>
+        <v>0.1981661379632127</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>18.11271858215332</v>
+        <v>18.11271476745605</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
@@ -9273,10 +9273,10 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>15.05220985412598</v>
+        <v>15.05221176147461</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>-0.168970147366111</v>
+        <v>-0.1689698670395005</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>15.05220985412598</v>
+        <v>15.05221176147461</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
@@ -9309,10 +9309,10 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>12.10898780822754</v>
+        <v>12.10898971557617</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>-0.195534215535247</v>
+        <v>-0.1955341907580299</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>12.10898780822754</v>
+        <v>12.10898971557617</v>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
@@ -9345,10 +9345,10 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>13.46363067626953</v>
+        <v>13.46363162994385</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1118708590260178</v>
+        <v>0.1118707626471229</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>13.46363067626953</v>
+        <v>13.46363162994385</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>16.8854808807373</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.2541550854108761</v>
+        <v>0.2541549965748526</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -9453,10 +9453,10 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>19.49368858337402</v>
+        <v>19.49368667602539</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.3368690408023851</v>
+        <v>0.3368689099972106</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>19.49368858337402</v>
+        <v>19.49368667602539</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -9489,10 +9489,10 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>23.16452598571777</v>
+        <v>23.16452980041504</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1883090204628883</v>
+        <v>0.1883093324211624</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>23.16452598571777</v>
+        <v>23.16452980041504</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -9525,10 +9525,10 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>27.72012519836426</v>
+        <v>27.72012710571289</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1966627426546637</v>
+        <v>0.1966626279293711</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>27.72012519836426</v>
+        <v>27.72012710571289</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
@@ -9561,10 +9561,10 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>27.69218635559082</v>
+        <v>27.69218254089355</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>-0.001007890208774564</v>
+        <v>-0.001008096561490035</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>27.69218635559082</v>
+        <v>27.69218254089355</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
@@ -9597,10 +9597,10 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>37.75652694702148</v>
+        <v>37.75653076171875</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.3634361137902264</v>
+        <v>0.3634364393620109</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>37.75652694702148</v>
+        <v>37.75653076171875</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
@@ -9633,10 +9633,10 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>42.21975326538086</v>
+        <v>42.21974945068359</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.1182107222049846</v>
+        <v>0.1182105081934617</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>42.21975326538086</v>
+        <v>42.21974945068359</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
@@ -9669,10 +9669,10 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>46.63814544677734</v>
+        <v>46.63813781738281</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.1046522501830784</v>
+        <v>0.1046521692853788</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>46.63814544677734</v>
+        <v>46.63813781738281</v>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
@@ -9708,7 +9708,7 @@
         <v>49.25904083251953</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.05619638947121319</v>
+        <v>0.05619656225124547</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -9741,10 +9741,10 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>43.41800308227539</v>
+        <v>43.41799926757812</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>-0.1185779838893664</v>
+        <v>-0.1185780613309324</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>43.41800308227539</v>
+        <v>43.41799926757812</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>40.70405960083008</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>-0.06250733080244375</v>
+        <v>-0.06250724843451383</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -9813,10 +9813,10 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>46.68291473388672</v>
+        <v>46.68291091918945</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.1468859664536928</v>
+        <v>0.1468858727358351</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>46.68291473388672</v>
+        <v>46.68291091918945</v>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
@@ -9849,10 +9849,10 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>49.43412399291992</v>
+        <v>49.43413543701172</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.05893396491449421</v>
+        <v>0.05893429659056126</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>49.43412399291992</v>
+        <v>49.43413543701172</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
         <v>61.41783142089844</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.2424177159424299</v>
+        <v>0.2424174283204805</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -9957,10 +9957,10 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>90.19991302490234</v>
+        <v>90.19990539550781</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.1421811675620739</v>
+        <v>0.1421810709527707</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>90.19991302490234</v>
+        <v>90.19990539550781</v>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         <v>86.25274658203125</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>-0.04376020231617472</v>
+        <v>-0.04376012143437502</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -10065,10 +10065,10 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>123.3367233276367</v>
+        <v>123.3367080688477</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.1269430297426406</v>
+        <v>0.1269428903211811</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -10093,7 +10093,7 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>123.3367233276367</v>
+        <v>123.3367080688477</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>116.8274383544922</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>-0.05277653562964368</v>
+        <v>-0.05277641844244729</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -10137,10 +10137,10 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>119.173583984375</v>
+        <v>119.1735763549805</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.02008214562373478</v>
+        <v>0.02008208031891745</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>119.173583984375</v>
+        <v>119.1735763549805</v>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
@@ -10173,10 +10173,10 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>121.2505493164062</v>
+        <v>121.2505340576172</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.0174280680549439</v>
+        <v>0.01742800515149523</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>121.2505493164062</v>
+        <v>121.2505340576172</v>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
@@ -10209,10 +10209,10 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>132.5528564453125</v>
+        <v>132.5528869628906</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>0.09321448185288306</v>
+        <v>0.09321487111885762</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>132.5528564453125</v>
+        <v>132.5528869628906</v>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>138.0343170166016</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.04135301734180707</v>
+        <v>0.04135277759167555</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -10317,10 +10317,10 @@
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>119.8909378051758</v>
+        <v>119.8909454345703</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>-0.1058902751059577</v>
+        <v>-0.1058902182082808</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>119.8909378051758</v>
+        <v>119.8909454345703</v>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
@@ -10353,10 +10353,10 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>124.7337036132812</v>
+        <v>124.7337112426758</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.04039309306242167</v>
+        <v>0.04039309049196182</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>124.7337036132812</v>
+        <v>124.7337112426758</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>108.2283248901367</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>-0.1323249309931265</v>
+        <v>-0.1323249840648691</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -10569,10 +10569,10 @@
         </is>
       </c>
       <c r="F105" s="3" t="n">
-        <v>173.9483032226562</v>
+        <v>173.9483184814453</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>-0.02074555918313137</v>
+        <v>-0.02074547328268472</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -10597,7 +10597,7 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>173.9483032226562</v>
+        <v>173.9483184814453</v>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>186.3423309326172</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.07125121360969189</v>
+        <v>0.07125111963927333</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -10713,10 +10713,10 @@
         </is>
       </c>
       <c r="F109" s="3" t="n">
-        <v>186.2728118896484</v>
+        <v>186.2727966308594</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>0.05373101785259271</v>
+        <v>0.05373093153479269</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>186.2728118896484</v>
+        <v>186.2727966308594</v>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
@@ -10752,7 +10752,7 @@
         <v>190.8971710205078</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0.02482573320254033</v>
+        <v>0.02482581715253174</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>3.520614035087721</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4.759474108721161</v>
+        <v>4.759474550358498</v>
       </c>
     </row>
     <row r="3">
@@ -11409,7 +11409,7 @@
         <v>3.448521353622169</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3.874489132034076</v>
+        <v>3.87448954575127</v>
       </c>
     </row>
     <row r="4">
@@ -11448,7 +11448,7 @@
         <v>3.721926605504589</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>12.3704578842066</v>
+        <v>12.3704579133961</v>
       </c>
     </row>
     <row r="7">
@@ -11461,7 +11461,7 @@
         <v>-0.8680000000000002</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-8.791789686655342</v>
+        <v>-8.791788510659671</v>
       </c>
     </row>
     <row r="8">
@@ -11474,7 +11474,7 @@
         <v>21.97</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>38.54459628071724</v>
+        <v>38.54465342164011</v>
       </c>
     </row>
     <row r="9">
@@ -11487,7 +11487,7 @@
         <v>-2.2</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>-32.02741816102964</v>
+        <v>-32.02741339540493</v>
       </c>
     </row>
     <row r="10">
@@ -11500,7 +11500,7 @@
         <v>3.520614035087721</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4.759474108721161</v>
+        <v>4.759474550358498</v>
       </c>
     </row>
     <row r="11">
@@ -11513,7 +11513,7 @@
         <v>4.001514378174758</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>13.50731721943351</v>
+        <v>13.50731790338343</v>
       </c>
     </row>
     <row r="12">
@@ -11526,7 +11526,7 @@
         <v>2.626664430542024</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.03004063066969971</v>
+        <v>-0.0300397442826129</v>
       </c>
     </row>
     <row r="13">
@@ -11539,7 +11539,7 @@
         <v>8.443105350916397</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.1259009991169342</v>
+        <v>0.1259025844626875</v>
       </c>
     </row>
     <row r="14">
@@ -11552,7 +11552,7 @@
         <v>0.8798204135639283</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.3523626513985706</v>
+        <v>0.3523626662526618</v>
       </c>
     </row>
     <row r="15">
@@ -11565,7 +11565,7 @@
         <v>14.52592048115421</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.6696209906580181</v>
+        <v>0.6696211286574246</v>
       </c>
     </row>
     <row r="16">
@@ -11578,7 +11578,7 @@
         <v>93.47695852534564</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.505229331977628</v>
+        <v>2.505229672990199</v>
       </c>
     </row>
   </sheetData>

--- a/Project_1_May2026_Update.xlsx
+++ b/Project_1_May2026_Update.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T14:28:05</t>
+          <t>2026-08-10T14:18:23</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
         <v>21.19</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>27.82295583188716</v>
+        <v>27.82296257687193</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>114</v>
@@ -839,13 +839,13 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.01997541333835227</v>
+        <v>0.01997541778106075</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>26.78749981121109</v>
+        <v>26.78750643819328</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>5.59749981121109</v>
+        <v>5.597506438193275</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3</v>
@@ -6790,7 +6790,7 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -6861,10 +6861,10 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.685508012771606</v>
+        <v>2.685507774353027</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.02285947846851455</v>
+        <v>0.02285938765936324</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2.685508012771606</v>
+        <v>2.685507774353027</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -6897,10 +6897,10 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2.499259471893311</v>
+        <v>2.49925971031189</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-0.06935318755056563</v>
+        <v>-0.06935301614831746</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.499259471893311</v>
+        <v>2.49925971031189</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -6933,10 +6933,10 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2.682740211486816</v>
+        <v>2.682739973068237</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.07341404190198397</v>
+        <v>0.07341384410724183</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2.682740211486816</v>
+        <v>2.682739973068237</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -6969,10 +6969,10 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2.568711280822754</v>
+        <v>2.56871223449707</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-0.04250464885709748</v>
+        <v>-0.04250420827805912</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2.568711280822754</v>
+        <v>2.56871223449707</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>3.558812141418457</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.3854465342164011</v>
+        <v>0.3854460198478553</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -7077,10 +7077,10 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>4.006529808044434</v>
+        <v>4.006528377532959</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.1241699560255558</v>
+        <v>0.1241695546462829</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>4.006529808044434</v>
+        <v>4.006528377532959</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -7113,10 +7113,10 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>4.18105936050415</v>
+        <v>4.181059837341309</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.04356127642162821</v>
+        <v>0.04356176803515321</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>4.18105936050415</v>
+        <v>4.181059837341309</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -7149,10 +7149,10 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>4.411284446716309</v>
+        <v>4.411284923553467</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.055063816693671</v>
+        <v>0.05506381041381037</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4.411284446716309</v>
+        <v>4.411284923553467</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -7185,10 +7185,10 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>5.103193759918213</v>
+        <v>5.103194236755371</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.1568498521370461</v>
+        <v>0.1568498351823857</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>5.103193759918213</v>
+        <v>5.103194236755371</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
@@ -7221,10 +7221,10 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>4.956112861633301</v>
+        <v>4.956110000610352</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-0.02882134310480688</v>
+        <v>-0.02882199448448508</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>4.956112861633301</v>
+        <v>4.956110000610352</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -7257,10 +7257,10 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>4.778074264526367</v>
+        <v>4.778075695037842</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0.03592303122981355</v>
+        <v>-0.03592218605934583</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4.778074264526367</v>
+        <v>4.778075695037842</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -7293,10 +7293,10 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>6.069514274597168</v>
+        <v>6.069513320922852</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.2702846248453648</v>
+        <v>0.2702840449401422</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -7321,7 +7321,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>6.069514274597168</v>
+        <v>6.069513320922852</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>5.979394435882568</v>
+        <v>5.979395389556885</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-0.01484794905117526</v>
+        <v>-0.01484763713349335</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5.979394435882568</v>
+        <v>5.979395389556885</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -7365,10 +7365,10 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>5.722182273864746</v>
+        <v>5.722182750701904</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.04301642328097344</v>
+        <v>-0.04301649616685432</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>5.722182273864746</v>
+        <v>5.722182750701904</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -7401,10 +7401,10 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5.556884288787842</v>
+        <v>5.556884765625</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.02888722818772815</v>
+        <v>-0.02888722578051672</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>5.556884288787842</v>
+        <v>5.556884765625</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -7437,10 +7437,10 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>6.235025405883789</v>
+        <v>6.235026836395264</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.1220362134342508</v>
+        <v>0.1220363745826194</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>6.235025405883789</v>
+        <v>6.235026836395264</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5.857003211975098</v>
+        <v>5.857002258300781</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>-0.06062881372575712</v>
+        <v>-0.06062918220140889</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5.857003211975098</v>
+        <v>5.857002258300781</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -7509,10 +7509,10 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>6.0538010597229</v>
+        <v>6.053802013397217</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.03360043363907228</v>
+        <v>0.03360076476281404</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>6.0538010597229</v>
+        <v>6.053802013397217</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>6.94319486618042</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.1469149378519929</v>
+        <v>0.146914757174905</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -7581,10 +7581,10 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>6.951603889465332</v>
+        <v>6.951605796813965</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.001211117280586649</v>
+        <v>0.001211391988220623</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>6.951603889465332</v>
+        <v>6.951605796813965</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>5.215310573577881</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-0.2497687358911059</v>
+        <v>-0.2497689417360024</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -7725,10 +7725,10 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>3.559508562088013</v>
+        <v>3.559508323669434</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.07677904634156918</v>
+        <v>0.0767789742180931</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -7753,7 +7753,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.559508562088013</v>
+        <v>3.559508323669434</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
@@ -7761,10 +7761,10 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.823691844940186</v>
+        <v>3.823692321777344</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.07421903283671338</v>
+        <v>0.07421923875024605</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>3.823691844940186</v>
+        <v>3.823692321777344</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
@@ -7797,10 +7797,10 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>4.450811862945557</v>
+        <v>4.450810432434082</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.1640090371914322</v>
+        <v>0.164008517914757</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>4.450811862945557</v>
+        <v>4.450810432434082</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         <v>4.486504554748535</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.008019366556499818</v>
+        <v>0.008019690538680679</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -7869,10 +7869,10 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3.361522436141968</v>
+        <v>3.361522197723389</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-0.2507480166081368</v>
+        <v>-0.2507480697494133</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>3.361522436141968</v>
+        <v>3.361522197723389</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -7905,10 +7905,10 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>4.075467586517334</v>
+        <v>4.075469017028809</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.2123874416839424</v>
+        <v>0.2123879532281372</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>4.075467586517334</v>
+        <v>4.075469017028809</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>4.1868896484375</v>
+        <v>4.186890125274658</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.02733970018281529</v>
+        <v>0.02733945658285974</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>4.1868896484375</v>
+        <v>4.186890125274658</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
@@ -7977,10 +7977,10 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>4.160977840423584</v>
+        <v>4.1609787940979</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>-0.006188796502813454</v>
+        <v>-0.006188681909835902</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>4.160977840423584</v>
+        <v>4.1609787940979</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
@@ -8013,10 +8013,10 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>4.323929309844971</v>
+        <v>4.323929786682129</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.03916182101195664</v>
+        <v>0.03916169743892106</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>4.323929309844971</v>
+        <v>4.323929786682129</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
@@ -8049,10 +8049,10 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>4.993372917175293</v>
+        <v>4.993371963500977</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.1548229768248279</v>
+        <v>0.1548226289151955</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>4.993372917175293</v>
+        <v>4.993371963500977</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
@@ -8085,10 +8085,10 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>5.387832164764404</v>
+        <v>5.387831687927246</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.07899655285755292</v>
+        <v>0.07899666343896872</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>5.387832164764404</v>
+        <v>5.387831687927246</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
@@ -8121,10 +8121,10 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>5.849206447601318</v>
+        <v>5.849205493927002</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.08563263827225942</v>
+        <v>0.08563255734836273</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>5.849206447601318</v>
+        <v>5.849205493927002</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
@@ -8157,10 +8157,10 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>5.877295017242432</v>
+        <v>5.877296924591064</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.004802116302910164</v>
+        <v>0.004802606216045779</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>5.877295017242432</v>
+        <v>5.877296924591064</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
@@ -8193,10 +8193,10 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>6.717551708221436</v>
+        <v>6.717551231384277</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.142966566849871</v>
+        <v>0.1429661147929286</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>6.717551708221436</v>
+        <v>6.717551231384277</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -8229,10 +8229,10 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>6.556620121002197</v>
+        <v>6.556621074676514</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>-0.02395688104972504</v>
+        <v>-0.02395666979894417</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6.556620121002197</v>
+        <v>6.556621074676514</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -8265,10 +8265,10 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>7.269989013671875</v>
+        <v>7.269989967346191</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.1088013152362772</v>
+        <v>0.1088012994108971</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>7.269989013671875</v>
+        <v>7.269989967346191</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -8301,10 +8301,10 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>8.830545425415039</v>
+        <v>8.830544471740723</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2146573273781289</v>
+        <v>0.2146570368602847</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>8.830545425415039</v>
+        <v>8.830544471740723</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -8337,10 +8337,10 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>9.453956604003906</v>
+        <v>9.45395565032959</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.07059713172355564</v>
+        <v>0.07059713934785017</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>9.453956604003906</v>
+        <v>9.45395565032959</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -8373,10 +8373,10 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>10.56580352783203</v>
+        <v>10.56580543518066</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.1176065186672466</v>
+        <v>0.1176068331579609</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -8401,7 +8401,7 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>10.56580352783203</v>
+        <v>10.56580543518066</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -8409,10 +8409,10 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>13.31282901763916</v>
+        <v>13.31282997131348</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2599921040147133</v>
+        <v>0.2599919668202599</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>13.31282901763916</v>
+        <v>13.31282997131348</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -8445,10 +8445,10 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>13.47213935852051</v>
+        <v>13.47213745117188</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.01196667820718389</v>
+        <v>0.01196646244274691</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>13.47213935852051</v>
+        <v>13.47213745117188</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>12.47993755340576</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>-0.07364842202936572</v>
+        <v>-0.07364829087902502</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -8553,10 +8553,10 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>13.00253200531006</v>
+        <v>13.00253105163574</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>-0.02556747199089759</v>
+        <v>-0.0255675434609216</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>13.00253200531006</v>
+        <v>13.00253105163574</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -8589,10 +8589,10 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>12.93754386901855</v>
+        <v>12.93754291534424</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>-0.004998113926192538</v>
+        <v>-0.004998114292780631</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>12.93754386901855</v>
+        <v>12.93754291534424</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -8625,10 +8625,10 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>13.65937805175781</v>
+        <v>13.65937995910645</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.05579375730410696</v>
+        <v>0.05579398255800871</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>13.65937805175781</v>
+        <v>13.65937995910645</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -8661,10 +8661,10 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>13.29919242858887</v>
+        <v>13.29919147491455</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>-0.02636910859368102</v>
+        <v>-0.02636931436640821</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -8689,7 +8689,7 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>13.29919242858887</v>
+        <v>13.29919147491455</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -8697,10 +8697,10 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>14.95433712005615</v>
+        <v>14.95433521270752</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.1244545261191403</v>
+        <v>0.1244544633344791</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>14.95433712005615</v>
+        <v>14.95433521270752</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -8733,10 +8733,10 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>16.1847972869873</v>
+        <v>16.18479537963867</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.08228115743632047</v>
+        <v>0.08228116793085949</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>16.1847972869873</v>
+        <v>16.18479537963867</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -8769,10 +8769,10 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>19.93354988098145</v>
+        <v>19.93355369567871</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2316218440998432</v>
+        <v>0.2316222249405868</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>19.93354988098145</v>
+        <v>19.93355369567871</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>19.43178749084473</v>
+        <v>19.43178939819336</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>-0.02517175280532691</v>
+        <v>-0.02517184367352054</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>19.43178749084473</v>
+        <v>19.43178939819336</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -8841,10 +8841,10 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>22.31177520751953</v>
+        <v>22.31177711486816</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.148210128277273</v>
+        <v>0.1482101137295451</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>22.31177520751953</v>
+        <v>22.31177711486816</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -8877,10 +8877,10 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>20.64823532104492</v>
+        <v>20.64823150634766</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>-0.07455883142431274</v>
+        <v>-0.07455908150910806</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>20.64823532104492</v>
+        <v>20.64823150634766</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
@@ -8913,10 +8913,10 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>25.48336029052734</v>
+        <v>25.48336410522461</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.2341664987009522</v>
+        <v>0.2341669114563416</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>25.48336029052734</v>
+        <v>25.48336410522461</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>32.5691032409668</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.2780537130761895</v>
+        <v>0.2780535217596904</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -8985,10 +8985,10 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>29.31838226318359</v>
+        <v>29.31838035583496</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>-0.09980996264257924</v>
+        <v>-0.09981002120570948</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>29.31838226318359</v>
+        <v>29.31838035583496</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
@@ -9021,10 +9021,10 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>24.40888977050781</v>
+        <v>24.40889358520508</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>-0.1674544130233561</v>
+        <v>-0.1674542287481032</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>24.40888977050781</v>
+        <v>24.40889358520508</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -9057,10 +9057,10 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>24.30820465087891</v>
+        <v>24.30820846557617</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>-0.00412493647091472</v>
+        <v>-0.004124935826256948</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>24.30820465087891</v>
+        <v>24.30820846557617</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>27.20470428466797</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1191572835340735</v>
+        <v>0.1191571079042555</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -9129,10 +9129,10 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>18.49174118041992</v>
+        <v>18.49174308776855</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>-0.3202741339540492</v>
+        <v>-0.3202740638430636</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>18.49174118041992</v>
+        <v>18.49174308776855</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
@@ -9165,10 +9165,10 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>18.61637115478516</v>
+        <v>18.61637306213379</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.006739764154670258</v>
+        <v>0.006739763459490788</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>18.61637115478516</v>
+        <v>18.61637306213379</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
@@ -9201,10 +9201,10 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>15.11703109741211</v>
+        <v>15.11703300476074</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>-0.1879711157603117</v>
+        <v>-0.1879710965016489</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>15.11703109741211</v>
+        <v>15.11703300476074</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
@@ -9237,10 +9237,10 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>18.11271476745605</v>
+        <v>18.11271095275879</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1981661379632127</v>
+        <v>0.1981657344436987</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>18.11271476745605</v>
+        <v>18.11271095275879</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
@@ -9273,10 +9273,10 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>15.05221176147461</v>
+        <v>15.05221080780029</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>-0.1689698670395005</v>
+        <v>-0.1689697446694109</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>15.05221176147461</v>
+        <v>15.05221080780029</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
@@ -9309,10 +9309,10 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>12.10898971557617</v>
+        <v>12.10899066925049</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>-0.1955341907580299</v>
+        <v>-0.1955340764311234</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>12.10898971557617</v>
+        <v>12.10899066925049</v>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
@@ -9348,7 +9348,7 @@
         <v>13.46363162994385</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1118707626471229</v>
+        <v>0.1118706750789171</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -9381,10 +9381,10 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>16.8854808807373</v>
+        <v>16.88548278808594</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.2541549965748526</v>
+        <v>0.2541551382415801</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -9409,7 +9409,7 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>16.8854808807373</v>
+        <v>16.88548278808594</v>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>14.58159923553467</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>-0.1364415773216663</v>
+        <v>-0.13644167486741</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -9561,10 +9561,10 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>27.69218254089355</v>
+        <v>27.69218063354492</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>-0.001008096561490035</v>
+        <v>-0.001008165368845293</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>27.69218254089355</v>
+        <v>27.69218063354492</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         <v>37.75653076171875</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.3634364393620109</v>
+        <v>0.3634365332711422</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -9633,10 +9633,10 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>42.21974945068359</v>
+        <v>42.21975326538086</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.1182105081934617</v>
+        <v>0.1182106092275659</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>42.21974945068359</v>
+        <v>42.21975326538086</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>46.63813781738281</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.1046521692853788</v>
+        <v>0.1046520694763253</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>49.25904083251953</v>
+        <v>49.2590446472168</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.05619656225124547</v>
+        <v>0.05619664404476143</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>49.25904083251953</v>
+        <v>49.2590446472168</v>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>43.41799926757812</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>-0.1185780613309324</v>
+        <v>-0.1185781295896224</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -9849,10 +9849,10 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>49.43413543701172</v>
+        <v>49.43412780761719</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.05893429659056126</v>
+        <v>0.05893413316042428</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>49.43413543701172</v>
+        <v>49.43412780761719</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
         <v>61.41783142089844</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.2424174283204805</v>
+        <v>0.242417620068432</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -9957,10 +9957,10 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>90.19990539550781</v>
+        <v>90.19991302490234</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.1421810709527707</v>
+        <v>0.1421811675620739</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>90.19990539550781</v>
+        <v>90.19991302490234</v>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
@@ -9993,10 +9993,10 @@
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>86.25274658203125</v>
+        <v>86.25273895263672</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>-0.04376012143437502</v>
+        <v>-0.0437602868993443</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>86.25274658203125</v>
+        <v>86.25273895263672</v>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
@@ -10029,10 +10029,10 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>109.4436187744141</v>
+        <v>109.443603515625</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.2688711155456016</v>
+        <v>0.2688710508743717</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>109.4436187744141</v>
+        <v>109.443603515625</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
@@ -10065,10 +10065,10 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>123.3367080688477</v>
+        <v>123.3367233276367</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.1269428903211811</v>
+        <v>0.1269431868627044</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -10093,7 +10093,7 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>123.3367080688477</v>
+        <v>123.3367233276367</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>116.8274383544922</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>-0.05277641844244729</v>
+        <v>-0.05277653562964368</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -10137,10 +10137,10 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>119.1735763549805</v>
+        <v>119.173583984375</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.02008208031891745</v>
+        <v>0.02008214562373478</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>119.1735763549805</v>
+        <v>119.173583984375</v>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
@@ -10173,10 +10173,10 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>121.2505340576172</v>
+        <v>121.2505416870117</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.01742800515149523</v>
+        <v>0.01742800403576883</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>121.2505340576172</v>
+        <v>121.2505416870117</v>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
@@ -10209,10 +10209,10 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>132.5528869628906</v>
+        <v>132.5528717041016</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>0.09321487111885762</v>
+        <v>0.09321467648585813</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>132.5528869628906</v>
+        <v>132.5528717041016</v>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>138.0343170166016</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.04135277759167555</v>
+        <v>0.04135289746672743</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -10281,10 +10281,10 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>134.0897369384766</v>
+        <v>134.0897216796875</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>-0.02857680729967016</v>
+        <v>-0.02857691784311611</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>134.0897369384766</v>
+        <v>134.0897216796875</v>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
@@ -10317,10 +10317,10 @@
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>119.8909454345703</v>
+        <v>119.8909378051758</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>-0.1058902182082808</v>
+        <v>-0.1058901733604136</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>119.8909454345703</v>
+        <v>119.8909378051758</v>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
@@ -10353,10 +10353,10 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>124.7337112426758</v>
+        <v>124.7337036132812</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.04039309049196182</v>
+        <v>0.04039309306242167</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>124.7337112426758</v>
+        <v>124.7337036132812</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>108.2283248901367</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>-0.1323249840648691</v>
+        <v>-0.1323249309931265</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -10461,10 +10461,10 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>134.9409027099609</v>
+        <v>134.9408874511719</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>0.2406355273027898</v>
+        <v>0.240635387014742</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>134.9409027099609</v>
+        <v>134.9408874511719</v>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>157.7798614501953</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0.1692515633256428</v>
+        <v>0.1692516955417807</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>3.520614035087721</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4.759474550358498</v>
+        <v>4.759474260033616</v>
       </c>
     </row>
     <row r="3">
@@ -11448,7 +11448,7 @@
         <v>3.721926605504589</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>12.3704579133961</v>
+        <v>12.37045721245495</v>
       </c>
     </row>
     <row r="7">
@@ -11461,7 +11461,7 @@
         <v>-0.8680000000000002</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-8.791788510659671</v>
+        <v>-8.791788069887311</v>
       </c>
     </row>
     <row r="8">
@@ -11474,7 +11474,7 @@
         <v>21.97</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>38.54465342164011</v>
+        <v>38.54460198478553</v>
       </c>
     </row>
     <row r="9">
@@ -11487,7 +11487,7 @@
         <v>-2.2</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>-32.02741339540493</v>
+        <v>-32.02740638430635</v>
       </c>
     </row>
     <row r="10">
@@ -11500,7 +11500,7 @@
         <v>3.520614035087721</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4.759474550358498</v>
+        <v>4.759474260033616</v>
       </c>
     </row>
     <row r="11">
@@ -11513,7 +11513,7 @@
         <v>4.001514378174758</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>13.50731790338343</v>
+        <v>13.50731527656471</v>
       </c>
     </row>
     <row r="12">
@@ -11526,7 +11526,7 @@
         <v>2.626664430542024</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.0300397442826129</v>
+        <v>-0.03004051713995683</v>
       </c>
     </row>
     <row r="13">
@@ -11539,7 +11539,7 @@
         <v>8.443105350916397</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.1259025844626875</v>
+        <v>0.1259024146109362</v>
       </c>
     </row>
     <row r="14">
@@ -11552,7 +11552,7 @@
         <v>0.8798204135639283</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.3523626662526618</v>
+        <v>0.3523627132840631</v>
       </c>
     </row>
     <row r="15">
@@ -11565,7 +11565,7 @@
         <v>14.52592048115421</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.6696211286574246</v>
+        <v>0.6696211014887262</v>
       </c>
     </row>
     <row r="16">
@@ -11578,7 +11578,7 @@
         <v>93.47695852534564</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.505229672990199</v>
+        <v>2.505229656636168</v>
       </c>
     </row>
   </sheetData>

--- a/Project_1_May2026_Update.xlsx
+++ b/Project_1_May2026_Update.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Source_and_Method" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="LSQ_Returns" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SP500TR_Returns" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="NVIDIA_Returns" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Verification" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Updated_Table_2" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Updated_Table_4" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Regression" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Serial_Correlation" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Newey_West" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="MPPM" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_and_Method" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LSQ_Returns" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP500TR_Returns" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NVIDIA_Returns" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Updated_Table_2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Updated_Table_4" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regression" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Serial_Correlation" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Newey_West" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MPPM" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Source_and_Method'!$A$1:$B$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'LSQ_Returns'!$A$1:$C$115</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SP500TR_Returns'!$A$1:$H$115</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NVIDIA_Returns'!$A$1:$H$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'LSQ_Returns'!$A$1:$C$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SP500TR_Returns'!$A$1:$H$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NVIDIA_Returns'!$A$1:$H$116</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Verification'!$A$1:$I$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Updated_Table_2'!$A$1:$C$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Updated_Table_4'!$A$1:$C$16</definedName>
@@ -482,7 +482,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Project 1 update through Jun 2026</t>
+          <t>Project 1 update through Jul 2026</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>data/LSQ_latest_spartan.pdf</t>
+          <t>data\LSQ_latest_spartan.pdf</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10T14:18:23</t>
+          <t>2026-08-10T18:30:47</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
   </cols>
@@ -620,19 +620,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.520614035087721</v>
+        <v>3.519478260869565</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.3747761591438624</v>
+        <v>0.3715046783874216</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9.393911403356611</v>
+        <v>9.473577226931436</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.5288328374812032</v>
+        <v>0.5241488622315456</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>6.657328716303208</v>
+        <v>6.714654012384019</v>
       </c>
     </row>
     <row r="3">
@@ -642,19 +642,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3.553834897000299</v>
+        <v>3.552270603645034</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.3917940053800512</v>
+        <v>0.3882041321353366</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>9.070671955669612</v>
+        <v>9.150522391674681</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.5847909478065225</v>
+        <v>0.5791256161049188</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>6.077103126049211</v>
+        <v>6.133851628834663</v>
       </c>
     </row>
     <row r="4">
@@ -664,19 +664,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.02540694158567561</v>
+        <v>-0.02530998899887835</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.08345823680342875</v>
+        <v>0.08305537019862617</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-0.3044270111471107</v>
+        <v>-0.3047363335850498</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.1060104541983708</v>
+        <v>0.1058495973296159</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-0.2396644913730222</v>
+        <v>-0.2391127565659318</v>
       </c>
     </row>
   </sheetData>
@@ -762,24 +762,24 @@
         <v>35.16</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>46.57265489959113</v>
+        <v>46.57265489959188</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.03262752823095071</v>
+        <v>0.03263370241484337</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>47.0023852738126</v>
+        <v>47.01293292530049</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>11.8423852738126</v>
+        <v>11.85293292530049</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>3</v>
@@ -798,21 +798,21 @@
         <v>12.80668196833166</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.009916832011085525</v>
+        <v>0.009824109332120121</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>12.57120795593889</v>
+        <v>12.44724565179145</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>4.201207955938891</v>
+        <v>4.077245651791451</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>3</v>
@@ -828,24 +828,24 @@
         <v>21.19</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>27.82296257687193</v>
+        <v>27.82296044992847</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Jul 2026</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.01997541778106075</v>
+        <v>0.0198279274293732</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>26.78750643819328</v>
+        <v>26.56767680106729</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>5.597506438193275</v>
+        <v>5.377676801067285</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3</v>
@@ -863,7 +863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C115"/>
+  <dimension ref="A1:C116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2598,8 +2598,23 @@
         <v>0.0639</v>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0.0339</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C115"/>
+  <autoFilter ref="A1:C116"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2610,7 +2625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H115"/>
+  <dimension ref="A1:H116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2697,7 +2712,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -2733,7 +2748,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -2769,7 +2784,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2820,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2856,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2892,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -2913,7 +2928,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2964,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -2985,7 +3000,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3036,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3072,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3108,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3144,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3165,7 +3180,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3216,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3237,7 +3252,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3273,7 +3288,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3324,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3360,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3396,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3417,7 +3432,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3468,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3504,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3540,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3561,7 +3576,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3597,7 +3612,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3633,7 +3648,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3684,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3720,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3741,7 +3756,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3792,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3828,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3849,7 +3864,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3900,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3936,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3957,7 +3972,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -3993,7 +4008,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4044,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4065,7 +4080,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4116,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4137,7 +4152,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4173,7 +4188,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4209,7 +4224,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4245,7 +4260,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4281,7 +4296,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4317,7 +4332,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4353,7 +4368,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4389,7 +4404,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4440,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4476,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4512,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4533,7 +4548,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4569,7 +4584,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4605,7 +4620,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4656,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4677,7 +4692,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4728,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4764,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4785,7 +4800,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4836,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4872,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4893,7 +4908,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4944,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -4965,7 +4980,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5001,7 +5016,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5037,7 +5052,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5073,7 +5088,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5124,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5145,7 +5160,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5196,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5217,7 +5232,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5268,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5304,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5325,7 +5340,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5361,7 +5376,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5412,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5448,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5469,7 +5484,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5505,7 +5520,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5556,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5577,7 +5592,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5613,7 +5628,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5649,7 +5664,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5685,7 +5700,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5721,7 +5736,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5757,7 +5772,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5793,7 +5808,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5829,7 +5844,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5865,7 +5880,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5916,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5952,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5988,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6009,7 +6024,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6060,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6081,7 +6096,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6117,7 +6132,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6153,7 +6168,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6204,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6225,7 +6240,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6276,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6297,7 +6312,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6333,7 +6348,7 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6384,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6405,7 +6420,7 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6456,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6477,7 +6492,7 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6513,7 +6528,7 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6549,7 +6564,7 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6585,7 +6600,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6621,7 +6636,7 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6672,7 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6693,7 +6708,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6744,7 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6765,12 +6780,48 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>16774.0703125</v>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>16763.419921875</v>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>-0.0006349317981017011</v>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H115"/>
+  <autoFilter ref="A1:H116"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6781,7 +6832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H115"/>
+  <dimension ref="A1:H116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6853,7 +6904,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2.625490665435791</v>
+        <v>2.625491619110107</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -6861,14 +6912,14 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.685507774353027</v>
+        <v>2.685507535934448</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.02285938765936324</v>
+        <v>0.02285892531040834</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6889,7 +6940,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2.685507774353027</v>
+        <v>2.685507535934448</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -6897,14 +6948,14 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2.49925971031189</v>
+        <v>2.499259948730469</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-0.06935301614831746</v>
+        <v>-0.06935284474603898</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6925,7 +6976,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.49925971031189</v>
+        <v>2.499259948730469</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -6933,14 +6984,14 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2.682739973068237</v>
+        <v>2.682739496231079</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.07341384410724183</v>
+        <v>0.07341355091686697</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6961,7 +7012,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2.682739973068237</v>
+        <v>2.682739496231079</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -6969,14 +7020,14 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2.56871223449707</v>
+        <v>2.568711757659912</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-0.04250420827805912</v>
+        <v>-0.04250421583286856</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -6997,7 +7048,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2.56871223449707</v>
+        <v>2.568711757659912</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -7008,11 +7059,11 @@
         <v>3.558812141418457</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.3854460198478553</v>
+        <v>0.3854462770320806</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7041,14 +7092,14 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3.563989400863647</v>
+        <v>3.563990116119385</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.00145477177200104</v>
+        <v>0.001454972753595296</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7120,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>3.563989400863647</v>
+        <v>3.563990116119385</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -7080,11 +7131,11 @@
         <v>4.006528377532959</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.1241695546462829</v>
+        <v>0.1241693290371488</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7113,14 +7164,14 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>4.181059837341309</v>
+        <v>4.181058406829834</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.04356176803515321</v>
+        <v>0.04356141099001598</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7141,7 +7192,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>4.181059837341309</v>
+        <v>4.181058406829834</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -7149,14 +7200,14 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>4.411284923553467</v>
+        <v>4.41128396987915</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.05506381041381037</v>
+        <v>0.05506394330039477</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7177,7 +7228,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4.411284923553467</v>
+        <v>4.41128396987915</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -7185,14 +7236,14 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>5.103194236755371</v>
+        <v>5.10319185256958</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.1568498351823857</v>
+        <v>0.1568495448071063</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7213,7 +7264,7 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>5.103194236755371</v>
+        <v>5.10319185256958</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
@@ -7221,14 +7272,14 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>4.956110000610352</v>
+        <v>4.956111907958984</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-0.02882199448448508</v>
+        <v>-0.02882116699895132</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7249,7 +7300,7 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>4.956110000610352</v>
+        <v>4.956111907958984</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -7257,14 +7308,14 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>4.778075695037842</v>
+        <v>4.778077125549316</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0.03592218605934583</v>
+        <v>-0.03592226844671587</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7285,7 +7336,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4.778075695037842</v>
+        <v>4.778077125549316</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -7293,14 +7344,14 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>6.069513320922852</v>
+        <v>6.069514274597168</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.2702840449401422</v>
+        <v>0.270283864222761</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7372,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>6.069513320922852</v>
+        <v>6.069514274597168</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -7329,14 +7380,14 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>5.979395389556885</v>
+        <v>5.979394912719727</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-0.01484763713349335</v>
+        <v>-0.01484787048851988</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7357,7 +7408,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5.979395389556885</v>
+        <v>5.979394912719727</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -7365,14 +7416,14 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>5.722182750701904</v>
+        <v>5.722182273864746</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.04301649616685432</v>
+        <v>-0.04301649959727905</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7393,7 +7444,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>5.722182750701904</v>
+        <v>5.722182273864746</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -7401,14 +7452,14 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5.556884765625</v>
+        <v>5.556884288787842</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.02888722578051672</v>
+        <v>-0.02888722818772815</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7429,7 +7480,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>5.556884765625</v>
+        <v>5.556884288787842</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -7437,14 +7488,14 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>6.235026836395264</v>
+        <v>6.235025405883789</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.1220363745826194</v>
+        <v>0.1220362134342508</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7465,7 +7516,7 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>6.235026836395264</v>
+        <v>6.235025405883789</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
@@ -7473,14 +7524,14 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5.857002258300781</v>
+        <v>5.857003688812256</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>-0.06062918220140889</v>
+        <v>-0.06062873724857742</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7501,7 +7552,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5.857002258300781</v>
+        <v>5.857003688812256</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -7512,11 +7563,11 @@
         <v>6.053802013397217</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.03360076476281404</v>
+        <v>0.03360051231671157</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7552,7 +7603,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7581,14 +7632,14 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>6.951605796813965</v>
+        <v>6.951604843139648</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.001211391988220623</v>
+        <v>0.001211254634403636</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7660,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>6.951605796813965</v>
+        <v>6.951604843139648</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -7617,14 +7668,14 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>5.215310573577881</v>
+        <v>5.215311527252197</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-0.2497689417360024</v>
+        <v>-0.2497687016259206</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7645,7 +7696,7 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>5.215310573577881</v>
+        <v>5.215311527252197</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
@@ -7653,14 +7704,14 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>4.046821117401123</v>
+        <v>4.046820640563965</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-0.2240498316814782</v>
+        <v>-0.2240500650023255</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7681,7 +7732,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>4.046821117401123</v>
+        <v>4.046820640563965</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
@@ -7689,14 +7740,14 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>3.305700063705444</v>
+        <v>3.305699825286865</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>-0.1831365983806144</v>
+        <v>-0.1831365610445778</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7717,7 +7768,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3.305700063705444</v>
+        <v>3.305699825286865</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
@@ -7725,14 +7776,14 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>3.559508323669434</v>
+        <v>3.559507608413696</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.0767789742180931</v>
+        <v>0.0767788355086978</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7753,7 +7804,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.559508323669434</v>
+        <v>3.559507608413696</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
@@ -7761,14 +7812,14 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.823692321777344</v>
+        <v>3.823692083358765</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.07421923875024605</v>
+        <v>0.074219387625583</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7840,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>3.823692321777344</v>
+        <v>3.823692083358765</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
@@ -7800,11 +7851,11 @@
         <v>4.450810432434082</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.164008517914757</v>
+        <v>0.1640085904941517</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7833,14 +7884,14 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.486504554748535</v>
+        <v>4.486504077911377</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.008019690538680679</v>
+        <v>0.008019583403774622</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7861,7 +7912,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>4.486504554748535</v>
+        <v>4.486504077911377</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
@@ -7872,11 +7923,11 @@
         <v>3.361522197723389</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-0.2507480697494133</v>
+        <v>-0.2507479901169969</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7905,14 +7956,14 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>4.075469017028809</v>
+        <v>4.075468063354492</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.2123879532281372</v>
+        <v>0.2123876695250229</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7933,7 +7984,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>4.075469017028809</v>
+        <v>4.075468063354492</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -7944,11 +7995,11 @@
         <v>4.186890125274658</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.02733945658285974</v>
+        <v>0.02733969698402072</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -7977,14 +8028,14 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>4.1609787940979</v>
+        <v>4.160977840423584</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>-0.006188681909835902</v>
+        <v>-0.006188909686129951</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8005,7 +8056,7 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>4.1609787940979</v>
+        <v>4.160977840423584</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
@@ -8013,14 +8064,14 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>4.323929786682129</v>
+        <v>4.323929309844971</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.03916169743892106</v>
+        <v>0.03916182101195664</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8041,7 +8092,7 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>4.323929786682129</v>
+        <v>4.323929309844971</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
@@ -8052,11 +8103,11 @@
         <v>4.993371963500977</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.1548226289151955</v>
+        <v>0.1548227562674951</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8085,14 +8136,14 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>5.387831687927246</v>
+        <v>5.387832641601562</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.07899666343896872</v>
+        <v>0.07899685442700721</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8113,7 +8164,7 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>5.387831687927246</v>
+        <v>5.387832641601562</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
@@ -8124,11 +8175,11 @@
         <v>5.849205493927002</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.08563255734836273</v>
+        <v>0.08563236518577044</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8157,14 +8208,14 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>5.877296924591064</v>
+        <v>5.877295970916748</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.004802606216045779</v>
+        <v>0.00480244317265166</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8185,7 +8236,7 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>5.877296924591064</v>
+        <v>5.877295970916748</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
@@ -8193,14 +8244,14 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>6.717551231384277</v>
+        <v>6.717550277709961</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.1429661147929286</v>
+        <v>0.1429661379912008</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8221,7 +8272,7 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>6.717551231384277</v>
+        <v>6.717550277709961</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -8229,14 +8280,14 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>6.556621074676514</v>
+        <v>6.556621551513672</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>-0.02395666979894417</v>
+        <v>-0.02395646024865339</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8257,7 +8308,7 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6.556621074676514</v>
+        <v>6.556621551513672</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -8268,11 +8319,11 @@
         <v>7.269989967346191</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.1088012994108971</v>
+        <v>0.1088012187721632</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8308,7 +8359,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8395,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8373,14 +8424,14 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>10.56580543518066</v>
+        <v>10.56580352783203</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.1176068331579609</v>
+        <v>0.1176066314065773</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8401,7 +8452,7 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>10.56580543518066</v>
+        <v>10.56580352783203</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -8409,14 +8460,14 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>13.31282997131348</v>
+        <v>13.31283283233643</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2599919668202599</v>
+        <v>0.2599924650565644</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8437,7 +8488,7 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>13.31282997131348</v>
+        <v>13.31283283233643</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -8445,14 +8496,14 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>13.47213745117188</v>
+        <v>13.47213935852051</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.01196646244274691</v>
+        <v>0.01196638823535223</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8473,7 +8524,7 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>13.47213745117188</v>
+        <v>13.47213935852051</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -8481,14 +8532,14 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>12.47993755340576</v>
+        <v>12.47993659973145</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>-0.07364829087902502</v>
+        <v>-0.07364849281799779</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8560,7 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>12.47993755340576</v>
+        <v>12.47993659973145</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -8517,14 +8568,14 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>13.34369659423828</v>
+        <v>13.34369564056396</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.0692118079226125</v>
+        <v>0.06921181321154357</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8545,7 +8596,7 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>13.34369659423828</v>
+        <v>13.34369564056396</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -8553,14 +8604,14 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>13.00253105163574</v>
+        <v>13.00253200531006</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>-0.0255675434609216</v>
+        <v>-0.02556740234817645</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8581,7 +8632,7 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>13.00253105163574</v>
+        <v>13.00253200531006</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -8589,14 +8640,14 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>12.93754291534424</v>
+        <v>12.93754100799561</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>-0.004998114292780631</v>
+        <v>-0.004998333962024648</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8617,7 +8668,7 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>12.93754291534424</v>
+        <v>12.93754100799561</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -8625,14 +8676,14 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>13.65937995910645</v>
+        <v>13.65938186645508</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.05579398255800871</v>
+        <v>0.05579428563846589</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8653,7 +8704,7 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>13.65937995910645</v>
+        <v>13.65938186645508</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -8661,14 +8712,14 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>13.29919147491455</v>
+        <v>13.29919242858887</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>-0.02636931436640821</v>
+        <v>-0.02636938050255189</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8689,7 +8740,7 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>13.29919147491455</v>
+        <v>13.29919242858887</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -8697,14 +8748,14 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>14.95433521270752</v>
+        <v>14.9543342590332</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.1244544633344791</v>
+        <v>0.1244543109915703</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8725,7 +8776,7 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>14.95433521270752</v>
+        <v>14.9543342590332</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -8736,11 +8787,11 @@
         <v>16.18479537963867</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.08228116793085949</v>
+        <v>0.08228123695056544</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8769,14 +8820,14 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>19.93355369567871</v>
+        <v>19.93355178833008</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2316222249405868</v>
+        <v>0.2316221070924096</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8848,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>19.93355369567871</v>
+        <v>19.93355178833008</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -8805,14 +8856,14 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>19.43178939819336</v>
+        <v>19.43178749084473</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>-0.02517184367352054</v>
+        <v>-0.02517184608209688</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8884,7 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>19.43178939819336</v>
+        <v>19.43178749084473</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -8841,14 +8892,14 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>22.31177711486816</v>
+        <v>22.31177139282227</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.1482101137295451</v>
+        <v>0.1482099319650567</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8869,7 +8920,7 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>22.31177711486816</v>
+        <v>22.31177139282227</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -8880,11 +8931,11 @@
         <v>20.64823150634766</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>-0.07455908150910806</v>
+        <v>-0.07455884417181569</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8913,14 +8964,14 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>25.48336410522461</v>
+        <v>25.48336791992188</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.2341669114563416</v>
+        <v>0.234167096203266</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8941,7 +8992,7 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>25.48336410522461</v>
+        <v>25.48336791992188</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
@@ -8949,14 +9000,14 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>32.5691032409668</v>
+        <v>32.56910705566406</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.2780535217596904</v>
+        <v>0.2780534801368559</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -8977,7 +9028,7 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>32.5691032409668</v>
+        <v>32.56910705566406</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
@@ -8985,14 +9036,14 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>29.31838035583496</v>
+        <v>29.31837844848633</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>-0.09981002120570948</v>
+        <v>-0.09981018520470619</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9013,7 +9064,7 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>29.31838035583496</v>
+        <v>29.31837844848633</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
@@ -9021,14 +9072,14 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>24.40889358520508</v>
+        <v>24.40889167785645</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>-0.1674542287481032</v>
+        <v>-0.1674542396420752</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9049,7 +9100,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>24.40889358520508</v>
+        <v>24.40889167785645</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -9060,11 +9111,11 @@
         <v>24.30820846557617</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>-0.004124935826256948</v>
+        <v>-0.004124858007035659</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9093,14 +9144,14 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>27.20470428466797</v>
+        <v>27.20470237731934</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1191571079042555</v>
+        <v>0.1191570294390476</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9121,7 +9172,7 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>27.20470428466797</v>
+        <v>27.20470237731934</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
@@ -9132,11 +9183,11 @@
         <v>18.49174308776855</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>-0.3202740638430636</v>
+        <v>-0.3202740161868048</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9165,14 +9216,14 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>18.61637306213379</v>
+        <v>18.61636734008789</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.006739763459490788</v>
+        <v>0.006739454021604363</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9193,7 +9244,7 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>18.61637306213379</v>
+        <v>18.61636734008789</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
@@ -9201,14 +9252,14 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>15.11703300476074</v>
+        <v>15.11703205108643</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>-0.1879710965016489</v>
+        <v>-0.1879708981389784</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9229,7 +9280,7 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>15.11703300476074</v>
+        <v>15.11703205108643</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
@@ -9237,14 +9288,14 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>18.11271095275879</v>
+        <v>18.11271667480469</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1981657344436987</v>
+        <v>0.198166188547769</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9265,7 +9316,7 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>18.11271095275879</v>
+        <v>18.11271667480469</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
@@ -9273,14 +9324,14 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>15.05221080780029</v>
+        <v>15.05221176147461</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>-0.1689697446694109</v>
+        <v>-0.168969954550624</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9301,7 +9352,7 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>15.05221080780029</v>
+        <v>15.05221176147461</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
@@ -9309,14 +9360,14 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>12.10899066925049</v>
+        <v>12.10898876190186</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>-0.1955340764311234</v>
+        <v>-0.195534254115783</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9337,7 +9388,7 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>12.10899066925049</v>
+        <v>12.10898876190186</v>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
@@ -9345,14 +9396,14 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>13.46363162994385</v>
+        <v>13.46363067626953</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1118706750789171</v>
+        <v>0.1118707714577905</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9373,7 +9424,7 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>13.46363162994385</v>
+        <v>13.46363067626953</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
@@ -9384,11 +9435,11 @@
         <v>16.88548278808594</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.2541551382415801</v>
+        <v>0.2541552270776135</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9424,7 +9475,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9453,14 +9504,14 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>19.49368667602539</v>
+        <v>19.49368858337402</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.3368689099972106</v>
+        <v>0.3368690408023851</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9481,7 +9532,7 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>19.49368667602539</v>
+        <v>19.49368858337402</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -9492,11 +9543,11 @@
         <v>23.16452980041504</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1883093324211624</v>
+        <v>0.1883092161517261</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9525,14 +9576,14 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>27.72012710571289</v>
+        <v>27.72012519836426</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1966626279293711</v>
+        <v>0.1966625455901805</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9553,7 +9604,7 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>27.72012710571289</v>
+        <v>27.72012519836426</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
@@ -9561,14 +9612,14 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>27.69218063354492</v>
+        <v>27.69218254089355</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>-0.001008165368845293</v>
+        <v>-0.001008027823494517</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9589,7 +9640,7 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>27.69218063354492</v>
+        <v>27.69218254089355</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
@@ -9600,11 +9651,11 @@
         <v>37.75653076171875</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.3634365332711422</v>
+        <v>0.3634364393620109</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9640,7 +9691,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9676,7 +9727,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9705,14 +9756,14 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>49.2590446472168</v>
+        <v>49.25904083251953</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.05619664404476143</v>
+        <v>0.05619656225124547</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9784,7 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>49.2590446472168</v>
+        <v>49.25904083251953</v>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
@@ -9741,14 +9792,14 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>43.41799926757812</v>
+        <v>43.41800308227539</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>-0.1185781295896224</v>
+        <v>-0.1185779838893664</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9820,7 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>43.41799926757812</v>
+        <v>43.41800308227539</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
@@ -9777,14 +9828,14 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>40.70405960083008</v>
+        <v>40.70406341552734</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>-0.06250724843451383</v>
+        <v>-0.06250724294263921</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9805,7 +9856,7 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>40.70405960083008</v>
+        <v>40.70406341552734</v>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
@@ -9816,11 +9867,11 @@
         <v>46.68291091918945</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.1468858727358351</v>
+        <v>0.1468857652521582</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9856,7 +9907,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9885,14 +9936,14 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>61.41783142089844</v>
+        <v>61.41782760620117</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.242417620068432</v>
+        <v>0.2424175429011504</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9913,7 +9964,7 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>61.41783142089844</v>
+        <v>61.41782760620117</v>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
@@ -9921,14 +9972,14 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>78.97163391113281</v>
+        <v>78.97164154052734</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.2858095456014653</v>
+        <v>0.2858097496850216</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -9949,7 +10000,7 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>78.97163391113281</v>
+        <v>78.97164154052734</v>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
@@ -9960,11 +10011,11 @@
         <v>90.19991302490234</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.1421811675620739</v>
+        <v>0.1421810572167577</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10000,7 +10051,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10029,14 +10080,14 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>109.443603515625</v>
+        <v>109.4436111450195</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.2688710508743717</v>
+        <v>0.2688711393283107</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10057,7 +10108,7 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>109.443603515625</v>
+        <v>109.4436111450195</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
@@ -10068,11 +10119,11 @@
         <v>123.3367233276367</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.1269431868627044</v>
+        <v>0.1269431083026671</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10108,7 +10159,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10137,14 +10188,14 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>119.173583984375</v>
+        <v>119.1735763549805</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.02008214562373478</v>
+        <v>0.02008208031891745</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10165,7 +10216,7 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>119.173583984375</v>
+        <v>119.1735763549805</v>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
@@ -10176,11 +10227,11 @@
         <v>121.2505416870117</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.01742800403576883</v>
+        <v>0.01742806917067452</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10216,7 +10267,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10303,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10281,14 +10332,14 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>134.0897216796875</v>
+        <v>134.0897369384766</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>-0.02857691784311611</v>
+        <v>-0.02857680729967016</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10309,7 +10360,7 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>134.0897216796875</v>
+        <v>134.0897369384766</v>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
@@ -10320,11 +10371,11 @@
         <v>119.8909378051758</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>-0.1058901733604136</v>
+        <v>-0.1058902751059577</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10353,14 +10404,14 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>124.7337036132812</v>
+        <v>124.7337112426758</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.04039309306242167</v>
+        <v>0.04039315669854515</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10381,7 +10432,7 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>124.7337036132812</v>
+        <v>124.7337112426758</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
@@ -10392,11 +10443,11 @@
         <v>108.2283248901367</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>-0.1323249309931265</v>
+        <v>-0.1323249840648691</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10432,7 +10483,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10461,14 +10512,14 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>134.9408874511719</v>
+        <v>134.9409027099609</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>0.240635387014742</v>
+        <v>0.2406355273027898</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10489,7 +10540,7 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>134.9408874511719</v>
+        <v>134.9409027099609</v>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
@@ -10497,14 +10548,14 @@
         </is>
       </c>
       <c r="F103" s="3" t="n">
-        <v>157.7798614501953</v>
+        <v>157.7798461914062</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0.1692516955417807</v>
+        <v>0.1692514502480753</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10525,7 +10576,7 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>157.7798614501953</v>
+        <v>157.7798461914062</v>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
@@ -10533,14 +10584,14 @@
         </is>
       </c>
       <c r="F104" s="3" t="n">
-        <v>177.6334075927734</v>
+        <v>177.6334228515625</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>0.1258306729394936</v>
+        <v>0.1258308785272324</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10561,7 +10612,7 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>177.6334075927734</v>
+        <v>177.6334228515625</v>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
@@ -10569,14 +10620,14 @@
         </is>
       </c>
       <c r="F105" s="3" t="n">
-        <v>173.9483184814453</v>
+        <v>173.9483032226562</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>-0.02074547328268472</v>
+        <v>-0.02074564330151807</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10648,7 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>173.9483184814453</v>
+        <v>173.9483032226562</v>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
@@ -10608,11 +10659,11 @@
         <v>186.3423309326172</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.07125111963927333</v>
+        <v>0.07125121360969189</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10648,7 +10699,7 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10684,7 +10735,7 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10720,7 +10771,7 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10756,7 +10807,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10792,7 +10843,7 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10828,7 +10879,7 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10864,7 +10915,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10900,7 +10951,7 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -10936,12 +10987,48 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>200.0899963378906</v>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>200.75</v>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>0.003298534030631073</v>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H115"/>
+  <autoFilter ref="A1:H116"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11026,17 +11113,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>-0.9523233980697987</v>
+        <v>-0.06349317981017011</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-0.9523233980697987</v>
+        <v>-0.06349317981017011</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>-0.9523233980697987</v>
+        <v>-0.06349317981017011</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0</v>
@@ -11048,7 +11135,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/%5ESP500TR?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -11065,17 +11152,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>-5.123049341072095</v>
+        <v>0.3298534030631073</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-5.123049341072095</v>
+        <v>0.3298534030631073</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>-5.123049341072095</v>
+        <v>0.3298534030631073</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
@@ -11087,7 +11174,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1783209600&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
+          <t>https://query2.finance.yahoo.com/v8/finance/chart/NVDA?period1=1480550400&amp;period2=1785888000&amp;interval=1d&amp;events=history&amp;includeAdjustedClose=true</t>
         </is>
       </c>
     </row>
@@ -11135,10 +11222,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.520614035087721</v>
+        <v>3.519478260869565</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1.307550607795648</v>
+        <v>1.295628487903424</v>
       </c>
     </row>
     <row r="3">
@@ -11148,10 +11235,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3.448521353622169</v>
+        <v>3.448012329545969</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1.205625872082727</v>
+        <v>1.194520884974981</v>
       </c>
     </row>
     <row r="4">
@@ -11161,10 +11248,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>95.6140350877193</v>
+        <v>95.65217391304348</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>70.17543859649122</v>
+        <v>69.56521739130434</v>
       </c>
     </row>
     <row r="5">
@@ -11174,10 +11261,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>4.385964912280701</v>
+        <v>4.347826086956522</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>29.82456140350877</v>
+        <v>30.43478260869566</v>
       </c>
     </row>
     <row r="6">
@@ -11187,10 +11274,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3.721926605504589</v>
+        <v>3.718909090909091</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3.616317163875842</v>
+        <v>3.616317163875843</v>
       </c>
     </row>
     <row r="7">
@@ -11200,10 +11287,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>-0.8680000000000002</v>
+        <v>-0.868</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-4.124841288863633</v>
+        <v>-4.008802771462106</v>
       </c>
     </row>
     <row r="8">
@@ -11239,10 +11326,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3.520614035087721</v>
+        <v>3.519478260869565</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1.307550607795648</v>
+        <v>1.295628487903424</v>
       </c>
     </row>
     <row r="11">
@@ -11252,10 +11339,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>4.001514378174758</v>
+        <v>3.983943837120484</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>4.528627069815164</v>
+        <v>4.510533237481415</v>
       </c>
     </row>
     <row r="12">
@@ -11265,10 +11352,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2.626664430542024</v>
+        <v>2.638684739182457</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.438794641537164</v>
+        <v>-0.4323133842228436</v>
       </c>
     </row>
     <row r="13">
@@ -11278,10 +11365,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>8.443105350916397</v>
+        <v>8.543303212889626</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.5239364253231313</v>
+        <v>0.5443369456982401</v>
       </c>
     </row>
     <row r="14">
@@ -11291,10 +11378,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.8798204135639283</v>
+        <v>0.8834156315349503</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.2887300251572749</v>
+        <v>0.287245081609658</v>
       </c>
     </row>
     <row r="15">
@@ -11304,10 +11391,10 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>14.52592048115421</v>
+        <v>14.58478488287688</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.4680407905555371</v>
+        <v>0.4658018365243973</v>
       </c>
     </row>
     <row r="16">
@@ -11317,10 +11404,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>93.47695852534564</v>
+        <v>94.25806451612902</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.062862778510679</v>
+        <v>2.061929277735463</v>
       </c>
     </row>
     <row r="17">
@@ -11330,7 +11417,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>3.553834897000299</v>
+        <v>3.552270603645034</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>0</v>
@@ -11343,7 +11430,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.02540694158567561</v>
+        <v>-0.02530998899887835</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>1</v>
@@ -11365,7 +11452,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -11393,10 +11480,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.520614035087721</v>
+        <v>3.519478260869565</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4.759474260033616</v>
+        <v>4.720955480839763</v>
       </c>
     </row>
     <row r="3">
@@ -11406,10 +11493,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3.448521353622169</v>
+        <v>3.448012329545969</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3.87448954575127</v>
+        <v>3.843132845486785</v>
       </c>
     </row>
     <row r="4">
@@ -11419,10 +11506,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>95.6140350877193</v>
+        <v>95.65217391304348</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>64.03508771929825</v>
+        <v>64.34782608695652</v>
       </c>
     </row>
     <row r="5">
@@ -11432,10 +11519,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>4.385964912280701</v>
+        <v>4.347826086956522</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>35.96491228070175</v>
+        <v>35.65217391304348</v>
       </c>
     </row>
     <row r="6">
@@ -11445,10 +11532,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3.721926605504589</v>
+        <v>3.718909090909091</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>12.37045721245495</v>
+        <v>12.20774455035246</v>
       </c>
     </row>
     <row r="7">
@@ -11458,10 +11545,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>-0.8680000000000002</v>
+        <v>-0.868</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-8.791788069887311</v>
+        <v>-8.791785766573398</v>
       </c>
     </row>
     <row r="8">
@@ -11474,7 +11561,7 @@
         <v>21.97</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>38.54460198478553</v>
+        <v>38.54462770320806</v>
       </c>
     </row>
     <row r="9">
@@ -11487,7 +11574,7 @@
         <v>-2.2</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>-32.02740638430635</v>
+        <v>-32.02740161868049</v>
       </c>
     </row>
     <row r="10">
@@ -11497,10 +11584,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3.520614035087721</v>
+        <v>3.519478260869565</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4.759474260033616</v>
+        <v>4.720955480839763</v>
       </c>
     </row>
     <row r="11">
@@ -11510,10 +11597,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>4.001514378174758</v>
+        <v>3.983943837120484</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>13.50731527656471</v>
+        <v>13.45428483462503</v>
       </c>
     </row>
     <row r="12">
@@ -11523,10 +11610,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2.626664430542024</v>
+        <v>2.638684739182457</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.03004051713995683</v>
+        <v>-0.02170278602512823</v>
       </c>
     </row>
     <row r="13">
@@ -11536,10 +11623,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>8.443105350916397</v>
+        <v>8.543303212889626</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.1259024146109362</v>
+        <v>0.1472125616225912</v>
       </c>
     </row>
     <row r="14">
@@ -11549,10 +11636,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.8798204135639283</v>
+        <v>0.8834156315349503</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.3523627132840631</v>
+        <v>0.3508886231314379</v>
       </c>
     </row>
     <row r="15">
@@ -11562,10 +11649,10 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>14.52592048115421</v>
+        <v>14.58478488287688</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.6696211014887262</v>
+        <v>0.6671086844656693</v>
       </c>
     </row>
     <row r="16">
@@ -11575,10 +11662,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>93.47695852534564</v>
+        <v>94.25806451612902</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.505229656636168</v>
+        <v>2.50614502548762</v>
       </c>
     </row>
   </sheetData>
@@ -11599,7 +11686,7 @@
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11631,13 +11718,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.553834897000299</v>
+        <v>3.552270603645034</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.3917940053800512</v>
+        <v>0.3882041321353366</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9.070671955669612</v>
+        <v>9.150522391674681</v>
       </c>
     </row>
     <row r="3">
@@ -11647,13 +11734,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.02540694158567561</v>
+        <v>-0.02530998899887835</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.08345823680342875</v>
+        <v>0.08305537019862617</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>-0.3044270111471107</v>
+        <v>-0.3047363335850498</v>
       </c>
     </row>
   </sheetData>
@@ -11712,16 +11799,16 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.3520359755657159</v>
+        <v>0.3518264189608741</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.000139934911654884</v>
+        <v>0.0001322452612779051</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>6.230754539099949e-05</v>
+        <v>5.670595079073566e-05</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>7.123636759103555e-05</v>
+        <v>6.444721769888924e-05</v>
       </c>
     </row>
     <row r="3">
@@ -11731,16 +11818,16 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.1416351891195366</v>
+        <v>-0.140188581203098</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.1254749098985961</v>
+        <v>0.1277568081678594</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.4456255431559045</v>
+        <v>0.4457248592970166</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.3138843342034664</v>
+        <v>0.3066839911331238</v>
       </c>
     </row>
     <row r="4">
@@ -11750,16 +11837,16 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.01316612202744002</v>
+        <v>0.01465478878200355</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.8867407299564685</v>
+        <v>0.8735038164340262</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.9769962252070046</v>
+        <v>0.9787208520808428</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.8757247539116003</v>
+        <v>0.8799447076786946</v>
       </c>
     </row>
   </sheetData>

--- a/Project_1_May2026_Update.xlsx
+++ b/Project_1_May2026_Update.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_and_Method" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LSQ_Returns" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP500TR_Returns" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NVIDIA_Returns" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verification" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Updated_Table_2" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Updated_Table_4" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regression" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Serial_Correlation" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Newey_West" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MPPM" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Source_and_Method" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="LSQ_Returns" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SP500TR_Returns" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="NVIDIA_Returns" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Verification" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Updated_Table_2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Updated_Table_4" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Regression" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Serial_Correlation" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Newey_West" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="MPPM" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Source_and_Method'!$A$1:$B$8</definedName>
@@ -506,7 +506,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>data\LSQ_latest_spartan.pdf</t>
+          <t>data/LSQ_latest_spartan.pdf</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10T18:30:47</t>
+          <t>2026-08-20T13:41:56</t>
         </is>
       </c>
     </row>
@@ -620,19 +620,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.519478260869565</v>
+        <v>3.519478260869567</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0.3715046783874216</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9.473577226931436</v>
+        <v>9.473577226931443</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>0.5241488622315456</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>6.714654012384019</v>
+        <v>6.714654012384022</v>
       </c>
     </row>
     <row r="3">
@@ -642,19 +642,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3.552270603645034</v>
+        <v>3.552270603645037</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0.3882041321353366</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>9.150522391674681</v>
+        <v>9.150522391674688</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.5791256161049188</v>
+        <v>0.5791256161049186</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>6.133851628834663</v>
+        <v>6.133851628834669</v>
       </c>
     </row>
     <row r="4">
@@ -664,19 +664,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.02530998899887835</v>
+        <v>-0.02530998899887851</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0.08305537019862617</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-0.3047363335850498</v>
+        <v>-0.3047363335850518</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.1058495973296159</v>
+        <v>0.1058495973296158</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-0.2391127565659318</v>
+        <v>-0.2391127565659335</v>
       </c>
     </row>
   </sheetData>
@@ -762,7 +762,7 @@
         <v>35.16</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>46.57265489959188</v>
+        <v>46.57265489959113</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>115</v>
@@ -773,13 +773,13 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.03263370241484337</v>
+        <v>0.03263370241484307</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>47.01293292530049</v>
+        <v>47.01293292530011</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>11.85293292530049</v>
+        <v>11.85293292530012</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>3</v>
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.009824109332120121</v>
+        <v>0.009824109332120233</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>12.44724565179145</v>
+        <v>12.44724565179176</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>4.077245651791451</v>
+        <v>4.077245651791761</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>3</v>
@@ -828,7 +828,7 @@
         <v>21.19</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>27.82296044992847</v>
+        <v>27.82295882614039</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>115</v>
@@ -839,13 +839,13 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.0198279274293732</v>
+        <v>0.01982792636944819</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>26.56767680106729</v>
+        <v>26.56767522253958</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>5.377676801067285</v>
+        <v>5.377675222539576</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3</v>
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2.625491619110107</v>
+        <v>2.62549090385437</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -6912,10 +6912,10 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.685507535934448</v>
+        <v>2.685508012771606</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.02285892531040834</v>
+        <v>0.02285938558352174</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -6940,7 +6940,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2.685507535934448</v>
+        <v>2.685508012771606</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -6948,10 +6948,10 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2.499259948730469</v>
+        <v>2.499260425567627</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>-0.06935284474603898</v>
+        <v>-0.06935283243179036</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.499259948730469</v>
+        <v>2.499260425567627</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -6984,10 +6984,10 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2.682739496231079</v>
+        <v>2.682739734649658</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.07341355091686697</v>
+        <v>0.0734134415145471</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2.682739496231079</v>
+        <v>2.682739734649658</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -7020,10 +7020,10 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2.568711757659912</v>
+        <v>2.568711996078491</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-0.04250421583286856</v>
+        <v>-0.04250421205546351</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2.568711757659912</v>
+        <v>2.568711996078491</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>3.558812141418457</v>
+        <v>3.558812379837036</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.3854462770320806</v>
+        <v>0.3854462412563477</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3.558812141418457</v>
+        <v>3.558812379837036</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -7092,10 +7092,10 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3.563990116119385</v>
+        <v>3.56398868560791</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.001454972753595296</v>
+        <v>0.001454503699099385</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>3.563990116119385</v>
+        <v>3.56398868560791</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>4.006528377532959</v>
+        <v>4.006528854370117</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.1241693290371488</v>
+        <v>0.1241699140486252</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>4.006528377532959</v>
+        <v>4.006528854370117</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -7164,10 +7164,10 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>4.181058406829834</v>
+        <v>4.181059837341309</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.04356141099001598</v>
+        <v>0.04356164383561634</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>4.181058406829834</v>
+        <v>4.181059837341309</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -7200,10 +7200,10 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>4.41128396987915</v>
+        <v>4.411285400390625</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.05506394330039477</v>
+        <v>0.05506392446076891</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4.41128396987915</v>
+        <v>4.411285400390625</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -7236,10 +7236,10 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>5.10319185256958</v>
+        <v>5.103194236755371</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.1568495448071063</v>
+        <v>0.1568497101328961</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>5.10319185256958</v>
+        <v>5.103194236755371</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>4.956111907958984</v>
+        <v>4.956111431121826</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>-0.02882116699895132</v>
+        <v>-0.02882171416760748</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>4.956111907958984</v>
+        <v>4.956111431121826</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -7308,10 +7308,10 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>4.778077125549316</v>
+        <v>4.778075218200684</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0.03592226844671587</v>
+        <v>-0.03592256053872533</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4.778077125549316</v>
+        <v>4.778075218200684</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -7344,10 +7344,10 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>6.069514274597168</v>
+        <v>6.069513320922852</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.270283864222761</v>
+        <v>0.2702841717105691</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>6.069514274597168</v>
+        <v>6.069513320922852</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -7380,10 +7380,10 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>5.979394912719727</v>
+        <v>5.979395866394043</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-0.01484787048851988</v>
+        <v>-0.01484755857082565</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5.979394912719727</v>
+        <v>5.979395866394043</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -7416,10 +7416,10 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>5.722182273864746</v>
+        <v>5.722181797027588</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.04301649959727905</v>
+        <v>-0.0430167319765653</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>5.722182273864746</v>
+        <v>5.722181797027588</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -7452,10 +7452,10 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5.556884288787842</v>
+        <v>5.556883811950684</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.02888722818772815</v>
+        <v>-0.02888723059494003</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -7480,7 +7480,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>5.556884288787842</v>
+        <v>5.556883811950684</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>6.235025405883789</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.1220362134342508</v>
+        <v>0.1220363097163717</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>6.951604843139648</v>
+        <v>6.951605796813965</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.001211254634403636</v>
+        <v>0.001211391988220623</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>6.951604843139648</v>
+        <v>6.951605796813965</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         <v>5.215311527252197</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-0.2497687016259206</v>
+        <v>-0.2497688045483735</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -7740,10 +7740,10 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>3.305699825286865</v>
+        <v>3.305700540542603</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>-0.1831365610445778</v>
+        <v>-0.1831363842994731</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3.305699825286865</v>
+        <v>3.305700540542603</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
@@ -7776,10 +7776,10 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>3.559507608413696</v>
+        <v>3.559508323669434</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.0767788355086978</v>
+        <v>0.07677881889603055</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.559507608413696</v>
+        <v>3.559508323669434</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
@@ -7812,10 +7812,10 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.823692083358765</v>
+        <v>3.823691368103027</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.074219387625583</v>
+        <v>0.07421897082719897</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>3.823692083358765</v>
+        <v>3.823691368103027</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         <v>4.450810432434082</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.1640085904941517</v>
+        <v>0.1640088082323901</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -7884,10 +7884,10 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.486504077911377</v>
+        <v>4.486505031585693</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.008019583403774622</v>
+        <v>0.008019797673586959</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>4.486504077911377</v>
+        <v>4.486505031585693</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
         <v>3.361522197723389</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-0.2507479901169969</v>
+        <v>-0.2507481493818129</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -7956,10 +7956,10 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>4.075468063354492</v>
+        <v>4.075469017028809</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.2123876695250229</v>
+        <v>0.2123879532281372</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>4.075468063354492</v>
+        <v>4.075469017028809</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -7992,10 +7992,10 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>4.186890125274658</v>
+        <v>4.186889171600342</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.02733969698402072</v>
+        <v>0.02733922257928567</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>4.186890125274658</v>
+        <v>4.186889171600342</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
@@ -8028,10 +8028,10 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>4.160977840423584</v>
+        <v>4.160976886749268</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>-0.006188909686129951</v>
+        <v>-0.006188911095817207</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>4.160977840423584</v>
+        <v>4.160976886749268</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>4.323929309844971</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.03916182101195664</v>
+        <v>0.0391620591824553</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -8100,10 +8100,10 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>4.993371963500977</v>
+        <v>4.993372917175293</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.1548227562674951</v>
+        <v>0.1548229768248279</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>4.993371963500977</v>
+        <v>4.993372917175293</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
@@ -8136,10 +8136,10 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>5.387832641601562</v>
+        <v>5.387831687927246</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.07899685442700721</v>
+        <v>0.07899645736355199</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>5.387832641601562</v>
+        <v>5.387831687927246</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
@@ -8172,10 +8172,10 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>5.849205493927002</v>
+        <v>5.849206924438477</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.08563236518577044</v>
+        <v>0.08563282285618801</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>5.849205493927002</v>
+        <v>5.849206924438477</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>5.877295970916748</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.00480244317265166</v>
+        <v>0.004802197433110722</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -8244,10 +8244,10 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>6.717550277709961</v>
+        <v>6.717552185058594</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.1429661379912008</v>
+        <v>0.1429664625194604</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>6.717550277709961</v>
+        <v>6.717552185058594</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>6.556621551513672</v>
+        <v>6.556621074676514</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>-0.02395646024865339</v>
+        <v>-0.02395680836540848</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6.556621551513672</v>
+        <v>6.556621074676514</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -8316,10 +8316,10 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>7.269989967346191</v>
+        <v>7.26999044418335</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.1088012187721632</v>
+        <v>0.1088013721369481</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>7.269989967346191</v>
+        <v>7.26999044418335</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -8352,10 +8352,10 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>8.830544471740723</v>
+        <v>8.830543518066406</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2146570368602847</v>
+        <v>0.2146568260115995</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>8.830544471740723</v>
+        <v>8.830543518066406</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -8388,10 +8388,10 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>9.45395565032959</v>
+        <v>9.453957557678223</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.07059713934785017</v>
+        <v>0.07059747096386237</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>9.45395565032959</v>
+        <v>9.453957557678223</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -8424,10 +8424,10 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>10.56580352783203</v>
+        <v>10.56580543518066</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.1176066314065773</v>
+        <v>0.1176066076792814</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>10.56580352783203</v>
+        <v>10.56580543518066</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -8460,10 +8460,10 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>13.31283283233643</v>
+        <v>13.31282806396484</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2599924650565644</v>
+        <v>0.2599917862993668</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>13.31283283233643</v>
+        <v>13.31282806396484</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -8496,10 +8496,10 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>13.47213935852051</v>
+        <v>13.47214031219482</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.01196638823535223</v>
+        <v>0.01196682233590973</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>13.47213935852051</v>
+        <v>13.47214031219482</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -8532,10 +8532,10 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>12.47993659973145</v>
+        <v>12.47994041442871</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>-0.07364849281799779</v>
+        <v>-0.07364827523864081</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>12.47993659973145</v>
+        <v>12.47994041442871</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -8568,10 +8568,10 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>13.34369564056396</v>
+        <v>13.3436975479126</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.06921181321154357</v>
+        <v>0.06921163922267226</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>13.34369564056396</v>
+        <v>13.3436975479126</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>13.00253200531006</v>
+        <v>13.00253009796143</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>-0.02556740234817645</v>
+        <v>-0.02556768457364667</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>13.00253200531006</v>
+        <v>13.00253009796143</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -8640,10 +8640,10 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>12.93754100799561</v>
+        <v>12.93754291534424</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>-0.004998333962024648</v>
+        <v>-0.004998041314080548</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>12.93754100799561</v>
+        <v>12.93754291534424</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -8676,10 +8676,10 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>13.65938186645508</v>
+        <v>13.65938091278076</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.05579428563846589</v>
+        <v>0.05579405627172118</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>13.65938186645508</v>
+        <v>13.65938091278076</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -8712,10 +8712,10 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>13.29919242858887</v>
+        <v>13.29919147491455</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>-0.02636938050255189</v>
+        <v>-0.0263693823436163</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>13.29919242858887</v>
+        <v>13.29919147491455</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -8748,10 +8748,10 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>14.9543342590332</v>
+        <v>14.95433521270752</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.1244543109915703</v>
+        <v>0.1244544633344791</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>14.9543342590332</v>
+        <v>14.95433521270752</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -8784,10 +8784,10 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>16.18479537963867</v>
+        <v>16.18479347229004</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.08228123695056544</v>
+        <v>0.0822810403859966</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>16.18479537963867</v>
+        <v>16.18479347229004</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -8820,10 +8820,10 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>19.93355178833008</v>
+        <v>19.93355560302734</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2316221070924096</v>
+        <v>0.2316224879332291</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>19.93355178833008</v>
+        <v>19.93355560302734</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -8856,10 +8856,10 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>19.43178749084473</v>
+        <v>19.43178939819336</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>-0.02517184608209688</v>
+        <v>-0.02517193695026387</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>19.43178749084473</v>
+        <v>19.43178939819336</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>22.31177139282227</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.1482099319650567</v>
+        <v>0.1482098192612498</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -8928,10 +8928,10 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>20.64823150634766</v>
+        <v>20.64822959899902</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>-0.07455884417181569</v>
+        <v>-0.07455892965801925</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>20.64823150634766</v>
+        <v>20.64822959899902</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
@@ -8964,10 +8964,10 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>25.48336791992188</v>
+        <v>25.48336029052734</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.234167096203266</v>
+        <v>0.2341668407136812</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -8992,7 +8992,7 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>25.48336791992188</v>
+        <v>25.48336029052734</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
@@ -9000,10 +9000,10 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>32.56910705566406</v>
+        <v>32.5691032409668</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.2780534801368559</v>
+        <v>0.2780537130761895</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>32.56910705566406</v>
+        <v>32.5691032409668</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>29.31837844848633</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>-0.09981018520470619</v>
+        <v>-0.0998100797688396</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -9072,10 +9072,10 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>24.40889167785645</v>
+        <v>24.40888595581055</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>-0.1674542396420752</v>
+        <v>-0.167454434811324</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>24.40889167785645</v>
+        <v>24.40888595581055</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>24.30820846557617</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>-0.004124858007035659</v>
+        <v>-0.004124624549298961</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>27.20470237731934</v>
+        <v>27.20470428466797</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1191570294390476</v>
+        <v>0.1191571079042555</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>27.20470237731934</v>
+        <v>27.20470428466797</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
@@ -9180,10 +9180,10 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>18.49174308776855</v>
+        <v>18.49174118041992</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>-0.3202740161868048</v>
+        <v>-0.3202741339540492</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -9208,7 +9208,7 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>18.49174308776855</v>
+        <v>18.49174118041992</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
@@ -9216,10 +9216,10 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>18.61636734008789</v>
+        <v>18.61636924743652</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.006739454021604363</v>
+        <v>0.006739661008697384</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -9244,7 +9244,7 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>18.61636734008789</v>
+        <v>18.61636924743652</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
         <v>15.11703205108643</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>-0.1879708981389784</v>
+        <v>-0.1879709813357917</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -9288,10 +9288,10 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>18.11271667480469</v>
+        <v>18.11271095275879</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.198166188547769</v>
+        <v>0.19816581003128</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>18.11271667480469</v>
+        <v>18.11271095275879</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
@@ -9324,10 +9324,10 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>15.05221176147461</v>
+        <v>15.05220985412598</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>-0.168969954550624</v>
+        <v>-0.1689697973216241</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>15.05221176147461</v>
+        <v>15.05220985412598</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
@@ -9360,10 +9360,10 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>12.10898876190186</v>
+        <v>12.10898971557617</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>-0.195534254115783</v>
+        <v>-0.1955340888197248</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>12.10898876190186</v>
+        <v>12.10898971557617</v>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
@@ -9396,10 +9396,10 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>13.46363067626953</v>
+        <v>13.46363258361816</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1118707714577905</v>
+        <v>0.1118708414046692</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>13.46363067626953</v>
+        <v>13.46363258361816</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>16.88548278808594</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.2541552270776135</v>
+        <v>0.2541550494055593</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -9468,10 +9468,10 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>14.58159923553467</v>
+        <v>14.5816011428833</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>-0.13644167486741</v>
+        <v>-0.1364415619095126</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>14.58159923553467</v>
+        <v>14.5816011428833</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
@@ -9504,10 +9504,10 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>19.49368858337402</v>
+        <v>19.49368667602539</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.3368690408023851</v>
+        <v>0.3368687351278623</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>19.49368858337402</v>
+        <v>19.49368667602539</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>23.16452980041504</v>
+        <v>23.16453170776367</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1883092161517261</v>
+        <v>0.1883094302655908</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>23.16452980041504</v>
+        <v>23.16453170776367</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -9576,10 +9576,10 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>27.72012519836426</v>
+        <v>27.72012138366699</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1966625455901805</v>
+        <v>0.1966622823795958</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>27.72012519836426</v>
+        <v>27.72012138366699</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
@@ -9612,10 +9612,10 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>27.69218254089355</v>
+        <v>27.69218063354492</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>-0.001008027823494517</v>
+        <v>-0.00100795915484464</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>27.69218254089355</v>
+        <v>27.69218063354492</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>37.75653076171875</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.3634364393620109</v>
+        <v>0.3634365332711422</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -9684,10 +9684,10 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>42.21975326538086</v>
+        <v>42.21974945068359</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.1182106092275659</v>
+        <v>0.1182105081934617</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>42.21975326538086</v>
+        <v>42.21974945068359</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
@@ -9720,10 +9720,10 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>46.63813781738281</v>
+        <v>46.63814544677734</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.1046520694763253</v>
+        <v>0.1046523499921483</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>46.63813781738281</v>
+        <v>46.63814544677734</v>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>49.25904083251953</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.05619656225124547</v>
+        <v>0.05619638947121319</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -9792,10 +9792,10 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>43.41800308227539</v>
+        <v>43.41799926757812</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>-0.1185779838893664</v>
+        <v>-0.1185780613309324</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>43.41800308227539</v>
+        <v>43.41799926757812</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         <v>40.70406341552734</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>-0.06250724294263921</v>
+        <v>-0.06250716057470163</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -9864,10 +9864,10 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>46.68291091918945</v>
+        <v>46.68291473388672</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.1468857652521582</v>
+        <v>0.1468858589700071</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>46.68291091918945</v>
+        <v>46.68291473388672</v>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
@@ -9900,10 +9900,10 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>49.43412780761719</v>
+        <v>49.43413162231445</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.05893413316042428</v>
+        <v>0.05893412834461786</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>49.43412780761719</v>
+        <v>49.43413162231445</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
@@ -9936,10 +9936,10 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>61.41782760620117</v>
+        <v>61.41783142089844</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.2424175429011504</v>
+        <v>0.2424175241944488</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>61.41782760620117</v>
+        <v>61.41783142089844</v>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
@@ -9972,10 +9972,10 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>78.97164154052734</v>
+        <v>78.97162628173828</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.2858097496850216</v>
+        <v>0.2858094213803009</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>78.97164154052734</v>
+        <v>78.97162628173828</v>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>90.19991302490234</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.1421810572167577</v>
+        <v>0.1421812779074114</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -10080,10 +10080,10 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>109.4436111450195</v>
+        <v>109.4435958862305</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.2688711393283107</v>
+        <v>0.2688709624204324</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>109.4436111450195</v>
+        <v>109.4435958862305</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
@@ -10116,10 +10116,10 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>123.3367233276367</v>
+        <v>123.3367309570312</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.1269431083026671</v>
+        <v>0.1269433351334972</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>123.3367233276367</v>
+        <v>123.3367309570312</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>116.8274383544922</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>-0.05277653562964368</v>
+        <v>-0.05277659422323111</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -10224,10 +10224,10 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>121.2505416870117</v>
+        <v>121.2505493164062</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.01742806917067452</v>
+        <v>0.01742813318985359</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>121.2505416870117</v>
+        <v>121.2505493164062</v>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         <v>132.5528717041016</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>0.09321467648585813</v>
+        <v>0.09321460769799583</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -10296,10 +10296,10 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>138.0343170166016</v>
+        <v>138.0343322753906</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.04135289746672743</v>
+        <v>0.04135301258146518</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>138.0343170166016</v>
+        <v>138.0343322753906</v>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>134.0897369384766</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>-0.02857680729967016</v>
+        <v>-0.02857691468412549</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -10404,10 +10404,10 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>124.7337112426758</v>
+        <v>124.7337036132812</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.04039315669854515</v>
+        <v>0.04039309306242167</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>124.7337112426758</v>
+        <v>124.7337036132812</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>108.2283248901367</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>-0.1323249840648691</v>
+        <v>-0.1323249309931265</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -10548,10 +10548,10 @@
         </is>
       </c>
       <c r="F103" s="3" t="n">
-        <v>157.7798461914062</v>
+        <v>157.7798614501953</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0.1692514502480753</v>
+        <v>0.1692515633256428</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -10576,7 +10576,7 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>157.7798461914062</v>
+        <v>157.7798614501953</v>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
@@ -10584,10 +10584,10 @@
         </is>
       </c>
       <c r="F104" s="3" t="n">
-        <v>177.6334228515625</v>
+        <v>177.6334075927734</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>0.1258308785272324</v>
+        <v>0.1258306729394936</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -10612,7 +10612,7 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>177.6334228515625</v>
+        <v>177.6334075927734</v>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>173.9483032226562</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>-0.02074564330151807</v>
+        <v>-0.02074555918313137</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -10764,10 +10764,10 @@
         </is>
       </c>
       <c r="F109" s="3" t="n">
-        <v>186.2727966308594</v>
+        <v>186.2728118896484</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>0.05373093153479269</v>
+        <v>0.05373101785259271</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>186.2727966308594</v>
+        <v>186.2728118896484</v>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         <v>190.8971710205078</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0.02482581715253174</v>
+        <v>0.02482573320254033</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.519478260869565</v>
+        <v>3.519478260869567</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1.295628487903424</v>
@@ -11274,10 +11274,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3.718909090909091</v>
+        <v>3.718909090909092</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3.616317163875843</v>
+        <v>3.616317163875842</v>
       </c>
     </row>
     <row r="7">
@@ -11287,7 +11287,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>-0.868</v>
+        <v>-0.8680000000000002</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>-4.008802771462106</v>
@@ -11326,7 +11326,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3.519478260869565</v>
+        <v>3.519478260869567</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>1.295628487903424</v>
@@ -11342,7 +11342,7 @@
         <v>3.983943837120484</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>4.510533237481415</v>
+        <v>4.510533237481414</v>
       </c>
     </row>
     <row r="12">
@@ -11352,10 +11352,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2.638684739182457</v>
+        <v>2.638684739182456</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.4323133842228436</v>
+        <v>-0.4323133842228444</v>
       </c>
     </row>
     <row r="13">
@@ -11365,10 +11365,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>8.543303212889626</v>
+        <v>8.54330321288962</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.5443369456982401</v>
+        <v>0.5443369456982423</v>
       </c>
     </row>
     <row r="14">
@@ -11378,10 +11378,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.8834156315349503</v>
+        <v>0.8834156315349508</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.287245081609658</v>
+        <v>0.2872450816096581</v>
       </c>
     </row>
     <row r="15">
@@ -11391,7 +11391,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>14.58478488287688</v>
+        <v>14.58478488287689</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>0.4658018365243973</v>
@@ -11404,7 +11404,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>94.25806451612902</v>
+        <v>94.25806451612905</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>2.061929277735463</v>
@@ -11417,7 +11417,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>3.552270603645034</v>
+        <v>3.552270603645037</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>0</v>
@@ -11430,7 +11430,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.02530998899887835</v>
+        <v>-0.02530998899887851</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>1</v>
@@ -11452,7 +11452,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -11480,10 +11480,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.519478260869565</v>
+        <v>3.519478260869567</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4.720955480839763</v>
+        <v>4.720955800193191</v>
       </c>
     </row>
     <row r="3">
@@ -11496,7 +11496,7 @@
         <v>3.448012329545969</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3.843132845486785</v>
+        <v>3.843133091484296</v>
       </c>
     </row>
     <row r="4">
@@ -11532,10 +11532,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3.718909090909091</v>
+        <v>3.718909090909092</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>12.20774455035246</v>
+        <v>12.20774600360396</v>
       </c>
     </row>
     <row r="7">
@@ -11545,10 +11545,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>-0.868</v>
+        <v>-0.8680000000000002</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-8.791785766573398</v>
+        <v>-8.791787493767707</v>
       </c>
     </row>
     <row r="8">
@@ -11561,7 +11561,7 @@
         <v>21.97</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>38.54462770320806</v>
+        <v>38.54462412563478</v>
       </c>
     </row>
     <row r="9">
@@ -11574,7 +11574,7 @@
         <v>-2.2</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>-32.02740161868049</v>
+        <v>-32.02741339540493</v>
       </c>
     </row>
     <row r="10">
@@ -11584,10 +11584,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3.519478260869565</v>
+        <v>3.519478260869567</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4.720955480839763</v>
+        <v>4.720955800193191</v>
       </c>
     </row>
     <row r="11">
@@ -11600,7 +11600,7 @@
         <v>3.983943837120484</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>13.45428483462503</v>
+        <v>13.45428494013697</v>
       </c>
     </row>
     <row r="12">
@@ -11610,10 +11610,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2.638684739182457</v>
+        <v>2.638684739182456</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.02170278602512823</v>
+        <v>-0.0217036217385676</v>
       </c>
     </row>
     <row r="13">
@@ -11623,10 +11623,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>8.543303212889626</v>
+        <v>8.54330321288962</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.1472125616225912</v>
+        <v>0.147212041724103</v>
       </c>
     </row>
     <row r="14">
@@ -11636,10 +11636,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.8834156315349503</v>
+        <v>0.8834156315349508</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.3508886231314379</v>
+        <v>0.350888644115867</v>
       </c>
     </row>
     <row r="15">
@@ -11649,10 +11649,10 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>14.58478488287688</v>
+        <v>14.58478488287689</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.6671086844656693</v>
+        <v>0.6671086457840698</v>
       </c>
     </row>
     <row r="16">
@@ -11662,10 +11662,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>94.25806451612902</v>
+        <v>94.25806451612905</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.50614502548762</v>
+        <v>2.506144831481828</v>
       </c>
     </row>
   </sheetData>
@@ -11718,13 +11718,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.552270603645034</v>
+        <v>3.552270603645037</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0.3882041321353366</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9.150522391674681</v>
+        <v>9.150522391674688</v>
       </c>
     </row>
     <row r="3">
@@ -11734,13 +11734,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.02530998899887835</v>
+        <v>-0.02530998899887851</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0.08305537019862617</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>-0.3047363335850498</v>
+        <v>-0.3047363335850518</v>
       </c>
     </row>
   </sheetData>
@@ -11761,7 +11761,7 @@
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -11799,16 +11799,16 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.3518264189608741</v>
+        <v>0.3518264189608743</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.0001322452612779051</v>
+        <v>0.0001322452612779038</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>5.670595079073566e-05</v>
+        <v>5.670595079073489e-05</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>6.444721769888924e-05</v>
+        <v>6.444721769888872e-05</v>
       </c>
     </row>
     <row r="3">
@@ -11821,13 +11821,13 @@
         <v>-0.140188581203098</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.1277568081678594</v>
+        <v>0.1277568081678591</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.4457248592970166</v>
+        <v>0.4457248592970162</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.3066839911331238</v>
+        <v>0.3066839911331234</v>
       </c>
     </row>
     <row r="4">
@@ -11843,7 +11843,7 @@
         <v>0.8735038164340262</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.9787208520808428</v>
+        <v>0.9787208520808429</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0.8799447076786946</v>
